--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,44 @@
       </c>
       <c r="F2" t="n">
         <v>1876.88818359375</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1922.650024414062</v>
+      </c>
+      <c r="H2" t="n">
+        <v>45.7618408203125</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.38014408442632</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.170500592010403</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:22</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1924.212646484375</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,6 +641,24 @@
           <t>1878.358643,1878.039185,1878.237549,1879.439819,1878.074219,1878.225952,1879.386230,1879.053955,1879.044678,1878.342041,1878.264038,1878.139282,1877.787598,1876.652588,1877.800659,1878.670288,1878.465576,1877.928467,1878.245361,1877.297241,1878.254639,1877.376221,1877.500732,1876.888184</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1867.079956,1853.800049,1848.000000,1862.380005,1859.180054,1862.400024,1867.239990,1891.560059,1871.300049,1860.670044,1866.189941,1901.089966,1898.119995,1906.329956,1898.010010,1897.400024,1903.540039,1901.050049,1894.589966,1903.540039,1913.900024,1906.300049,1916.170044,1922.650024</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>11.278687,24.239136,30.237549,17.059814,18.894165,15.825928,12.146240,12.506104,7.744629,17.671997,12.074097,22.950684,20.332397,29.677368,20.209351,18.729736,25.074463,23.121582,16.344605,26.242798,35.645385,28.923828,38.669312,45.761840</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.604082,1.307538,1.636231,0.916022,1.016263,0.849760,0.650492,0.661153,0.413864,0.949765,0.646992,1.207238,1.071186,1.556780,1.064765,0.987126,1.317254,1.216253,0.862699,1.378631,1.862448,1.517276,2.018052,2.380144</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1.170500592010403</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>1876.110107,1878.225342,1876.743164,1878.140991,1876.842896,1875.315552,1878.837891,1878.863892,1876.426880,1876.634766,1874.946411,1873.196045,1872.434082,1872.315674,1873.894287,1874.288574,1874.396240,1870.997559,1875.083984,1872.002197,1873.040039,1873.361206,1869.279785,1871.055298</t>
@@ -616,6 +672,49 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>1873.752319,1872.189819,1871.423096,1872.162476,1869.015259,1868.255737,1868.394409,1867.646240,1867.387451,1864.920898,1863.993652,1862.975464,1862.701294,1859.617188,1860.338257,1861.397583,1859.845337,1857.757080,1855.729248,1854.356934,1853.807739,1851.157715,1851.855591,1850.773682</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:22</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1922.106689,1921.976807,1921.923584,1923.354126,1922.268799,1923.040527,1924.221924,1923.919067,1924.363647,1923.906494,1923.789917,1923.495605,1923.073364,1923.078125,1923.819092,1924.204590,1924.286743,1923.670044,1923.880737,1923.137207,1923.478882,1924.149536,1924.512085,1924.212646</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1918.596069,1921.279175,1919.752075,1919.012695,1919.753662,1918.647461,1922.255249,1923.056274,1919.390137,1921.015869,1919.615967,1915.540405,1916.261475,1917.031982,1919.615723,1919.945190,1917.925903,1917.510986,1918.656982,1916.463745,1918.925171,1919.651123,1915.694824,1916.949829</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1908.295654,1905.055298,1901.569824,1901.130859,1896.754395,1895.375000,1894.453247,1892.034790,1890.533325,1887.727539,1886.462402,1882.986450,1884.472046,1881.932007,1879.945557,1879.905273,1878.200439,1877.439575,1871.920776,1869.735229,1869.037476,1868.793945,1869.359497,1868.468750</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1914.096191,1911.877075,1910.408813,1910.932861,1907.463135,1906.320190,1906.426636,1905.360352,1905.336182,1902.955811,1902.255371,1901.376221,1901.234009,1898.608154,1898.078125,1899.094849,1897.905396,1895.765503,1893.212891,1892.153564,1891.392456,1890.412354,1891.694214,1891.198730</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,6 +531,44 @@
       </c>
       <c r="F3" t="n">
         <v>1924.212646484375</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1931.380004882812</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7.1673583984375</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.371100372806872</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3994088277308368</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:29:54</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1933.929077148438</v>
       </c>
     </row>
   </sheetData>
@@ -544,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,6 +740,24 @@
           <t>1922.106689,1921.976807,1921.923584,1923.354126,1922.268799,1923.040527,1924.221924,1923.919067,1924.363647,1923.906494,1923.789917,1923.495605,1923.073364,1923.078125,1923.819092,1924.204590,1924.286743,1923.670044,1923.880737,1923.137207,1923.478882,1924.149536,1924.512085,1924.212646</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1923.359985,1929.260010,1933.589966,1932.890015,1938.619995,1940.800049,1932.849976,1934.609985,1941.609985,1938.939941,1930.150024,1930.760010,1925.300049,1917.300049,1918.949951,1922.640015,1922.180054,1923.170044,1919.599976,1922.800049,1938.130005,1932.420044,1929.069946,1931.380005</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.253296,7.283203,11.666382,9.535889,16.351196,17.759522,8.628052,10.690918,17.246338,15.033447,6.360107,7.264405,2.226685,5.778076,4.869141,1.564575,2.106689,0.500000,4.280761,0.337158,14.651123,8.270508,4.557861,7.167359</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.065162,0.377513,0.603353,0.493349,0.843445,0.915062,0.446390,0.552614,0.888249,0.775344,0.329514,0.376246,0.115654,0.301365,0.253740,0.081376,0.109599,0.025999,0.223003,0.017535,0.755941,0.427987,0.236272,0.371100</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3994088277308368</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>1918.596069,1921.279175,1919.752075,1919.012695,1919.753662,1918.647461,1922.255249,1923.056274,1919.390137,1921.015869,1919.615967,1915.540405,1916.261475,1917.031982,1919.615723,1919.945190,1917.925903,1917.510986,1918.656982,1916.463745,1918.925171,1919.651123,1915.694824,1916.949829</t>
@@ -715,6 +771,49 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>1914.096191,1911.877075,1910.408813,1910.932861,1907.463135,1906.320190,1906.426636,1905.360352,1905.336182,1902.955811,1902.255371,1901.376221,1901.234009,1898.608154,1898.078125,1899.094849,1897.905396,1895.765503,1893.212891,1892.153564,1891.392456,1890.412354,1891.694214,1891.198730</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:29:54</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1931.635742,1931.369995,1931.198486,1932.817505,1931.436768,1931.836182,1933.158081,1931.597290,1932.879517,1932.183105,1931.431763,1932.406494,1932.034180,1931.087769,1932.041992,1933.010376,1933.463867,1933.226196,1933.032959,1933.722778,1933.755981,1934.009399,1934.033813,1933.929077</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1928.073975,1932.305298,1928.927490,1929.368164,1929.626099,1929.529053,1933.316406,1931.882324,1930.062500,1928.925049,1929.187378,1926.090698,1926.639893,1925.365479,1927.712891,1927.973511,1929.208862,1928.648804,1929.272339,1928.428711,1929.325928,1929.254761,1928.118652,1926.447754</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1923.966064,1921.559082,1918.843262,1919.088379,1913.134033,1912.439697,1910.845703,1906.024536,1906.551392,1903.162598,1901.575806,1899.479004,1900.453247,1898.027832,1896.633423,1898.199707,1896.946899,1896.016235,1889.475586,1888.578125,1889.335449,1888.206543,1888.490479,1889.246216</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1927.803589,1925.692139,1924.347900,1925.260620,1922.271851,1920.515869,1919.802979,1917.208008,1918.583984,1915.210571,1914.029785,1914.738892,1914.400024,1911.903076,1910.798828,1913.339355,1913.432617,1910.444946,1907.678223,1908.576416,1907.845825,1906.994507,1907.677002,1907.299683</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,44 @@
       </c>
       <c r="F4" t="n">
         <v>1933.929077148438</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1922.93994140625</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10.98913574218795</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5714757650803995</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4207716709412297</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:34:53</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1922.66796875</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +839,24 @@
           <t>1931.635742,1931.369995,1931.198486,1932.817505,1931.436768,1931.836182,1933.158081,1931.597290,1932.879517,1932.183105,1931.431763,1932.406494,1932.034180,1931.087769,1932.041992,1933.010376,1933.463867,1933.226196,1933.032959,1933.722778,1933.755981,1934.009399,1934.033813,1933.929077</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1935.489990,1918.079956,1916.270020,1912.880005,1919.800049,1923.199951,1929.410034,1926.160034,1915.589966,1938.810059,1932.119995,1941.949951,1949.420044,1937.660034,1929.910034,1924.300049,1926.030029,1937.930054,1937.430054,1933.540039,1931.400024,1927.650024,1926.339966,1922.939941</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3.854248,13.290039,14.928466,19.937500,11.636719,8.636231,3.748047,5.437256,17.289551,6.626954,0.688232,9.543457,17.385864,6.572265,2.131958,8.710327,7.433838,4.703858,4.397095,0.182739,2.355957,6.359375,7.693847,10.989136</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.199136,0.692882,0.779038,1.042277,0.606142,0.449055,0.194259,0.282285,0.902571,0.341805,0.035621,0.491437,0.891848,0.339186,0.110469,0.452649,0.385967,0.242726,0.226955,0.009451,0.121982,0.329903,0.399402,0.571476</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4207716709412297</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>1928.073975,1932.305298,1928.927490,1929.368164,1929.626099,1929.529053,1933.316406,1931.882324,1930.062500,1928.925049,1929.187378,1926.090698,1926.639893,1925.365479,1927.712891,1927.973511,1929.208862,1928.648804,1929.272339,1928.428711,1929.325928,1929.254761,1928.118652,1926.447754</t>
@@ -814,6 +870,49 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>1927.803589,1925.692139,1924.347900,1925.260620,1922.271851,1920.515869,1919.802979,1917.208008,1918.583984,1915.210571,1914.029785,1914.738892,1914.400024,1911.903076,1910.798828,1913.339355,1913.432617,1910.444946,1907.678223,1908.576416,1907.845825,1906.994507,1907.677002,1907.299683</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:34:53</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1923.312134,1922.222534,1922.395264,1923.202148,1921.877319,1923.069580,1924.160889,1922.911865,1924.364136,1924.469116,1923.682983,1924.203735,1924.135010,1922.909180,1923.202148,1923.856323,1924.278564,1923.128418,1922.611450,1923.443237,1923.555176,1923.101807,1922.541382,1922.667969</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1921.523071,1923.554321,1920.560669,1921.793335,1921.431885,1923.258545,1922.948242,1921.769897,1922.323486,1923.912964,1921.722412,1918.568970,1919.353882,1920.286987,1920.049438,1919.047363,1920.383301,1919.038208,1919.850342,1917.868896,1920.055786,1918.323730,1918.989990,1918.016724</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1914.692261,1911.966431,1909.109375,1908.926636,1903.461426,1903.766846,1902.063110,1898.637207,1898.887939,1897.128418,1894.619019,1894.693481,1893.580322,1890.886963,1889.205933,1889.475830,1888.483398,1886.867310,1880.868530,1881.725464,1880.990234,1879.492554,1878.336670,1879.314209</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1918.861694,1915.535034,1914.469727,1914.319458,1911.263062,1910.664429,1910.694824,1908.146606,1909.544678,1907.649658,1906.311279,1907.446045,1906.310791,1903.593262,1903.277710,1903.894775,1903.806030,1900.688232,1898.662231,1899.283813,1898.433105,1896.565918,1896.205688,1896.426880</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,6 +607,44 @@
       </c>
       <c r="F5" t="n">
         <v>1922.66796875</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1878</v>
+      </c>
+      <c r="H5" t="n">
+        <v>44.66796875</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.378486088924388</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.512613994730014</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:18</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1868.601196289062</v>
       </c>
     </row>
   </sheetData>
@@ -620,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +938,24 @@
           <t>1923.312134,1922.222534,1922.395264,1923.202148,1921.877319,1923.069580,1924.160889,1922.911865,1924.364136,1924.469116,1923.682983,1924.203735,1924.135010,1922.909180,1923.202148,1923.856323,1924.278564,1923.128418,1922.611450,1923.443237,1923.555176,1923.101807,1922.541382,1922.667969</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1918.459961,1921.949951,1924.400024,1914.199951,1925.550049,1923.180054,1927.300049,1925.260010,1903.099976,1897.349976,1895.650024,1893.800049,1886.310059,1877.000000,1879.640015,1874.140015,1884.469971,1881.199951,1881.969971,1876.910034,1869.949951,1871.219971,1867.819946,1878.000000</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4.852173,0.272583,2.004760,9.002197,3.672730,0.110474,3.139160,2.348145,21.264160,27.119140,28.032959,30.403686,37.824951,45.909180,43.562133,49.716308,39.808593,41.928467,40.641479,46.533203,53.605225,51.881836,54.721436,44.667969</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.252920,0.014183,0.104176,0.470285,0.190737,0.005744,0.162879,0.121965,1.117343,1.429317,1.478805,1.605433,2.005235,2.445881,2.317579,2.652753,2.112456,2.228815,2.159518,2.479245,2.866666,2.772621,2.929695,2.378486</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1.512613994730014</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>1921.523071,1923.554321,1920.560669,1921.793335,1921.431885,1923.258545,1922.948242,1921.769897,1922.323486,1923.912964,1921.722412,1918.568970,1919.353882,1920.286987,1920.049438,1919.047363,1920.383301,1919.038208,1919.850342,1917.868896,1920.055786,1918.323730,1918.989990,1918.016724</t>
@@ -913,6 +969,49 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>1918.861694,1915.535034,1914.469727,1914.319458,1911.263062,1910.664429,1910.694824,1908.146606,1909.544678,1907.649658,1906.311279,1907.446045,1906.310791,1903.593262,1903.277710,1903.894775,1903.806030,1900.688232,1898.662231,1899.283813,1898.433105,1896.565918,1896.205688,1896.426880</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:18</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1876.300659,1875.324219,1874.927002,1875.155762,1873.758911,1873.686523,1874.026978,1872.110962,1871.876831,1872.324463,1871.303101,1872.113770,1871.780273,1870.908936,1870.880249,1870.789307,1870.201050,1869.468628,1869.466064,1869.734009,1869.717041,1869.558228,1869.111938,1868.601196</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1874.995239,1877.026123,1872.658081,1873.697754,1874.044189,1874.470459,1873.300293,1869.890991,1871.699951,1873.455811,1868.984131,1868.216553,1870.091553,1871.115112,1869.654175,1866.562256,1869.555298,1868.364990,1870.434082,1865.094971,1869.160034,1864.288574,1866.813843,1867.356689</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1863.602905,1860.825317,1856.625244,1855.645020,1851.661011,1849.103271,1848.472900,1845.922729,1843.220825,1842.428345,1839.741699,1840.885986,1838.921631,1836.610107,1835.619629,1834.282227,1832.008545,1830.222412,1825.516846,1825.472290,1823.302979,1821.725098,1820.944702,1820.308716</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1868.525879,1865.529541,1862.875610,1862.227905,1858.988525,1857.893433,1858.034058,1854.533569,1854.873779,1853.682861,1851.861938,1853.444214,1851.435913,1848.985962,1850.234009,1848.502441,1846.597412,1844.185669,1843.367676,1843.233765,1841.786011,1839.985474,1840.338379,1839.667725</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,6 +645,44 @@
       </c>
       <c r="F6" t="n">
         <v>1868.601196289062</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1857.829956054688</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10.77124023437455</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.5797753556115811</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5695001129243402</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:11</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1856.4150390625</v>
       </c>
     </row>
   </sheetData>
@@ -658,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,6 +1037,24 @@
           <t>1876.300659,1875.324219,1874.927002,1875.155762,1873.758911,1873.686523,1874.026978,1872.110962,1871.876831,1872.324463,1871.303101,1872.113770,1871.780273,1870.908936,1870.880249,1870.789307,1870.201050,1869.468628,1869.466064,1869.734009,1869.717041,1869.558228,1869.111938,1868.601196</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1874.380005,1879.280029,1886.750000,1894.640015,1886.660034,1886.660034,1882.400024,1882.760010,1870.709961,1854.900024,1860.880005,1860.000000,1855.660034,1864.900024,1860.800049,1862.030029,1859.229980,1855.619995,1857.680054,1859.880005,1858.510010,1858.130005,1857.900024,1857.829956</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.920654,3.955810,11.822998,19.484253,12.901123,12.973511,8.373046,10.649048,1.166870,17.424439,10.423096,12.113770,16.120239,6.008912,10.080200,8.759278,10.971070,13.848633,11.786010,9.854004,11.207031,11.428223,11.211914,10.771240</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.102469,0.210496,0.626633,1.028388,0.683808,0.687644,0.444807,0.565608,0.062376,0.939373,0.560117,0.651278,0.868706,0.322211,0.541713,0.470415,0.590087,0.746308,0.634448,0.529819,0.603012,0.615039,0.603472,0.579775</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5695001129243402</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>1874.995239,1877.026123,1872.658081,1873.697754,1874.044189,1874.470459,1873.300293,1869.890991,1871.699951,1873.455811,1868.984131,1868.216553,1870.091553,1871.115112,1869.654175,1866.562256,1869.555298,1868.364990,1870.434082,1865.094971,1869.160034,1864.288574,1866.813843,1867.356689</t>
@@ -1012,6 +1068,49 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>1868.525879,1865.529541,1862.875610,1862.227905,1858.988525,1857.893433,1858.034058,1854.533569,1854.873779,1853.682861,1851.861938,1853.444214,1851.435913,1848.985962,1850.234009,1848.502441,1846.597412,1844.185669,1843.367676,1843.233765,1841.786011,1839.985474,1840.338379,1839.667725</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:11</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1858.778076,1858.614380,1858.978394,1859.696899,1858.681030,1858.819946,1859.107300,1858.393188,1857.899536,1857.687622,1856.770020,1857.303711,1857.073730,1856.626465,1856.685181,1856.846069,1856.557739,1856.501953,1856.779175,1856.503906,1856.624268,1856.552002,1856.068604,1856.415039</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1856.978882,1859.250122,1858.290649,1858.239014,1858.067261,1858.626587,1857.881104,1856.776245,1856.502197,1858.543335,1855.119751,1854.782593,1855.194336,1857.222900,1855.984985,1853.820312,1856.369507,1856.615845,1857.867310,1852.473877,1856.978149,1852.660522,1854.091797,1855.484741</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1850.106323,1848.195679,1844.727905,1844.183960,1841.231567,1838.956055,1837.745850,1836.455200,1833.162476,1831.955566,1830.518799,1830.769165,1829.427612,1828.211792,1827.713501,1826.371216,1824.625122,1824.114990,1821.048828,1820.837402,1818.875244,1816.894043,1815.944702,1815.709717</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1853.727905,1851.802734,1849.970581,1849.584595,1847.156616,1846.324097,1846.704712,1844.244873,1843.990234,1841.677856,1840.348022,1841.359985,1840.441528,1838.131592,1840.260254,1839.168091,1837.308838,1835.847168,1835.809204,1835.197266,1833.726562,1831.874878,1832.199951,1831.685059</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,6 +683,44 @@
       </c>
       <c r="F7" t="n">
         <v>1856.4150390625</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1880.719970703125</v>
+      </c>
+      <c r="H7" t="n">
+        <v>24.304931640625</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.292320601643761</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5787421804040652</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:42:06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1887.635375976562</v>
       </c>
     </row>
   </sheetData>
@@ -696,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,6 +1136,24 @@
           <t>1858.778076,1858.614380,1858.978394,1859.696899,1858.681030,1858.819946,1859.107300,1858.393188,1857.899536,1857.687622,1856.770020,1857.303711,1857.073730,1856.626465,1856.685181,1856.846069,1856.557739,1856.501953,1856.779175,1856.503906,1856.624268,1856.552002,1856.068604,1856.415039</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1859.619995,1856.640015,1857.180054,1854.489990,1852.079956,1856.540039,1856.770020,1856.060059,1858.369995,1865.260010,1867.050049,1866.099976,1866.329956,1871.359985,1873.709961,1873.060059,1870.500000,1870.989990,1874.310059,1872.239990,1879.400024,1877.040039,1879.140015,1880.719971</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.841919,1.974365,1.798340,5.206909,6.601074,2.279907,2.337280,2.333129,0.470459,7.572388,10.280029,8.796265,9.256226,14.733520,17.024780,16.213990,13.942261,14.488037,17.530884,15.736084,22.775756,20.488037,23.071411,24.304932</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.045274,0.106341,0.096832,0.280773,0.356414,0.122804,0.125879,0.125703,0.025316,0.405970,0.550603,0.471372,0.495959,0.787316,0.908613,0.865642,0.745376,0.774351,0.935325,0.840495,1.211863,1.091508,1.227764,1.292321</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5787421804040652</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>1856.978882,1859.250122,1858.290649,1858.239014,1858.067261,1858.626587,1857.881104,1856.776245,1856.502197,1858.543335,1855.119751,1854.782593,1855.194336,1857.222900,1855.984985,1853.820312,1856.369507,1856.615845,1857.867310,1852.473877,1856.978149,1852.660522,1854.091797,1855.484741</t>
@@ -1111,6 +1167,49 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>1853.727905,1851.802734,1849.970581,1849.584595,1847.156616,1846.324097,1846.704712,1844.244873,1843.990234,1841.677856,1840.348022,1841.359985,1840.441528,1838.131592,1840.260254,1839.168091,1837.308838,1835.847168,1835.809204,1835.197266,1833.726562,1831.874878,1832.199951,1831.685059</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:42:06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1881.412231,1881.984375,1882.808350,1884.269043,1883.791138,1884.875610,1885.277100,1884.803101,1884.922974,1885.351562,1885.191650,1885.326538,1885.804077,1885.701294,1886.467651,1886.638062,1886.578369,1886.474854,1886.202148,1887.045410,1886.551270,1886.645142,1886.743896,1887.635376</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1880.588013,1882.973999,1882.490601,1882.288574,1884.777222,1884.334839,1885.192627,1884.894897,1883.489502,1884.584961,1883.456543,1882.361816,1884.910278,1886.505981,1885.958862,1884.145264,1885.902710,1885.590088,1886.654175,1883.213501,1885.802246,1881.855225,1884.182983,1885.884766</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1874.510742,1873.605225,1870.833862,1871.738403,1868.613647,1867.894409,1867.466187,1865.268311,1863.318359,1861.711182,1861.113525,1859.234863,1858.787354,1857.782959,1857.553711,1856.405518,1854.758545,1853.800781,1849.490967,1850.008301,1848.265137,1846.321655,1845.251953,1845.085449</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1878.066895,1876.958496,1875.958496,1876.371948,1873.588867,1874.452393,1874.211670,1872.816406,1872.814209,1870.904663,1869.976807,1869.563354,1870.097168,1867.411255,1869.449951,1869.113647,1867.477051,1865.698364,1864.358887,1864.613525,1862.616089,1861.547607,1861.435425,1862.186523</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,6 +721,44 @@
       </c>
       <c r="F8" t="n">
         <v>1887.635375976562</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1945.43994140625</v>
+      </c>
+      <c r="H8" t="n">
+        <v>57.80456542968795</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.97128501370771</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.247287537898723</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:37</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1951.257446289062</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1197,6 +1235,24 @@
           <t>1881.412231,1881.984375,1882.808350,1884.269043,1883.791138,1884.875610,1885.277100,1884.803101,1884.922974,1885.351562,1885.191650,1885.326538,1885.804077,1885.701294,1886.467651,1886.638062,1886.578369,1886.474854,1886.202148,1887.045410,1886.551270,1886.645142,1886.743896,1887.635376</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1884.680054,1881.739990,1883.380005,1879.849976,1879.829956,1882.089966,1884.319946,1884.229980,1884.780029,1885.010010,1896.939941,1913.290039,1914.520020,1909.550049,1912.739990,1912.479980,1912.020020,1924.180054,1947.910034,1952.890015,1940.680054,1946.300049,1941.250000,1945.439941</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3.267823,0.244385,0.571655,4.419067,3.961182,2.785644,0.957154,0.573121,0.142945,0.341552,11.748291,27.963501,28.715943,23.848755,26.272339,25.841918,25.441651,37.705200,61.707886,65.844605,54.128784,59.654907,54.506104,57.804565</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.173389,0.012987,0.030353,0.235076,0.210720,0.148008,0.050796,0.030417,0.007584,0.018119,0.619329,1.461540,1.499903,1.248920,1.373545,1.351226,1.330616,1.959546,3.167902,3.371649,2.789166,3.065042,2.807784,2.971285</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1.247287537898723</v>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>1880.588013,1882.973999,1882.490601,1882.288574,1884.777222,1884.334839,1885.192627,1884.894897,1883.489502,1884.584961,1883.456543,1882.361816,1884.910278,1886.505981,1885.958862,1884.145264,1885.902710,1885.590088,1886.654175,1883.213501,1885.802246,1881.855225,1884.182983,1885.884766</t>
@@ -1210,6 +1266,49 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>1878.066895,1876.958496,1875.958496,1876.371948,1873.588867,1874.452393,1874.211670,1872.816406,1872.814209,1870.904663,1869.976807,1869.563354,1870.097168,1867.411255,1869.449951,1869.113647,1867.477051,1865.698364,1864.358887,1864.613525,1862.616089,1861.547607,1861.435425,1862.186523</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:37</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1947.666748,1947.828735,1950.007935,1950.454346,1950.518799,1950.798828,1951.224976,1950.685669,1950.974121,1950.707520,1951.327271,1951.873535,1951.626587,1950.165039,1951.961914,1952.390991,1952.753662,1951.643921,1951.626099,1951.967285,1951.878662,1950.826904,1951.544800,1951.257446</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1944.099976,1947.925781,1948.393311,1947.365234,1950.603027,1946.888672,1950.648682,1951.340210,1945.178345,1948.055908,1947.977539,1945.038818,1947.426636,1948.155518,1949.336426,1950.428833,1950.526367,1946.185913,1947.681519,1948.248169,1947.592773,1948.738281,1945.263672,1944.960693</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1937.119751,1934.176147,1931.954712,1930.549194,1927.274902,1924.460449,1923.004639,1922.071899,1920.583008,1917.338257,1917.511230,1915.174805,1915.206909,1912.083252,1911.880493,1912.241943,1911.099365,1909.769653,1904.328369,1902.159546,1901.606934,1898.240479,1897.728149,1896.207764</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1941.004761,1939.193726,1939.689209,1937.986084,1935.918457,1933.535645,1934.435547,1932.643066,1931.944092,1929.349365,1928.855591,1928.857788,1929.885742,1924.936401,1926.044189,1928.107422,1926.621582,1925.179199,1922.125366,1921.393677,1920.002563,1916.821411,1917.221680,1916.836182</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,44 @@
       </c>
       <c r="F9" t="n">
         <v>1951.257446289062</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1878.02001953125</v>
+      </c>
+      <c r="H9" t="n">
+        <v>73.23742675781205</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.899714912309186</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.403280943835719</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:43</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1873.958251953125</v>
       </c>
     </row>
   </sheetData>
@@ -772,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1296,6 +1334,24 @@
           <t>1947.666748,1947.828735,1950.007935,1950.454346,1950.518799,1950.798828,1951.224976,1950.685669,1950.974121,1950.707520,1951.327271,1951.873535,1951.626587,1950.165039,1951.961914,1952.390991,1952.753662,1951.643921,1951.626099,1951.967285,1951.878662,1950.826904,1951.544800,1951.257446</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1951.540039,1963.930054,1966.770020,1962.689941,1963.300049,1963.420044,1965.920044,1957.979980,1955.579956,1959.089966,1930.170044,1925.439941,1938.500000,1941.900024,1937.199951,1946.839966,1945.000000,1940.000000,1892.109985,1890.670044,1877.310059,1874.130005,1874.000000,1878.020020</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3.873291,16.101319,16.762085,12.235595,12.781250,12.621216,14.695068,7.294311,4.605835,8.382446,21.157227,26.433594,13.126587,8.265015,14.761963,5.551025,7.753662,11.643921,59.516114,61.297241,74.568603,76.696899,77.544800,73.237426</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.198474,0.819852,0.852265,0.623409,0.651008,0.642818,0.747491,0.372543,0.235523,0.427874,1.096133,1.372860,0.677152,0.425615,0.762026,0.285130,0.398646,0.600202,3.145489,3.242091,3.972098,4.092400,4.137930,3.899715</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1.403280943835719</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>1944.099976,1947.925781,1948.393311,1947.365234,1950.603027,1946.888672,1950.648682,1951.340210,1945.178345,1948.055908,1947.977539,1945.038818,1947.426636,1948.155518,1949.336426,1950.428833,1950.526367,1946.185913,1947.681519,1948.248169,1947.592773,1948.738281,1945.263672,1944.960693</t>
@@ -1309,6 +1365,49 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>1941.004761,1939.193726,1939.689209,1937.986084,1935.918457,1933.535645,1934.435547,1932.643066,1931.944092,1929.349365,1928.855591,1928.857788,1929.885742,1924.936401,1926.044189,1928.107422,1926.621582,1925.179199,1922.125366,1921.393677,1920.002563,1916.821411,1917.221680,1916.836182</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:43</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1878.557007,1877.838013,1877.587402,1877.408813,1876.365723,1876.886475,1877.092529,1876.417358,1876.209351,1876.264893,1875.429688,1876.120850,1875.320801,1874.867920,1876.399414,1875.276611,1875.242432,1875.533813,1874.862061,1874.967896,1875.013794,1874.378052,1873.889526,1873.958252</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1875.049438,1879.215454,1877.323364,1877.311646,1877.494629,1877.812744,1878.314819,1876.479248,1873.663452,1877.831299,1875.002075,1874.921509,1872.362549,1876.119141,1875.439575,1873.797607,1874.877197,1873.963867,1874.792969,1875.433838,1875.133057,1873.701050,1872.861084,1872.181885</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1867.591064,1863.997925,1859.163452,1854.928833,1851.404785,1848.857056,1846.546631,1843.843628,1842.378784,1840.590210,1837.947021,1837.145264,1837.431641,1835.134888,1834.386230,1831.771118,1829.850708,1829.529541,1823.381470,1822.119629,1821.160034,1819.134277,1818.233521,1817.799927</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1872.698608,1869.815796,1866.005615,1863.829956,1860.178955,1858.681763,1858.807617,1855.790283,1855.159790,1854.082886,1851.381348,1853.455200,1852.119385,1849.508789,1851.251099,1850.250000,1847.664551,1847.313477,1844.851440,1844.061279,1843.536987,1841.013306,1840.527954,1840.710205</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,44 @@
       </c>
       <c r="F10" t="n">
         <v>1873.958251953125</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1903.849975585938</v>
+      </c>
+      <c r="H10" t="n">
+        <v>29.8917236328125</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.570067180509477</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.168539024476736</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:41</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1896.96337890625</v>
       </c>
     </row>
   </sheetData>
@@ -810,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1395,6 +1433,24 @@
           <t>1878.557007,1877.838013,1877.587402,1877.408813,1876.365723,1876.886475,1877.092529,1876.417358,1876.209351,1876.264893,1875.429688,1876.120850,1875.320801,1874.867920,1876.399414,1875.276611,1875.242432,1875.533813,1874.862061,1874.967896,1875.013794,1874.378052,1873.889526,1873.958252</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1877.369995,1881.310059,1886.599976,1881.880005,1882.489990,1874.260010,1876.920044,1874.790039,1890.400024,1872.099976,1886.890015,1918.300049,1924.010010,1899.489990,1908.819946,1919.510010,1916.160034,1921.849976,1909.760010,1904.400024,1915.170044,1903.270020,1908.400024,1903.849976</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1.187012,3.472046,9.012574,4.471192,6.124267,2.626465,0.172485,1.627319,14.190673,4.164917,11.460327,42.179199,48.689209,24.622070,32.420532,44.233399,40.917602,46.316163,34.897949,29.432128,40.156250,28.891968,34.510498,29.891724</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.063227,0.184555,0.477715,0.237592,0.325328,0.140133,0.009190,0.086800,0.750670,0.222473,0.607366,2.198780,2.530611,1.296246,1.698459,2.304411,2.135396,2.409978,1.827347,1.545480,2.096746,1.518017,1.808347,1.570067</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1.168539024476736</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>1875.049438,1879.215454,1877.323364,1877.311646,1877.494629,1877.812744,1878.314819,1876.479248,1873.663452,1877.831299,1875.002075,1874.921509,1872.362549,1876.119141,1875.439575,1873.797607,1874.877197,1873.963867,1874.792969,1875.433838,1875.133057,1873.701050,1872.861084,1872.181885</t>
@@ -1408,6 +1464,49 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>1872.698608,1869.815796,1866.005615,1863.829956,1860.178955,1858.681763,1858.807617,1855.790283,1855.159790,1854.082886,1851.381348,1853.455200,1852.119385,1849.508789,1851.251099,1850.250000,1847.664551,1847.313477,1844.851440,1844.061279,1843.536987,1841.013306,1840.527954,1840.710205</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:41</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1903.475098,1902.457397,1902.287476,1903.167725,1902.134277,1902.820435,1902.563477,1902.288330,1902.313599,1901.522949,1901.016968,1901.482910,1901.381592,1901.222168,1901.206299,1901.465332,1900.760986,1900.335693,1900.139893,1899.451416,1899.301147,1898.492676,1897.596436,1896.963379</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1901.224976,1902.128662,1901.415771,1900.717163,1901.047607,1901.027466,1899.970703,1899.656982,1898.827393,1899.693237,1898.890869,1895.612549,1896.584717,1898.598877,1898.971313,1898.166504,1896.912109,1897.532104,1895.792725,1895.196411,1894.581543,1893.692993,1893.232666,1889.966064</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1890.054199,1886.678955,1883.089844,1882.566162,1877.807617,1876.611572,1874.519287,1871.871338,1868.259521,1865.253906,1862.412476,1861.984131,1860.520874,1859.072144,1856.874390,1856.001465,1854.035400,1852.958740,1846.616577,1844.941406,1844.170898,1842.492920,1840.198486,1838.665527</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1895.833862,1892.930786,1890.611572,1890.118774,1887.774048,1886.336914,1885.213257,1883.735962,1882.798828,1880.519165,1878.205933,1878.198608,1877.787109,1875.856689,1875.769531,1875.378296,1873.479126,1871.688477,1869.521606,1868.347290,1867.950317,1864.658936,1863.750488,1862.173096</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,6 +835,44 @@
       </c>
       <c r="F11" t="n">
         <v>1896.96337890625</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1908.4599609375</v>
+      </c>
+      <c r="H11" t="n">
+        <v>11.49658203125</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.6024010074386099</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5342026917354792</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:58:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1906.95361328125</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,6 +1532,24 @@
           <t>1903.475098,1902.457397,1902.287476,1903.167725,1902.134277,1902.820435,1902.563477,1902.288330,1902.313599,1901.522949,1901.016968,1901.482910,1901.381592,1901.222168,1901.206299,1901.465332,1900.760986,1900.335693,1900.139893,1899.451416,1899.301147,1898.492676,1897.596436,1896.963379</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1903.069946,1910.219971,1917.810059,1921.280029,1912.859985,1919.979980,1909.829956,1913.010010,1902.930054,1907.300049,1892.650024,1889.810059,1892.709961,1913.739990,1918.199951,1886.619995,1882.469971,1896.050049,1904.709961,1907.989990,1895.829956,1914.300049,1908.459961,1908.459961</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.405152,7.762574,15.522583,18.112304,10.725708,17.159545,7.266479,10.721680,0.616455,5.777100,8.366944,11.672851,8.671631,12.517822,16.993652,14.845337,18.291015,4.285644,4.570068,8.538574,3.471191,15.807373,10.863525,11.496582</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.021289,0.406371,0.809391,0.942721,0.560716,0.893736,0.380478,0.560461,0.032395,0.302894,0.442076,0.617673,0.458160,0.654103,0.885917,0.786875,0.971650,0.226030,0.239935,0.447517,0.183096,0.825752,0.569230,0.602401</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5342026917354792</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>1901.224976,1902.128662,1901.415771,1900.717163,1901.047607,1901.027466,1899.970703,1899.656982,1898.827393,1899.693237,1898.890869,1895.612549,1896.584717,1898.598877,1898.971313,1898.166504,1896.912109,1897.532104,1895.792725,1895.196411,1894.581543,1893.692993,1893.232666,1889.966064</t>
@@ -1507,6 +1563,49 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>1895.833862,1892.930786,1890.611572,1890.118774,1887.774048,1886.336914,1885.213257,1883.735962,1882.798828,1880.519165,1878.205933,1878.198608,1877.787109,1875.856689,1875.769531,1875.378296,1873.479126,1871.688477,1869.521606,1868.347290,1867.950317,1864.658936,1863.750488,1862.173096</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:58:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1907.798340,1908.629028,1908.299316,1909.381714,1908.351318,1908.571533,1909.152832,1908.408936,1908.630737,1908.679688,1907.516235,1908.447632,1908.961792,1908.100830,1908.295654,1908.489990,1908.729980,1907.592285,1907.655396,1908.088989,1907.949951,1907.433960,1907.288574,1906.953613</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1907.226196,1907.578369,1906.979248,1907.612183,1908.562622,1906.952026,1909.161377,1906.396973,1906.905518,1906.209839,1905.260498,1904.896240,1906.059326,1906.445312,1906.633423,1904.761108,1905.429199,1906.047974,1905.501343,1902.353516,1904.893066,1902.465332,1904.212524,1903.315430</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1889.549194,1887.593872,1884.312012,1885.146362,1881.772705,1881.259033,1879.542480,1876.953613,1874.737915,1874.014893,1870.991089,1870.597168,1869.099609,1867.337524,1865.854126,1865.015381,1863.484375,1861.997314,1858.044800,1858.842407,1857.162476,1856.608643,1854.853271,1853.720093</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1897.032104,1895.234863,1893.281860,1893.882935,1891.515259,1890.451294,1890.603638,1888.736206,1888.253052,1887.476318,1884.331787,1885.401245,1885.257690,1882.136719,1883.533813,1882.781250,1880.930176,1879.329346,1878.249878,1878.264282,1877.637329,1876.760864,1876.275635,1875.279663</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,6 +873,44 @@
       </c>
       <c r="F12" t="n">
         <v>1906.95361328125</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1902.180053710938</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.7735595703125</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2509520358495941</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4572756779850879</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:39:52</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1896.601196289062</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1593,6 +1631,24 @@
           <t>1907.798340,1908.629028,1908.299316,1909.381714,1908.351318,1908.571533,1909.152832,1908.408936,1908.630737,1908.679688,1907.516235,1908.447632,1908.961792,1908.100830,1908.295654,1908.489990,1908.729980,1907.592285,1907.655396,1908.088989,1907.949951,1907.433960,1907.288574,1906.953613</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1907.540039,1899.319946,1903.800049,1898.599976,1900.459961,1912.599976,1915.489990,1915.910034,1920.550049,1922.890015,1927.890015,1915.680054,1916.699951,1917.339966,1918.670044,1914.260010,1922.079956,1919.560059,1916.890015,1924.119995,1916.819946,1914.939941,1908.400024,1902.180054</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.258301,9.309082,4.499267,10.781738,7.891357,4.028443,6.337158,7.501098,11.919312,14.210327,20.373780,7.232422,7.738159,9.239136,10.374390,5.770020,13.349976,11.967774,9.234619,16.031006,8.869995,7.505981,1.111450,4.773559</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.013541,0.490127,0.236331,0.567878,0.415234,0.210627,0.330837,0.391516,0.620620,0.739009,1.056792,0.377538,0.403723,0.481873,0.540707,0.301423,0.694559,0.623464,0.481750,0.833160,0.462745,0.391970,0.058240,0.250952</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4572756779850879</v>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>1907.226196,1907.578369,1906.979248,1907.612183,1908.562622,1906.952026,1909.161377,1906.396973,1906.905518,1906.209839,1905.260498,1904.896240,1906.059326,1906.445312,1906.633423,1904.761108,1905.429199,1906.047974,1905.501343,1902.353516,1904.893066,1902.465332,1904.212524,1903.315430</t>
@@ -1606,6 +1662,49 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>1897.032104,1895.234863,1893.281860,1893.882935,1891.515259,1890.451294,1890.603638,1888.736206,1888.253052,1887.476318,1884.331787,1885.401245,1885.257690,1882.136719,1883.533813,1882.781250,1880.930176,1879.329346,1878.249878,1878.264282,1877.637329,1876.760864,1876.275635,1875.279663</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:39:52</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1903.798096,1903.498047,1902.154419,1903.682007,1902.205078,1903.057739,1903.742554,1902.830566,1903.384277,1903.014160,1901.690552,1902.155640,1901.505127,1900.865723,1901.072388,1900.834106,1899.854980,1898.567261,1898.445190,1898.380493,1898.666748,1898.199951,1897.044678,1896.601196</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1902.950684,1902.591675,1901.013916,1903.422974,1904.355713,1901.220825,1902.550049,1900.813232,1899.071899,1899.376953,1897.787231,1897.844116,1898.275391,1897.609253,1896.088013,1895.393433,1893.971802,1893.847046,1891.863037,1889.149414,1890.961182,1889.375610,1888.837891,1887.612427</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1892.308594,1888.390747,1882.568726,1882.585327,1877.191528,1875.193481,1873.481445,1870.303467,1867.766968,1865.507568,1862.969482,1860.521973,1856.429077,1854.211426,1851.737793,1848.871826,1844.836060,1842.400391,1836.317627,1834.291748,1832.737427,1831.439209,1828.440796,1826.403198</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1897.326660,1894.194580,1890.213745,1890.755371,1887.546021,1885.661377,1886.122803,1884.518921,1883.437134,1882.313232,1879.021484,1878.303467,1876.864502,1873.047485,1873.070557,1871.958740,1868.231201,1866.083252,1863.277344,1861.996094,1861.174927,1859.740723,1858.302246,1857.627930</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,44 @@
       </c>
       <c r="F13" t="n">
         <v>1896.601196289062</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1866.339965820312</v>
+      </c>
+      <c r="H13" t="n">
+        <v>30.26123046874955</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.621421124926124</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.461208701461971</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:40:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>24</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1863.68896484375</v>
       </c>
     </row>
   </sheetData>
@@ -924,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1692,6 +1730,24 @@
           <t>1903.798096,1903.498047,1902.154419,1903.682007,1902.205078,1903.057739,1903.742554,1902.830566,1903.384277,1903.014160,1901.690552,1902.155640,1901.505127,1900.865723,1901.072388,1900.834106,1899.854980,1898.567261,1898.445190,1898.380493,1898.666748,1898.199951,1897.044678,1896.601196</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1903.920044,1904.400024,1900.800049,1888.239990,1888.619995,1881.930054,1885.180054,1882.599976,1880.560059,1864.329956,1857.300049,1860.560059,1862.979980,1873.270020,1869.780029,1866.520020,1860.400024,1860.000000,1859.630005,1860.640015,1862.859985,1865.160034,1866.569946,1866.339966</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.121948,0.901977,1.354370,15.442017,13.585083,21.127685,18.562500,20.230590,22.824218,38.684204,44.390503,41.595581,38.525147,27.595703,31.292359,34.314086,39.454956,38.567261,38.815185,37.740478,35.806763,33.039917,30.474732,30.261230</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.006405,0.047363,0.071253,0.817799,0.719313,1.122660,0.984654,1.074609,1.213693,2.074966,2.390056,2.235648,2.067931,1.473130,1.673585,1.838399,2.120778,2.073509,2.087253,2.028360,1.922139,1.771425,1.632660,1.621421</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1.461208701461971</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>1902.950684,1902.591675,1901.013916,1903.422974,1904.355713,1901.220825,1902.550049,1900.813232,1899.071899,1899.376953,1897.787231,1897.844116,1898.275391,1897.609253,1896.088013,1895.393433,1893.971802,1893.847046,1891.863037,1889.149414,1890.961182,1889.375610,1888.837891,1887.612427</t>
@@ -1705,6 +1761,49 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>1897.326660,1894.194580,1890.213745,1890.755371,1887.546021,1885.661377,1886.122803,1884.518921,1883.437134,1882.313232,1879.021484,1878.303467,1876.864502,1873.047485,1873.070557,1871.958740,1868.231201,1866.083252,1863.277344,1861.996094,1861.174927,1859.740723,1858.302246,1857.627930</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:40:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>24</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1866.206787,1866.521118,1866.386475,1866.568115,1865.661133,1865.907471,1866.345581,1865.450928,1864.826416,1864.843018,1864.274170,1864.350342,1864.697266,1864.208496,1864.768921,1863.792480,1864.148682,1863.886963,1863.419312,1864.646851,1864.269287,1864.222290,1863.227173,1863.688965</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1863.502686,1865.693115,1866.137451,1865.952148,1866.265381,1866.085693,1866.596191,1864.134521,1864.290405,1865.989746,1863.583130,1863.214600,1863.882080,1864.758301,1864.936646,1860.813354,1862.210815,1863.516235,1863.041870,1861.056519,1863.137939,1860.505249,1861.529541,1863.203003</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1857.710693,1855.422241,1851.652588,1850.546875,1847.097900,1845.867676,1845.177368,1843.304810,1841.054199,1839.625732,1838.374634,1837.517822,1836.430786,1834.195557,1834.129150,1830.950684,1828.829712,1827.834717,1822.582031,1823.016479,1822.421387,1820.943481,1819.099365,1818.519775</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1861.335205,1859.399292,1857.505615,1856.454224,1854.189941,1852.550293,1853.209595,1851.779419,1851.716797,1849.622559,1847.684326,1848.387085,1848.348389,1844.934937,1846.779663,1844.785156,1843.149170,1841.239258,1839.181885,1839.997559,1839.236694,1838.462891,1837.510010,1837.296997</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -949,6 +949,44 @@
       </c>
       <c r="F14" t="n">
         <v>1863.68896484375</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1876.469970703125</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12.781005859375</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6811196586634358</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5209493330757299</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:50</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1867.945434570312</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +1000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1791,6 +1829,24 @@
           <t>1866.206787,1866.521118,1866.386475,1866.568115,1865.661133,1865.907471,1866.345581,1865.450928,1864.826416,1864.843018,1864.274170,1864.350342,1864.697266,1864.208496,1864.768921,1863.792480,1864.148682,1863.886963,1863.419312,1864.646851,1864.269287,1864.222290,1863.227173,1863.688965</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1867.910034,1865.579956,1868.890015,1867.680054,1867.599976,1866.199951,1865.579956,1865.189941,1867.219971,1867.410034,1873.410034,1868.439941,1867.189941,1860.469971,1835.300049,1835.550049,1836.680054,1844.030029,1845.500000,1843.410034,1844.959961,1855.109985,1875.000000,1876.469971</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1.703247,0.941162,2.503540,1.111939,1.938843,0.292480,0.765625,0.260987,2.393555,2.567016,9.135864,4.089599,2.492675,3.738525,29.468872,28.242431,27.468628,19.856934,17.919312,21.236817,19.309326,9.112305,11.772827,12.781006</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.091185,0.050449,0.133959,0.059536,0.103815,0.015672,0.041040,0.013992,0.128188,0.137464,0.487660,0.218878,0.133499,0.200945,1.605671,1.538636,1.495559,1.076823,0.970973,1.152040,1.046599,0.491200,0.627884,0.681120</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5209493330757299</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>1863.502686,1865.693115,1866.137451,1865.952148,1866.265381,1866.085693,1866.596191,1864.134521,1864.290405,1865.989746,1863.583130,1863.214600,1863.882080,1864.758301,1864.936646,1860.813354,1862.210815,1863.516235,1863.041870,1861.056519,1863.137939,1860.505249,1861.529541,1863.203003</t>
@@ -1804,6 +1860,49 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>1861.335205,1859.399292,1857.505615,1856.454224,1854.189941,1852.550293,1853.209595,1851.779419,1851.716797,1849.622559,1847.684326,1848.387085,1848.348389,1844.934937,1846.779663,1844.785156,1843.149170,1841.239258,1839.181885,1839.997559,1839.236694,1838.462891,1837.510010,1837.296997</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:50</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1873.162476,1873.086182,1872.966553,1873.017944,1872.489258,1872.261841,1871.639404,1871.197876,1870.559082,1870.228882,1869.256104,1869.930176,1869.567627,1868.413086,1868.934326,1868.260010,1868.108276,1867.482422,1867.041138,1867.236572,1867.333008,1866.351929,1866.153564,1867.945435</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1871.081665,1871.627808,1872.729004,1870.390503,1872.076172,1872.125732,1870.260742,1869.245361,1868.017456,1869.378174,1866.966064,1867.962524,1867.042603,1868.632935,1867.783813,1865.971313,1862.731323,1866.087402,1864.238281,1863.732178,1863.439087,1862.614136,1863.198242,1864.332764</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1859.208008,1856.308350,1851.548950,1849.979248,1846.858887,1845.047363,1842.541382,1840.617432,1838.214600,1836.274658,1833.903687,1833.802856,1831.794678,1830.974976,1830.660034,1827.985840,1825.659546,1824.316040,1818.773315,1819.262695,1818.753906,1817.136353,1815.296753,1816.225708</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1865.815674,1863.175659,1859.809082,1859.075562,1856.155273,1854.453979,1853.561401,1852.430786,1851.998291,1849.535034,1846.232300,1847.367920,1847.032593,1844.581421,1845.440674,1844.772949,1841.870728,1840.272095,1838.149780,1838.583130,1838.331177,1835.590210,1835.373779,1836.457397</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,6 +987,44 @@
       </c>
       <c r="F15" t="n">
         <v>1867.945434570312</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1859.359985351562</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8.585449218749545</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.4617421739946841</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.4815432836503699</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:42:01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1860.959228515625</v>
       </c>
     </row>
   </sheetData>
@@ -1000,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,6 +1928,24 @@
           <t>1873.162476,1873.086182,1872.966553,1873.017944,1872.489258,1872.261841,1871.639404,1871.197876,1870.559082,1870.228882,1869.256104,1869.930176,1869.567627,1868.413086,1868.934326,1868.260010,1868.108276,1867.482422,1867.041138,1867.236572,1867.333008,1866.351929,1866.153564,1867.945435</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1879.209961,1874.589966,1875.640015,1874.050049,1866.209961,1869.119995,1866.849976,1850.800049,1855.359985,1853.000000,1853.020020,1857.119995,1861.310059,1866.800049,1873.839966,1880.060059,1881.680054,1888.380005,1879.930054,1883.349976,1871.619995,1864.920044,1862.000000,1859.359985</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6.047485,1.503784,2.673462,1.032105,6.279297,3.141846,4.789428,20.397827,15.199097,17.228882,16.236084,12.810181,8.257568,1.613037,4.905640,11.800049,13.571778,20.897583,12.888916,16.113404,4.286987,1.431885,4.153564,8.585450</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.321810,0.080219,0.142536,0.055073,0.336473,0.168092,0.256551,1.102109,0.819199,0.929783,0.876196,0.689787,0.443643,0.086407,0.261796,0.627642,0.721259,1.106641,0.685606,0.855571,0.229052,0.076780,0.223070,0.461742</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.4815432836503699</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>1871.081665,1871.627808,1872.729004,1870.390503,1872.076172,1872.125732,1870.260742,1869.245361,1868.017456,1869.378174,1866.966064,1867.962524,1867.042603,1868.632935,1867.783813,1865.971313,1862.731323,1866.087402,1864.238281,1863.732178,1863.439087,1862.614136,1863.198242,1864.332764</t>
@@ -1903,6 +1959,49 @@
       <c r="M15" t="inlineStr">
         <is>
           <t>1865.815674,1863.175659,1859.809082,1859.075562,1856.155273,1854.453979,1853.561401,1852.430786,1851.998291,1849.535034,1846.232300,1847.367920,1847.032593,1844.581421,1845.440674,1844.772949,1841.870728,1840.272095,1838.149780,1838.583130,1838.331177,1835.590210,1835.373779,1836.457397</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:42:01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1859.201172,1858.584717,1858.160889,1858.946899,1858.189331,1858.183228,1858.237671,1858.104248,1858.110352,1858.726807,1857.871460,1859.348022,1859.943115,1859.408813,1860.587402,1861.112549,1861.115234,1860.844238,1861.408081,1861.222656,1861.895752,1860.784668,1860.307129,1860.959229</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1858.092285,1857.982788,1858.752563,1858.343384,1860.507568,1859.100464,1859.654053,1857.853882,1855.730957,1858.119629,1857.336792,1858.796753,1859.674683,1859.649048,1860.896729,1859.235840,1858.699463,1861.097046,1858.606567,1858.389282,1859.398315,1858.528442,1858.083618,1858.824463</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1849.950439,1846.953247,1842.833252,1841.979248,1838.885010,1836.587402,1835.719238,1833.630859,1830.918335,1829.187622,1827.519409,1827.088379,1825.448120,1823.897705,1824.296143,1822.180176,1820.089233,1818.885620,1815.410400,1814.100342,1813.598145,1812.113525,1810.651978,1809.545044</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1854.362427,1851.586060,1848.640991,1848.391602,1846.236206,1844.678101,1844.250732,1843.395264,1843.050171,1840.967651,1838.392822,1839.658691,1839.732300,1837.427490,1839.109253,1838.452759,1836.038574,1835.000122,1834.534180,1833.002441,1833.486084,1831.047241,1830.577515,1830.209351</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,6 +1025,44 @@
       </c>
       <c r="F16" t="n">
         <v>1860.959228515625</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1858.0400390625</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.919189453125</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1571112242876057</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.4455497572022873</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:08</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1853.249145507812</v>
       </c>
     </row>
   </sheetData>
@@ -1038,7 +1076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1989,6 +2027,24 @@
           <t>1859.201172,1858.584717,1858.160889,1858.946899,1858.189331,1858.183228,1858.237671,1858.104248,1858.110352,1858.726807,1857.871460,1859.348022,1859.943115,1859.408813,1860.587402,1861.112549,1861.115234,1860.844238,1861.408081,1861.222656,1861.895752,1860.784668,1860.307129,1860.959229</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1852.569946,1857.530029,1846.729980,1841.430054,1837.849976,1850.109985,1843.680054,1837.400024,1841.229980,1856.900024,1871.699951,1861.099976,1864.319946,1867.130005,1867.000000,1868.569946,1867.520020,1862.089966,1858.630005,1858.890015,1849.300049,1865.829956,1864.339966,1858.040039</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6.631226,1.054688,11.430909,17.516845,20.339355,8.073243,14.557617,20.704224,16.880372,1.826783,13.828491,1.751954,4.376831,7.721192,6.412598,7.457397,6.404786,1.245728,2.778076,2.332641,12.595703,5.045288,4.032837,2.919190</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.357947,0.056779,0.618981,0.951263,1.106693,0.436366,0.789596,1.126822,0.916799,0.098378,0.738820,0.094135,0.234768,0.413533,0.343471,0.399097,0.342957,0.066899,0.149469,0.125486,0.681107,0.270404,0.216314,0.157111</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.4455497572022873</v>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>1858.092285,1857.982788,1858.752563,1858.343384,1860.507568,1859.100464,1859.654053,1857.853882,1855.730957,1858.119629,1857.336792,1858.796753,1859.674683,1859.649048,1860.896729,1859.235840,1858.699463,1861.097046,1858.606567,1858.389282,1859.398315,1858.528442,1858.083618,1858.824463</t>
@@ -2002,6 +2058,49 @@
       <c r="M16" t="inlineStr">
         <is>
           <t>1854.362427,1851.586060,1848.640991,1848.391602,1846.236206,1844.678101,1844.250732,1843.395264,1843.050171,1840.967651,1838.392822,1839.658691,1839.732300,1837.427490,1839.109253,1838.452759,1836.038574,1835.000122,1834.534180,1833.002441,1833.486084,1831.047241,1830.577515,1830.209351</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:08</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1857.212036,1856.537231,1855.703247,1856.786865,1855.797852,1855.546753,1855.525391,1854.904175,1854.996338,1854.781250,1854.370605,1855.126953,1855.540649,1854.794922,1855.730713,1855.449585,1855.593628,1855.188599,1854.702148,1854.327637,1854.587646,1854.143433,1852.946167,1853.249146</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1856.197021,1857.025879,1854.549316,1856.132446,1857.406616,1855.142212,1855.970825,1854.465454,1853.621338,1853.927368,1854.268921,1853.219849,1854.813232,1855.025879,1856.214600,1853.984131,1855.572998,1855.288574,1853.414795,1852.475952,1853.300171,1852.577393,1851.976929,1850.876831</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1845.884399,1842.322754,1837.784058,1837.647461,1833.710083,1832.317749,1831.354248,1829.489624,1826.825928,1825.468262,1824.323853,1823.982300,1821.543823,1820.636597,1820.994873,1817.931763,1816.743530,1815.704956,1811.842285,1810.813721,1810.117310,1809.075439,1806.838623,1806.451416</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1851.093506,1847.837524,1844.441040,1844.369141,1842.258301,1840.225952,1840.492798,1839.231201,1839.278687,1836.924683,1835.031494,1835.763428,1835.834229,1833.247803,1835.079712,1833.111572,1832.060547,1830.870972,1829.823120,1828.056641,1828.317627,1826.661011,1825.382446,1824.931763</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,6 +1063,44 @@
       </c>
       <c r="F17" t="n">
         <v>1853.249145507812</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1865.4599609375</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12.21081542968795</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.65457397560821</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6410640516644323</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:21:03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>24</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1867.350708007812</v>
       </c>
     </row>
   </sheetData>
@@ -1076,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2088,6 +2126,24 @@
           <t>1857.212036,1856.537231,1855.703247,1856.786865,1855.797852,1855.546753,1855.525391,1854.904175,1854.996338,1854.781250,1854.370605,1855.126953,1855.540649,1854.794922,1855.730713,1855.449585,1855.593628,1855.188599,1854.702148,1854.327637,1854.587646,1854.143433,1852.946167,1853.249146</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1866.280029,1862.660034,1855.229980,1862.079956,1855.760010,1856.680054,1864.910034,1870.829956,1873.510010,1859.229980,1871.119995,1871.410034,1868.219971,1868.060059,1873.900024,1873.680054,1875.319946,1870.880005,1875.199951,1862.469971,1862.469971,1871.949951,1872.979980,1865.459961</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>9.067993,6.122803,0.473267,5.293091,0.037842,1.133301,9.384643,15.925781,18.513672,4.448730,16.749390,16.283081,12.679322,13.265137,18.169311,18.230469,19.726318,15.691406,20.497803,8.142334,7.882325,17.806518,20.033813,12.210815</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.485886,0.328713,0.025510,0.284257,0.002039,0.061039,0.503222,0.851268,0.988181,0.239278,0.895153,0.870097,0.678685,0.710102,0.969599,0.972977,1.051891,0.838718,1.093100,0.437179,0.423219,0.951228,1.069622,0.654574</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6410640516644323</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>1856.197021,1857.025879,1854.549316,1856.132446,1857.406616,1855.142212,1855.970825,1854.465454,1853.621338,1853.927368,1854.268921,1853.219849,1854.813232,1855.025879,1856.214600,1853.984131,1855.572998,1855.288574,1853.414795,1852.475952,1853.300171,1852.577393,1851.976929,1850.876831</t>
@@ -2101,6 +2157,49 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>1851.093506,1847.837524,1844.441040,1844.369141,1842.258301,1840.225952,1840.492798,1839.231201,1839.278687,1836.924683,1835.031494,1835.763428,1835.834229,1833.247803,1835.079712,1833.111572,1832.060547,1830.870972,1829.823120,1828.056641,1828.317627,1826.661011,1825.382446,1824.931763</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:21:03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>24</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1866.451904,1865.774780,1864.982666,1865.986816,1865.452393,1865.608765,1865.392700,1865.338623,1865.808350,1865.850098,1866.106934,1867.214233,1867.587036,1867.167969,1868.006836,1868.130249,1868.662231,1868.559204,1868.088379,1867.052856,1867.713379,1867.141113,1867.210449,1867.350708</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1865.216187,1866.255127,1865.584106,1865.713257,1867.851440,1864.812134,1865.555664,1865.504883,1864.013062,1865.648071,1865.634521,1864.901367,1865.439087,1866.299316,1868.028809,1867.644531,1867.567993,1867.280762,1865.993408,1866.355347,1865.583862,1867.358765,1866.270630,1864.780762</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1857.408691,1854.563965,1851.272705,1851.407471,1848.437500,1847.187256,1846.091919,1844.798950,1842.590576,1841.381104,1840.327148,1840.421143,1838.040039,1836.986450,1837.373779,1835.558716,1834.651001,1834.319092,1830.457764,1828.424927,1828.456665,1827.525146,1826.909668,1826.548706</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1861.376587,1859.192139,1856.173340,1856.200684,1854.274658,1853.155640,1853.567139,1852.947144,1852.528442,1850.788818,1849.457642,1850.162598,1850.453613,1848.021851,1849.395874,1849.155029,1848.156006,1847.777466,1846.291504,1844.018188,1844.601440,1842.820679,1842.738403,1842.304321</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1101,44 @@
       </c>
       <c r="F18" t="n">
         <v>1867.350708007812</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1895.400024414062</v>
+      </c>
+      <c r="H18" t="n">
+        <v>28.04931640625045</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.479862617123344</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.157779439941174</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:49</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1893.091674804688</v>
       </c>
     </row>
   </sheetData>
@@ -1114,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2187,6 +2225,24 @@
           <t>1866.451904,1865.774780,1864.982666,1865.986816,1865.452393,1865.608765,1865.392700,1865.338623,1865.808350,1865.850098,1866.106934,1867.214233,1867.587036,1867.167969,1868.006836,1868.130249,1868.662231,1868.559204,1868.088379,1867.052856,1867.713379,1867.141113,1867.210449,1867.350708</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1865.819946,1871.880005,1868.250000,1870.609985,1868.089966,1870.329956,1866.719971,1867.109985,1874.569946,1878.030029,1874.510010,1872.410034,1893.949951,1914.500000,1916.760010,1915.619995,1915.560059,1906.920044,1905.270020,1907.290039,1908.550049,1904.939941,1897.410034,1895.400024</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.631958,6.105225,3.267334,4.623169,2.637573,4.721191,1.327271,1.771362,8.761596,12.179931,8.403076,5.195801,26.362915,47.332031,48.753174,47.489746,46.897828,38.360840,37.181641,40.237183,40.836670,37.798828,30.199585,28.049316</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.033870,0.326155,0.174887,0.247148,0.141191,0.252426,0.071102,0.094872,0.467392,0.648548,0.448281,0.277493,1.391954,2.472292,2.543520,2.479080,2.448257,2.011665,1.951516,2.109652,2.139670,1.984253,1.591621,1.479863</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1.157779439941174</v>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>1865.216187,1866.255127,1865.584106,1865.713257,1867.851440,1864.812134,1865.555664,1865.504883,1864.013062,1865.648071,1865.634521,1864.901367,1865.439087,1866.299316,1868.028809,1867.644531,1867.567993,1867.280762,1865.993408,1866.355347,1865.583862,1867.358765,1866.270630,1864.780762</t>
@@ -2200,6 +2256,49 @@
       <c r="M18" t="inlineStr">
         <is>
           <t>1861.376587,1859.192139,1856.173340,1856.200684,1854.274658,1853.155640,1853.567139,1852.947144,1852.528442,1850.788818,1849.457642,1850.162598,1850.453613,1848.021851,1849.395874,1849.155029,1848.156006,1847.777466,1846.291504,1844.018188,1844.601440,1842.820679,1842.738403,1842.304321</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:49</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1896.759033,1895.761963,1894.939209,1895.619019,1894.588867,1894.491699,1894.397827,1893.209229,1893.576904,1893.499512,1893.311279,1893.730957,1894.457397,1894.108765,1894.624390,1894.576050,1895.508789,1895.243286,1895.082886,1894.646362,1893.675049,1892.550293,1892.728149,1893.091675</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1895.003662,1894.549316,1895.443481,1894.737915,1895.588135,1895.054565,1893.030151,1893.798828,1891.733887,1893.242798,1892.943481,1891.113281,1891.064941,1891.320557,1892.923706,1893.579224,1891.027832,1892.060547,1891.521729,1890.861816,1890.591675,1890.420410,1892.198242,1888.184692</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1886.681030,1882.809082,1878.790894,1877.893188,1873.480469,1872.207764,1870.105713,1865.901855,1865.933228,1863.968506,1862.658569,1861.611328,1861.167969,1860.371948,1858.807861,1857.401611,1858.022095,1857.878906,1853.152710,1851.422607,1851.165894,1848.887573,1848.669067,1848.673950</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1891.690796,1888.502319,1885.052856,1884.883057,1881.703125,1879.395264,1879.337524,1876.753906,1877.578979,1874.977905,1873.246338,1872.969604,1874.501587,1872.015015,1871.732544,1872.137451,1873.191040,1871.699951,1870.390137,1868.894897,1867.187744,1865.447021,1865.062500,1864.661377</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,6 +1139,44 @@
       </c>
       <c r="F19" t="n">
         <v>1893.091674804688</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1901.510009765625</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8.418334960937045</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4427184141920277</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6263971644435736</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:11:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1904.052368164062</v>
       </c>
     </row>
   </sheetData>
@@ -1152,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2286,6 +2324,24 @@
           <t>1896.759033,1895.761963,1894.939209,1895.619019,1894.588867,1894.491699,1894.397827,1893.209229,1893.576904,1893.499512,1893.311279,1893.730957,1894.457397,1894.108765,1894.624390,1894.576050,1895.508789,1895.243286,1895.082886,1894.646362,1893.675049,1892.550293,1892.728149,1893.091675</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1906.089966,1912.469971,1911.670044,1907.119995,1914.199951,1905.660034,1900.739990,1905.839966,1896.750000,1905.839966,1913.239990,1909.109985,1914.010010,1912.439941,1904.430054,1908.569946,1905.660034,1904.579956,1903.719971,1902.420044,1902.189941,1901.780029,1900.979980,1901.510010</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>9.330933,16.708008,16.730835,11.500976,19.611084,11.168335,6.342163,12.630737,3.173096,12.340454,19.928711,15.379028,19.552613,18.331176,9.805664,13.993896,10.151245,9.336670,8.637085,7.773682,8.514892,9.229736,8.251831,8.418335</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.489533,0.873635,0.875195,0.603055,1.024506,0.586061,0.333668,0.662739,0.167291,0.647507,1.041621,0.805560,1.021552,0.958523,0.514887,0.733214,0.532689,0.490222,0.453695,0.408621,0.447636,0.485321,0.434083,0.442718</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6263971644435736</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>1895.003662,1894.549316,1895.443481,1894.737915,1895.588135,1895.054565,1893.030151,1893.798828,1891.733887,1893.242798,1892.943481,1891.113281,1891.064941,1891.320557,1892.923706,1893.579224,1891.027832,1892.060547,1891.521729,1890.861816,1890.591675,1890.420410,1892.198242,1888.184692</t>
@@ -2299,6 +2355,49 @@
       <c r="M19" t="inlineStr">
         <is>
           <t>1891.690796,1888.502319,1885.052856,1884.883057,1881.703125,1879.395264,1879.337524,1876.753906,1877.578979,1874.977905,1873.246338,1872.969604,1874.501587,1872.015015,1871.732544,1872.137451,1873.191040,1871.699951,1870.390137,1868.894897,1867.187744,1865.447021,1865.062500,1864.661377</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:11:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1901.776367,1901.180054,1901.183960,1901.181152,1900.991821,1901.056519,1901.856323,1900.944458,1901.493042,1901.566895,1901.595825,1902.386841,1903.172852,1903.292725,1904.192139,1904.688843,1905.648926,1904.960449,1904.865479,1905.262329,1904.099731,1903.565063,1904.292847,1904.052368</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1900.960449,1901.552368,1900.693237,1899.974243,1903.502563,1901.021851,1902.293213,1900.557129,1902.032471,1901.703003,1901.307617,1902.708984,1903.616943,1903.064697,1904.389771,1904.228149,1904.816040,1903.354370,1904.318359,1903.572021,1901.543823,1901.270630,1904.464600,1902.477783</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1894.838257,1891.893188,1889.112427,1886.916016,1884.310547,1882.323730,1881.850098,1878.818237,1878.864136,1877.100708,1876.029419,1875.129395,1873.930176,1873.599731,1873.397461,1872.255859,1872.536499,1872.317505,1867.559937,1866.562134,1865.978638,1864.542114,1864.501343,1863.176514</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1898.328247,1895.421875,1894.085815,1892.256226,1891.037842,1888.390625,1889.444458,1887.971924,1888.456299,1886.365601,1885.667725,1885.522339,1886.779907,1884.288696,1885.292236,1885.608643,1885.546143,1884.539917,1883.211670,1882.496460,1881.016357,1879.918457,1879.838867,1878.939575</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1177,6 +1177,44 @@
       </c>
       <c r="F20" t="n">
         <v>1904.052368164062</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1913.449951171875</v>
+      </c>
+      <c r="H20" t="n">
+        <v>9.397583007812955</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.4911329403759681</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.5114907609056839</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:08:01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1915.931762695312</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2385,6 +2423,24 @@
           <t>1901.776367,1901.180054,1901.183960,1901.181152,1900.991821,1901.056519,1901.856323,1900.944458,1901.493042,1901.566895,1901.595825,1902.386841,1903.172852,1903.292725,1904.192139,1904.688843,1905.648926,1904.960449,1904.865479,1905.262329,1904.099731,1903.565063,1904.292847,1904.052368</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1895.650024,1899.810059,1903.040039,1900.930054,1909.359985,1911.800049,1911.430054,1914.890015,1930.989990,1921.380005,1912.109985,1916.589966,1908.010010,1911.010010,1908.229980,1918.099976,1913.859985,1917.030029,1917.030029,1913.569946,1913.569946,1913.719971,1913.449951,1913.449951</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6.126343,1.369995,1.856079,0.251098,8.368164,10.743530,9.573731,13.945557,29.496948,19.813110,10.514160,14.203125,4.837158,7.717285,4.037841,13.411133,8.211059,12.069580,12.164550,8.307617,9.470215,10.154908,9.157104,9.397583</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.323179,0.072112,0.097532,0.013209,0.438271,0.561959,0.500867,0.728269,1.527556,1.031192,0.549872,0.741062,0.253518,0.403833,0.211601,0.699188,0.429031,0.629598,0.634552,0.434142,0.494898,0.530637,0.478565,0.491133</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.5114907609056839</v>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>1900.960449,1901.552368,1900.693237,1899.974243,1903.502563,1901.021851,1902.293213,1900.557129,1902.032471,1901.703003,1901.307617,1902.708984,1903.616943,1903.064697,1904.389771,1904.228149,1904.816040,1903.354370,1904.318359,1903.572021,1901.543823,1901.270630,1904.464600,1902.477783</t>
@@ -2398,6 +2454,49 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>1898.328247,1895.421875,1894.085815,1892.256226,1891.037842,1888.390625,1889.444458,1887.971924,1888.456299,1886.365601,1885.667725,1885.522339,1886.779907,1884.288696,1885.292236,1885.608643,1885.546143,1884.539917,1883.211670,1882.496460,1881.016357,1879.918457,1879.838867,1878.939575</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:08:01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1913.410889,1912.959351,1913.085693,1913.263062,1913.797241,1914.130737,1915.229858,1914.622559,1914.995850,1915.324463,1915.784180,1915.561401,1915.307861,1915.244629,1915.910156,1916.086304,1917.685059,1916.908325,1916.796387,1917.497925,1916.590088,1916.093506,1916.486572,1915.931763</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1911.690796,1912.513306,1913.382568,1911.426392,1913.788574,1914.034668,1914.791138,1913.982422,1914.265625,1916.066650,1915.017334,1914.708984,1914.914795,1915.726074,1915.648438,1916.663452,1916.213135,1914.646484,1916.401001,1916.601807,1914.641235,1915.274048,1915.493652,1915.261719</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1906.576050,1903.366943,1900.797974,1899.332764,1898.047852,1896.608643,1896.437500,1893.807129,1893.269287,1891.908569,1891.781738,1890.936401,1890.127197,1888.423096,1888.175903,1886.975098,1888.001343,1888.368408,1883.245728,1882.708618,1882.480957,1881.770508,1881.336792,1878.702148</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>1910.330078,1907.393921,1906.032593,1904.897095,1905.111084,1902.441406,1903.701904,1902.494629,1902.450928,1900.464844,1901.113159,1900.401733,1901.398315,1897.999878,1898.878662,1899.331299,1899.942139,1898.992432,1897.429932,1897.508301,1896.176270,1894.752808,1895.259644,1893.295898</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1215,6 +1215,44 @@
       </c>
       <c r="F21" t="n">
         <v>1915.931762695312</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1914.550048828125</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.381713867187045</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.07216911712664692</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.1626448236950036</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:19:04</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1916.78076171875</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,6 +2522,24 @@
           <t>1913.410889,1912.959351,1913.085693,1913.263062,1913.797241,1914.130737,1915.229858,1914.622559,1914.995850,1915.324463,1915.784180,1915.561401,1915.307861,1915.244629,1915.910156,1916.086304,1917.685059,1916.908325,1916.796387,1917.497925,1916.590088,1916.093506,1916.486572,1915.931763</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1917.109985,1916.209961,1916.569946,1915.550049,1914.270020,1915.880005,1917.719971,1919.989990,1919.609985,1918.099976,1918.949951,1922.599976,1921.239990,1921.420044,1922.479980,1920.109985,1919.160034,1918.839966,1919.239990,1915.439941,1916.959961,1916.510010,1914.739990,1914.550049</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3.699096,3.250610,3.484253,2.286987,0.472779,1.749268,2.490113,5.367431,4.614135,2.775513,3.165771,7.038575,5.932129,6.175415,6.569824,4.023681,1.474975,1.931641,2.443603,2.057984,0.369873,0.416504,1.746582,1.381714</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.192952,0.169637,0.181796,0.119391,0.024698,0.091304,0.129848,0.279555,0.240368,0.144701,0.164974,0.366097,0.308766,0.321398,0.341737,0.209555,0.076855,0.100667,0.127321,0.107442,0.019295,0.021732,0.091218,0.072169</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.1626448236950036</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>1911.690796,1912.513306,1913.382568,1911.426392,1913.788574,1914.034668,1914.791138,1913.982422,1914.265625,1916.066650,1915.017334,1914.708984,1914.914795,1915.726074,1915.648438,1916.663452,1916.213135,1914.646484,1916.401001,1916.601807,1914.641235,1915.274048,1915.493652,1915.261719</t>
@@ -2497,6 +2553,49 @@
       <c r="M21" t="inlineStr">
         <is>
           <t>1910.330078,1907.393921,1906.032593,1904.897095,1905.111084,1902.441406,1903.701904,1902.494629,1902.450928,1900.464844,1901.113159,1900.401733,1901.398315,1897.999878,1898.878662,1899.331299,1899.942139,1898.992432,1897.429932,1897.508301,1896.176270,1894.752808,1895.259644,1893.295898</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:19:04</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1913.300049,1913.056152,1914.808228,1914.132568,1914.402832,1914.822021,1915.449219,1914.661865,1915.195435,1915.209106,1916.251343,1917.017212,1917.659302,1917.278564,1917.471436,1917.637085,1918.849731,1917.373657,1916.825928,1917.417480,1916.324707,1916.158203,1916.994019,1916.780762</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1912.624268,1912.258789,1915.410034,1913.420410,1914.363770,1914.770142,1913.459717,1912.819702,1915.600220,1917.276855,1917.335449,1915.195679,1916.668091,1917.655396,1915.986328,1917.621704,1916.972656,1914.526855,1915.683594,1917.242798,1914.953613,1915.063965,1916.369507,1916.772461</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1909.101562,1908.104858,1908.151978,1905.869019,1904.346924,1902.896118,1903.144653,1900.741577,1900.557495,1899.112305,1899.092163,1899.726318,1899.992676,1900.321777,1899.388916,1898.541992,1898.897461,1897.553223,1892.460327,1891.538940,1891.744263,1891.206055,1890.967773,1889.977539</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1911.905518,1910.339966,1911.080322,1909.490356,1908.570312,1907.124146,1907.440308,1907.005737,1907.709717,1905.189087,1905.839355,1906.425049,1908.120361,1906.786865,1906.894165,1906.547241,1908.048828,1905.649170,1904.139893,1903.694824,1902.954956,1901.286377,1901.912964,1900.378418</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,6 +1253,44 @@
       </c>
       <c r="F22" t="n">
         <v>1916.78076171875</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1914.109985351562</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.6707763671875</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1395309771970581</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.1895993523092851</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>24</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1912.960205078125</v>
       </c>
     </row>
   </sheetData>
@@ -1266,7 +1304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2621,24 @@
           <t>1913.300049,1913.056152,1914.808228,1914.132568,1914.402832,1914.822021,1915.449219,1914.661865,1915.195435,1915.209106,1916.251343,1917.017212,1917.659302,1917.278564,1917.471436,1917.637085,1918.849731,1917.373657,1916.825928,1917.417480,1916.324707,1916.158203,1916.994019,1916.780762</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1912.699951,1911.839966,1913.150024,1917.709961,1917.500000,1914.479980,1919.829956,1918.719971,1917.930054,1916.270020,1921.989990,1923.489990,1924.640015,1922.719971,1921.670044,1920.099976,1920.579956,1919.780029,1923.219971,1918.280029,1909.089966,1911.069946,1923.920044,1914.109985</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.600098,1.216186,1.658204,3.577393,3.097168,0.342041,4.380737,4.058106,2.734619,1.060914,5.738647,6.472778,6.980713,5.441407,4.198608,2.462891,1.730225,2.406372,6.394043,0.862549,7.234741,5.088257,6.926025,2.670777</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.031374,0.063613,0.086674,0.186545,0.161521,0.017866,0.228184,0.211501,0.142582,0.055363,0.298578,0.336512,0.362702,0.283006,0.218487,0.128269,0.090089,0.125346,0.332465,0.044965,0.378963,0.266252,0.359995,0.139531</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.1895993523092851</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>1912.624268,1912.258789,1915.410034,1913.420410,1914.363770,1914.770142,1913.459717,1912.819702,1915.600220,1917.276855,1917.335449,1915.195679,1916.668091,1917.655396,1915.986328,1917.621704,1916.972656,1914.526855,1915.683594,1917.242798,1914.953613,1915.063965,1916.369507,1916.772461</t>
@@ -2596,6 +2652,49 @@
       <c r="M22" t="inlineStr">
         <is>
           <t>1911.905518,1910.339966,1911.080322,1909.490356,1908.570312,1907.124146,1907.440308,1907.005737,1907.709717,1905.189087,1905.839355,1906.425049,1908.120361,1906.786865,1906.894165,1906.547241,1908.048828,1905.649170,1904.139893,1903.694824,1902.954956,1901.286377,1901.912964,1900.378418</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>24</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1913.600098,1912.487183,1913.238281,1913.093994,1912.284180,1912.706665,1913.357300,1913.031128,1914.248535,1914.162720,1913.614990,1914.733521,1915.269653,1914.239014,1914.647949,1914.368774,1915.374146,1914.040527,1912.989258,1913.516846,1913.728027,1912.671997,1913.157593,1912.960205</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1913.183105,1913.566528,1913.000610,1912.182617,1913.420410,1913.666626,1912.700439,1912.521729,1912.410767,1913.906128,1914.955200,1911.906860,1913.972656,1914.208984,1913.325928,1913.090942,1912.549194,1911.091309,1910.552612,1910.641113,1910.257935,1909.604004,1911.295532,1910.670776</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1906.442993,1903.747681,1902.810791,1901.255737,1898.886719,1898.128418,1899.069458,1897.348389,1898.361450,1896.987305,1897.227905,1896.770874,1896.655762,1895.966064,1895.573242,1893.970215,1893.770020,1892.670654,1886.729736,1885.646240,1886.699097,1884.816406,1884.477783,1884.036865</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1909.985229,1907.597412,1906.147217,1906.254883,1904.115112,1903.360596,1904.510986,1904.841675,1905.441895,1903.823730,1902.811768,1904.032837,1904.790405,1902.616943,1903.504517,1902.718384,1903.046143,1901.790039,1898.726685,1898.024902,1898.162109,1895.926758,1896.076660,1895.046387</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,6 +1291,44 @@
       </c>
       <c r="F23" t="n">
         <v>1912.960205078125</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1876.349975585938</v>
+      </c>
+      <c r="H23" t="n">
+        <v>36.6102294921875</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.951140776962732</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.304322790275956</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:14:58</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1874.747192382812</v>
       </c>
     </row>
   </sheetData>
@@ -1304,7 +1342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2682,6 +2720,24 @@
           <t>1913.600098,1912.487183,1913.238281,1913.093994,1912.284180,1912.706665,1913.357300,1913.031128,1914.248535,1914.162720,1913.614990,1914.733521,1915.269653,1914.239014,1914.647949,1914.368774,1915.374146,1914.040527,1912.989258,1913.516846,1913.728027,1912.671997,1913.157593,1912.960205</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1915.839966,1914.119995,1921.630005,1926.489990,1923.979980,1925.199951,1914.900024,1915.989990,1918.500000,1904.640015,1895.699951,1891.619995,1875.020020,1870.339966,1871.869995,1870.709961,1876.640015,1877.810059,1872.780029,1872.780029,1873.510010,1873.510010,1876.150024,1876.349976</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2.239868,1.632812,8.391724,13.395996,11.695800,12.493286,1.542724,2.958862,4.251465,9.522705,17.915039,23.113526,40.249633,43.899048,42.777954,43.658813,38.734131,36.230468,40.209229,40.736817,40.218017,39.161987,37.007569,36.610229</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.116913,0.085304,0.436698,0.695358,0.607896,0.648934,0.080564,0.154430,0.221604,0.499974,0.945036,1.221891,2.146624,2.347116,2.285306,2.333810,2.064015,1.929400,2.147034,2.175206,2.146667,2.090300,1.972527,1.951141</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1.304322790275956</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>1913.183105,1913.566528,1913.000610,1912.182617,1913.420410,1913.666626,1912.700439,1912.521729,1912.410767,1913.906128,1914.955200,1911.906860,1913.972656,1914.208984,1913.325928,1913.090942,1912.549194,1911.091309,1910.552612,1910.641113,1910.257935,1909.604004,1911.295532,1910.670776</t>
@@ -2695,6 +2751,49 @@
       <c r="M23" t="inlineStr">
         <is>
           <t>1909.985229,1907.597412,1906.147217,1906.254883,1904.115112,1903.360596,1904.510986,1904.841675,1905.441895,1903.823730,1902.811768,1904.032837,1904.790405,1902.616943,1903.504517,1902.718384,1903.046143,1901.790039,1898.726685,1898.024902,1898.162109,1895.926758,1896.076660,1895.046387</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:14:58</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1875.328735,1875.508301,1875.723999,1874.939697,1875.886230,1875.862671,1875.774780,1874.533936,1875.017334,1875.067627,1874.229370,1874.401855,1874.817749,1874.436035,1874.867554,1874.350464,1875.236694,1874.205444,1873.900879,1874.221436,1875.131592,1873.955322,1874.253296,1874.747192</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1876.377563,1878.954102,1874.948853,1875.762451,1877.789185,1877.821533,1875.445923,1875.076904,1876.369263,1877.448120,1874.947021,1874.568970,1874.802246,1877.052002,1875.697388,1873.180908,1875.210205,1873.886230,1874.308350,1874.373779,1873.299805,1870.614014,1875.881226,1874.364624</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1865.677368,1863.702271,1861.665161,1859.224487,1858.557983,1857.276489,1856.764038,1854.138062,1854.127075,1852.130737,1852.234619,1851.358276,1851.698608,1849.482300,1848.771973,1846.276245,1845.477173,1844.003174,1838.730591,1837.347534,1838.592529,1836.013184,1834.966675,1834.670654</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1869.733032,1868.373291,1866.248779,1864.801392,1864.609253,1863.620117,1863.397705,1861.332764,1862.199829,1861.236450,1859.858521,1860.895752,1860.641113,1858.614624,1859.163818,1857.442383,1856.830933,1855.068115,1852.923096,1852.889771,1853.283081,1851.079712,1850.892456,1851.341553</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,6 +1329,44 @@
       </c>
       <c r="F24" t="n">
         <v>1874.747192382812</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1883.7099609375</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8.962768554687955</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.4758040643490196</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.3879290882176517</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:43</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1883.139526367188</v>
       </c>
     </row>
   </sheetData>
@@ -1342,7 +1380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2781,6 +2819,24 @@
           <t>1875.328735,1875.508301,1875.723999,1874.939697,1875.886230,1875.862671,1875.774780,1874.533936,1875.017334,1875.067627,1874.229370,1874.401855,1874.817749,1874.436035,1874.867554,1874.350464,1875.236694,1874.205444,1873.900879,1874.221436,1875.131592,1873.955322,1874.253296,1874.747192</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1879.079956,1874.430054,1872.140015,1872.500000,1876.010010,1877.579956,1883.790039,1884.609985,1891.420044,1886.319946,1888.310059,1871.859985,1861.199951,1863.189941,1862.739990,1864.390015,1879.689941,1880.479980,1883.000000,1880.630005,1877.290039,1880.760010,1882.920044,1883.709961</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>3.751221,1.078247,3.583984,2.439697,0.123780,1.717285,8.015259,10.076049,16.402710,11.252319,14.080689,2.541870,13.617798,11.246094,12.127564,9.960449,4.453247,6.274536,9.099121,6.408569,2.158447,6.804688,8.666748,8.962769</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.199631,0.057524,0.191438,0.130291,0.006598,0.091463,0.425486,0.534649,0.867217,0.596522,0.745677,0.135794,0.731668,0.603594,0.651060,0.534247,0.236914,0.333667,0.483225,0.340767,0.114977,0.361805,0.460282,0.475804</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.3879290882176517</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>1876.377563,1878.954102,1874.948853,1875.762451,1877.789185,1877.821533,1875.445923,1875.076904,1876.369263,1877.448120,1874.947021,1874.568970,1874.802246,1877.052002,1875.697388,1873.180908,1875.210205,1873.886230,1874.308350,1874.373779,1873.299805,1870.614014,1875.881226,1874.364624</t>
@@ -2794,6 +2850,49 @@
       <c r="M24" t="inlineStr">
         <is>
           <t>1869.733032,1868.373291,1866.248779,1864.801392,1864.609253,1863.620117,1863.397705,1861.332764,1862.199829,1861.236450,1859.858521,1860.895752,1860.641113,1858.614624,1859.163818,1857.442383,1856.830933,1855.068115,1852.923096,1852.889771,1853.283081,1851.079712,1850.892456,1851.341553</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:43</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1883.082764,1883.710327,1883.503662,1884.137817,1884.218018,1884.259399,1884.362305,1883.812378,1883.708130,1883.509033,1882.494263,1882.463745,1882.737183,1882.263428,1882.516113,1882.234863,1882.338989,1882.447510,1882.304932,1882.201904,1883.374634,1882.188354,1882.853638,1883.139526</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1882.812866,1885.059692,1882.358276,1883.539795,1884.460571,1883.577271,1883.565186,1883.831665,1884.061401,1884.272949,1882.647827,1880.124390,1881.931519,1882.735229,1881.740479,1881.808716,1878.977173,1881.388428,1881.076904,1879.640991,1881.382324,1881.287354,1883.192627,1879.844604</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1874.807007,1872.903076,1870.428955,1869.368652,1866.823486,1865.697266,1865.601440,1863.746094,1862.956421,1860.856689,1860.338745,1858.518677,1857.369507,1856.814941,1856.233521,1854.727051,1853.362427,1853.122803,1848.967529,1847.175415,1849.174438,1846.711060,1846.617432,1846.071533</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>1878.937256,1877.412720,1875.355591,1875.153442,1874.054077,1872.964111,1872.572388,1871.962158,1871.621948,1869.801025,1867.818115,1867.830200,1868.114014,1866.151123,1866.458130,1865.916260,1864.693970,1864.017822,1863.174927,1862.098022,1862.957642,1860.341431,1861.384399,1860.874146</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,6 +1367,44 @@
       </c>
       <c r="F25" t="n">
         <v>1883.139526367188</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1872.599975585938</v>
+      </c>
+      <c r="H25" t="n">
+        <v>10.53955078125045</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.5628298044782696</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.461293981034958</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:11</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1873.251708984375</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2880,6 +2918,24 @@
           <t>1883.082764,1883.710327,1883.503662,1884.137817,1884.218018,1884.259399,1884.362305,1883.812378,1883.708130,1883.509033,1882.494263,1882.463745,1882.737183,1882.263428,1882.516113,1882.234863,1882.338989,1882.447510,1882.304932,1882.201904,1883.374634,1882.188354,1882.853638,1883.139526</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1884.959961,1887.800049,1890.199951,1885.900024,1890.010010,1889.119995,1904.150024,1907.500000,1913.910034,1909.829956,1899.540039,1884.969971,1890.699951,1888.810059,1886.020020,1883.449951,1877.170044,1884.599976,1876.040039,1876.550049,1877.680054,1878.260010,1876.140015,1872.599976</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1.877197,4.089722,6.696289,1.762207,5.791992,4.860596,19.787719,23.687622,30.201904,26.320923,17.045776,2.506226,7.962768,6.546631,3.503907,1.215088,5.168945,2.152466,6.264893,5.651855,5.694580,3.928344,6.713623,10.539550</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.099588,0.216640,0.354264,0.093441,0.306453,0.257294,1.039189,1.241815,1.578021,1.378181,0.897363,0.132958,0.421155,0.346601,0.185783,0.064514,0.275358,0.114213,0.333942,0.301183,0.303277,0.209148,0.357842,0.562830</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.461293981034958</v>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>1882.812866,1885.059692,1882.358276,1883.539795,1884.460571,1883.577271,1883.565186,1883.831665,1884.061401,1884.272949,1882.647827,1880.124390,1881.931519,1882.735229,1881.740479,1881.808716,1878.977173,1881.388428,1881.076904,1879.640991,1881.382324,1881.287354,1883.192627,1879.844604</t>
@@ -2893,6 +2949,49 @@
       <c r="M25" t="inlineStr">
         <is>
           <t>1878.937256,1877.412720,1875.355591,1875.153442,1874.054077,1872.964111,1872.572388,1871.962158,1871.621948,1869.801025,1867.818115,1867.830200,1868.114014,1866.151123,1866.458130,1865.916260,1864.693970,1864.017822,1863.174927,1862.098022,1862.957642,1860.341431,1861.384399,1860.874146</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:11</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1873.561646,1873.295776,1873.077026,1873.207275,1873.327637,1873.562500,1874.482544,1874.426758,1874.621704,1875.215210,1874.189209,1873.918091,1873.971924,1873.332764,1873.415771,1872.996704,1873.106934,1873.008301,1872.529541,1872.070068,1872.723877,1872.741455,1872.902710,1873.251709</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1873.204956,1874.866089,1873.247559,1874.015503,1874.185303,1873.903687,1874.644043,1873.951782,1874.703491,1876.306885,1875.173584,1873.249512,1873.603760,1873.785767,1873.286743,1873.417603,1870.320679,1871.978516,1872.341797,1870.701294,1871.361328,1872.001465,1873.842773,1871.660522</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1864.819824,1862.329468,1860.080322,1858.811523,1856.914429,1856.586914,1856.469482,1854.624878,1854.393188,1853.198853,1852.308350,1850.087402,1849.293945,1848.049438,1846.796997,1844.770020,1843.928589,1843.215088,1839.559326,1838.096436,1838.895630,1838.100952,1836.962402,1837.061646</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1869.019409,1866.861450,1865.093018,1864.648193,1863.460693,1862.670410,1862.871094,1862.616211,1862.649292,1861.326416,1859.530640,1859.306519,1859.211060,1857.456787,1857.177002,1856.316040,1855.838623,1854.523560,1853.738647,1852.302124,1852.756836,1851.864746,1851.564331,1851.419312</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1405,6 +1405,44 @@
       </c>
       <c r="F26" t="n">
         <v>1873.251708984375</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1887.089965820312</v>
+      </c>
+      <c r="H26" t="n">
+        <v>13.8382568359375</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.7333119822891989</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.6667240396454083</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:32:59</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1887.682250976562</v>
       </c>
     </row>
   </sheetData>
@@ -1418,7 +1456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2979,6 +3017,24 @@
           <t>1873.561646,1873.295776,1873.077026,1873.207275,1873.327637,1873.562500,1874.482544,1874.426758,1874.621704,1875.215210,1874.189209,1873.918091,1873.971924,1873.332764,1873.415771,1872.996704,1873.106934,1873.008301,1872.529541,1872.070068,1872.723877,1872.741455,1872.902710,1873.251709</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1885.569946,1890.329956,1893.910034,1896.819946,1893.869995,1888.290039,1887.770020,1881.069946,1878.349976,1887.040039,1888.390015,1891.209961,1878.390015,1872.660034,1874.930054,1883.569946,1885.310059,1884.420044,1886.979980,1887.729980,1884.609985,1887.660034,1887.810059,1887.089966</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>12.008300,17.034180,20.833008,23.612671,20.542358,14.727539,13.287476,6.643188,3.728272,11.824829,14.200806,17.291870,4.418091,0.672730,1.514283,10.573242,12.203125,11.411743,14.450439,15.659912,11.886108,14.918579,14.907349,13.838257</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.636853,0.901122,1.100000,1.244856,1.084676,0.779941,0.703872,0.353160,0.198487,0.626634,0.752006,0.914328,0.235206,0.035924,0.080765,0.561341,0.647274,0.605584,0.765797,0.829563,0.630693,0.790321,0.789664,0.733312</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.6667240396454083</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>1873.204956,1874.866089,1873.247559,1874.015503,1874.185303,1873.903687,1874.644043,1873.951782,1874.703491,1876.306885,1875.173584,1873.249512,1873.603760,1873.785767,1873.286743,1873.417603,1870.320679,1871.978516,1872.341797,1870.701294,1871.361328,1872.001465,1873.842773,1871.660522</t>
@@ -2992,6 +3048,49 @@
       <c r="M26" t="inlineStr">
         <is>
           <t>1869.019409,1866.861450,1865.093018,1864.648193,1863.460693,1862.670410,1862.871094,1862.616211,1862.649292,1861.326416,1859.530640,1859.306519,1859.211060,1857.456787,1857.177002,1856.316040,1855.838623,1854.523560,1853.738647,1852.302124,1852.756836,1851.864746,1851.564331,1851.419312</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:32:59</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1886.685669,1886.663452,1886.647583,1886.848755,1886.331665,1886.294800,1887.086060,1886.518921,1887.210205,1887.044189,1886.449341,1886.048706,1886.534058,1886.311768,1886.377808,1886.513550,1887.076172,1886.892822,1886.903198,1886.703125,1886.936890,1887.178955,1887.504761,1887.682251</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1886.418213,1887.684448,1886.777466,1886.728394,1888.127197,1886.241211,1887.664795,1887.127686,1887.206909,1887.846680,1887.168091,1884.897217,1886.739746,1885.875977,1886.404297,1887.214600,1885.291748,1886.926880,1886.738892,1885.881958,1885.937134,1886.225952,1887.734741,1886.360840</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1878.954834,1876.746094,1874.607788,1874.081543,1871.676392,1871.516846,1871.375488,1869.539429,1869.184937,1867.881714,1867.198486,1865.733643,1864.922119,1864.030640,1863.297974,1862.466187,1861.918457,1861.727539,1859.140625,1858.738403,1858.915649,1858.816650,1858.370850,1858.102783</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1882.488647,1880.433716,1879.007080,1878.823608,1877.438843,1876.571167,1876.710938,1876.201294,1876.417358,1875.348389,1873.946655,1873.714844,1873.514404,1871.923218,1872.189453,1871.677612,1871.363403,1870.594849,1870.049561,1869.738159,1869.398804,1869.899292,1870.117188,1869.829346</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1443,44 @@
       </c>
       <c r="F27" t="n">
         <v>1887.682250976562</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1882.27001953125</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5.412231445312045</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2875374621681472</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5406461125092955</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:42:57</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1881.669311523438</v>
       </c>
     </row>
   </sheetData>
@@ -1456,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3078,6 +3116,24 @@
           <t>1886.685669,1886.663452,1886.647583,1886.848755,1886.331665,1886.294800,1887.086060,1886.518921,1887.210205,1887.044189,1886.449341,1886.048706,1886.534058,1886.311768,1886.377808,1886.513550,1887.076172,1886.892822,1886.903198,1886.703125,1886.936890,1887.178955,1887.504761,1887.682251</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1881.260010,1882.979980,1882.089966,1870.939941,1871.180054,1876.410034,1871.060059,1873.939941,1876.410034,1871.229980,1867.319946,1864.930054,1879.239990,1883.369995,1876.630005,1873.630005,1879.040039,1878.560059,1876.560059,1876.560059,1880.689941,1880.689941,1882.270020,1882.270020</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>5.425659,3.683472,4.557617,15.908814,15.151611,9.884766,16.026001,12.578980,10.800171,15.814209,19.129395,21.118652,7.294068,2.941773,9.747803,12.883545,8.036133,8.332763,10.343139,10.143066,6.246949,6.489014,5.234741,5.412231</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.288406,0.195619,0.242157,0.850311,0.809736,0.526791,0.856520,0.671258,0.575576,0.845124,1.024430,1.132410,0.388139,0.156197,0.519431,0.687625,0.427672,0.443572,0.551176,0.540514,0.332163,0.345034,0.278108,0.287537</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5406461125092955</v>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>1886.418213,1887.684448,1886.777466,1886.728394,1888.127197,1886.241211,1887.664795,1887.127686,1887.206909,1887.846680,1887.168091,1884.897217,1886.739746,1885.875977,1886.404297,1887.214600,1885.291748,1886.926880,1886.738892,1885.881958,1885.937134,1886.225952,1887.734741,1886.360840</t>
@@ -3091,6 +3147,49 @@
       <c r="M27" t="inlineStr">
         <is>
           <t>1882.488647,1880.433716,1879.007080,1878.823608,1877.438843,1876.571167,1876.710938,1876.201294,1876.417358,1875.348389,1873.946655,1873.714844,1873.514404,1871.923218,1872.189453,1871.677612,1871.363403,1870.594849,1870.049561,1869.738159,1869.398804,1869.899292,1870.117188,1869.829346</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:42:57</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1882.230591,1882.186279,1881.777100,1881.911987,1881.364502,1881.177246,1881.304565,1880.366699,1880.955811,1881.081787,1880.555054,1880.059448,1880.623535,1880.564331,1880.575195,1880.522339,1880.609741,1880.558228,1880.601440,1880.667725,1880.784668,1880.939575,1881.644287,1881.669312</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1882.439575,1882.590942,1882.658447,1881.837646,1882.862305,1881.603638,1881.952271,1880.945923,1881.727417,1881.026245,1881.608276,1879.842163,1881.730713,1880.464844,1881.322510,1880.504761,1879.619629,1881.227295,1881.229980,1880.633057,1880.343262,1879.970947,1881.516235,1882.079346</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1874.907104,1872.765625,1870.529175,1869.999756,1868.106323,1867.081787,1866.202881,1863.527100,1863.304321,1862.149780,1861.295044,1860.307983,1859.505493,1858.585693,1857.838501,1856.614746,1855.926025,1856.011963,1853.858032,1853.548096,1853.550537,1853.896362,1853.607300,1852.486206</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>1878.161011,1876.480103,1874.582642,1874.649170,1873.456177,1872.269897,1871.551147,1870.156738,1870.186401,1869.361694,1868.357422,1868.124023,1867.937744,1866.653931,1866.795654,1865.963623,1865.447021,1865.062622,1864.750366,1864.576416,1864.285400,1864.772705,1864.988159,1864.572510</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,6 +1481,44 @@
       </c>
       <c r="F28" t="n">
         <v>1881.669311523438</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1877.890014648438</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.779296875000455</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2012523015469563</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1001758249319217</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:49:59</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>24</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1879.285888671875</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3177,6 +3215,24 @@
           <t>1882.230591,1882.186279,1881.777100,1881.911987,1881.364502,1881.177246,1881.304565,1880.366699,1880.955811,1881.081787,1880.555054,1880.059448,1880.623535,1880.564331,1880.575195,1880.522339,1880.609741,1880.558228,1880.601440,1880.667725,1880.784668,1880.939575,1881.644287,1881.669312</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1883.119995,1880.890015,1882.579956,1878.959961,1880.359985,1878.560059,1875.099976,1878.410034,1879.160034,1877.290039,1881.560059,1881.500000,1881.479980,1882.890015,1883.089966,1882.400024,1880.869995,1882.359985,1881.329956,1883.130005,1882.579956,1880.979980,1880.650024,1877.890015</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.889404,1.296264,0.802856,2.952026,1.004517,2.617187,6.204589,1.956665,1.795777,3.791748,1.005005,1.440552,0.856445,2.325684,2.514771,1.877685,0.260254,1.801757,0.728516,2.462280,1.795288,0.040405,0.994263,3.779297</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.047230,0.068918,0.042647,0.157110,0.053422,0.139319,0.330894,0.104166,0.095563,0.201980,0.053413,0.076564,0.045520,0.123517,0.133545,0.099750,0.013837,0.095718,0.038723,0.130755,0.095363,0.002148,0.052868,0.201252</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1001758249319217</v>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>1882.439575,1882.590942,1882.658447,1881.837646,1882.862305,1881.603638,1881.952271,1880.945923,1881.727417,1881.026245,1881.608276,1879.842163,1881.730713,1880.464844,1881.322510,1880.504761,1879.619629,1881.227295,1881.229980,1880.633057,1880.343262,1879.970947,1881.516235,1882.079346</t>
@@ -3190,6 +3246,49 @@
       <c r="M28" t="inlineStr">
         <is>
           <t>1878.161011,1876.480103,1874.582642,1874.649170,1873.456177,1872.269897,1871.551147,1870.156738,1870.186401,1869.361694,1868.357422,1868.124023,1867.937744,1866.653931,1866.795654,1865.963623,1865.447021,1865.062622,1864.750366,1864.576416,1864.285400,1864.772705,1864.988159,1864.572510</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:49:59</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>24</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1878.018799,1877.909668,1877.861450,1877.726807,1877.598389,1877.650024,1877.781372,1877.522095,1877.990723,1877.873779,1877.817261,1878.101929,1878.379150,1878.427246,1878.591675,1878.788818,1879.191772,1879.122681,1879.207153,1878.843262,1878.922485,1878.826172,1878.887451,1879.285889</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1878.090576,1878.276245,1878.248779,1878.310913,1878.744507,1878.302124,1877.528687,1877.885376,1878.720947,1879.363037,1878.319336,1878.892212,1878.791138,1878.894897,1879.810791,1879.883545,1879.271362,1879.750366,1880.259155,1879.244873,1879.591919,1879.705078,1879.182495,1879.915527</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1874.778687,1873.397217,1871.817627,1871.536133,1870.027100,1869.661621,1869.385010,1868.452881,1867.514282,1866.422363,1865.844238,1865.563110,1864.890991,1864.784546,1864.044556,1863.530884,1863.594604,1862.999390,1860.886719,1860.401733,1860.482422,1860.498657,1859.835571,1859.817749</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>1876.564819,1875.361450,1874.261719,1873.724487,1873.095459,1872.729248,1872.639526,1872.407227,1872.726685,1871.527344,1870.774536,1871.029907,1871.163940,1870.396606,1870.545532,1870.266235,1870.362915,1869.759399,1869.306396,1868.755493,1868.833130,1868.106689,1868.258789,1868.393555</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1519,6 +1519,44 @@
       </c>
       <c r="F29" t="n">
         <v>1879.285888671875</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1890.619995117188</v>
+      </c>
+      <c r="H29" t="n">
+        <v>11.3341064453125</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.5994915146663288</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.1679393787965508</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:31</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1887.96630859375</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3276,6 +3314,24 @@
           <t>1878.018799,1877.909668,1877.861450,1877.726807,1877.598389,1877.650024,1877.781372,1877.522095,1877.990723,1877.873779,1877.817261,1878.101929,1878.379150,1878.427246,1878.591675,1878.788818,1879.191772,1879.122681,1879.207153,1878.843262,1878.922485,1878.826172,1878.887451,1879.285889</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1881.790039,1881.010010,1879.949951,1878.119995,1878.660034,1879.300049,1878.829956,1878.140015,1878.760010,1878.910034,1877.750000,1879.910034,1881.380005,1882.010010,1887.589966,1883.119995,1883.689941,1884.150024,1880.099976,1873.719971,1874.079956,1874.130005,1876.770020,1890.619995</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3.771240,3.100342,2.088501,0.393188,1.061645,1.650025,1.048584,0.617920,0.769287,1.036255,0.067261,1.808105,3.000855,3.582764,8.998291,4.331177,4.498169,5.027343,0.892823,5.123291,4.842529,4.696167,2.117431,11.334106</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.200407,0.164823,0.111093,0.020935,0.056511,0.087800,0.055810,0.032901,0.040947,0.055152,0.003582,0.096180,0.159503,0.190369,0.476708,0.230000,0.238796,0.266823,0.047488,0.273429,0.258395,0.250579,0.112823,0.599491</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.1679393787965508</v>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>1878.090576,1878.276245,1878.248779,1878.310913,1878.744507,1878.302124,1877.528687,1877.885376,1878.720947,1879.363037,1878.319336,1878.892212,1878.791138,1878.894897,1879.810791,1879.883545,1879.271362,1879.750366,1880.259155,1879.244873,1879.591919,1879.705078,1879.182495,1879.915527</t>
@@ -3289,6 +3345,49 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>1876.564819,1875.361450,1874.261719,1873.724487,1873.095459,1872.729248,1872.639526,1872.407227,1872.726685,1871.527344,1870.774536,1871.029907,1871.163940,1870.396606,1870.545532,1870.266235,1870.362915,1869.759399,1869.306396,1868.755493,1868.833130,1868.106689,1868.258789,1868.393555</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:31</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1889.545532,1889.303955,1888.416626,1887.884277,1887.539917,1887.684448,1887.642090,1887.140869,1887.529175,1887.818848,1887.931641,1887.806152,1887.917725,1887.681152,1887.835571,1887.773926,1888.277222,1887.888306,1887.779175,1887.593506,1887.153564,1886.822632,1887.436035,1887.966309</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>1889.940796,1888.930908,1889.252197,1888.054077,1888.259888,1887.925293,1887.743896,1887.373657,1887.826660,1888.242920,1888.269409,1887.912476,1888.317749,1887.990967,1888.199341,1888.121094,1888.067505,1888.121582,1888.372925,1886.442383,1886.616577,1887.269043,1887.629761,1887.746582</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1882.986084,1880.923096,1878.108154,1876.915894,1875.463135,1875.368164,1874.599365,1873.635742,1873.512207,1873.148071,1872.406982,1871.624146,1870.900513,1870.518188,1870.228882,1869.521729,1869.738281,1869.053223,1867.306274,1866.786011,1866.427856,1865.569336,1865.560913,1866.140625</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>1885.887329,1884.330811,1882.067871,1880.967651,1879.851196,1879.351196,1879.605469,1878.667114,1879.603516,1878.877808,1878.273071,1878.288330,1878.173462,1876.866699,1877.553467,1877.144165,1877.347412,1876.782104,1876.105713,1875.719604,1875.192871,1874.413208,1874.781860,1875.023926</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1557,6 +1557,44 @@
       </c>
       <c r="F30" t="n">
         <v>1887.96630859375</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1903.170043945312</v>
+      </c>
+      <c r="H30" t="n">
+        <v>15.2037353515625</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.798863737895161</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.8070067255495392</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:42:51</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>24</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1904.133422851562</v>
       </c>
     </row>
   </sheetData>
@@ -1570,7 +1608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3375,6 +3413,24 @@
           <t>1889.545532,1889.303955,1888.416626,1887.884277,1887.539917,1887.684448,1887.642090,1887.140869,1887.529175,1887.818848,1887.931641,1887.806152,1887.917725,1887.681152,1887.835571,1887.773926,1888.277222,1887.888306,1887.779175,1887.593506,1887.153564,1886.822632,1887.436035,1887.966309</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1900.400024,1899.060059,1901.780029,1897.790039,1905.140015,1899.140015,1892.369995,1891.969971,1905.239990,1902.699951,1897.119995,1902.869995,1907.709961,1911.459961,1905.410034,1907.219971,1908.410034,1905.670044,1904.880005,1905.810059,1905.810059,1908.079956,1908.079956,1903.170044</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>10.854492,9.756104,13.363403,9.905762,17.600098,11.455567,4.727905,4.829102,17.710815,14.881103,9.188354,15.063843,19.792236,23.778809,17.574463,19.446045,20.132812,17.781738,17.100830,18.216553,18.656495,21.257324,20.643921,15.203735</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.571169,0.513733,0.702679,0.521963,0.923822,0.603198,0.249840,0.255242,0.929584,0.782105,0.484332,0.791638,1.037487,1.244013,0.922345,1.019602,1.054952,0.933096,0.897738,0.955843,0.978927,1.114069,1.081921,0.798864</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.8070067255495392</v>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>1889.940796,1888.930908,1889.252197,1888.054077,1888.259888,1887.925293,1887.743896,1887.373657,1887.826660,1888.242920,1888.269409,1887.912476,1888.317749,1887.990967,1888.199341,1888.121094,1888.067505,1888.121582,1888.372925,1886.442383,1886.616577,1887.269043,1887.629761,1887.746582</t>
@@ -3388,6 +3444,49 @@
       <c r="M30" t="inlineStr">
         <is>
           <t>1885.887329,1884.330811,1882.067871,1880.967651,1879.851196,1879.351196,1879.605469,1878.667114,1879.603516,1878.877808,1878.273071,1878.288330,1878.173462,1876.866699,1877.553467,1877.144165,1877.347412,1876.782104,1876.105713,1875.719604,1875.192871,1874.413208,1874.781860,1875.023926</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:42:51</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>24</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1903.905762,1904.361206,1904.191772,1904.444702,1904.142334,1904.527466,1904.857422,1904.590332,1904.955933,1904.796387,1904.800415,1904.535400,1904.408081,1904.238770,1904.350464,1904.252075,1905.072510,1904.833130,1904.927246,1904.943115,1904.439209,1904.454102,1904.495605,1904.133423</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1903.088989,1903.655884,1905.181641,1903.989014,1904.804565,1904.041260,1904.337769,1903.994385,1903.237061,1904.857300,1904.020874,1903.208496,1903.196411,1904.522705,1903.712280,1904.954346,1904.366455,1903.238037,1904.071045,1904.087524,1903.100098,1904.545654,1903.840942,1903.628418</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1897.256348,1896.659546,1894.828735,1894.460571,1893.484985,1893.199097,1892.232178,1891.327759,1891.138916,1890.225830,1889.302612,1888.662354,1887.828003,1887.308716,1886.637329,1885.763062,1886.187500,1886.381714,1884.185181,1883.530273,1883.011108,1883.100220,1882.229248,1881.562622</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1900.230103,1899.816650,1898.467407,1898.652344,1897.588745,1896.962036,1897.015869,1896.383545,1897.131348,1895.871582,1895.285522,1894.798340,1894.675415,1893.853638,1893.437744,1893.288574,1893.618042,1893.689941,1892.973999,1892.729614,1891.837402,1891.764038,1891.184814,1890.211548</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1595,6 +1595,44 @@
       </c>
       <c r="F31" t="n">
         <v>1904.133422851562</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1912</v>
+      </c>
+      <c r="H31" t="n">
+        <v>7.866577148437955</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.4114318592279265</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.4385885498170279</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:35</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>24</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1913.7470703125</v>
       </c>
     </row>
   </sheetData>
@@ -1608,7 +1646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3474,6 +3512,24 @@
           <t>1903.905762,1904.361206,1904.191772,1904.444702,1904.142334,1904.527466,1904.857422,1904.590332,1904.955933,1904.796387,1904.800415,1904.535400,1904.408081,1904.238770,1904.350464,1904.252075,1905.072510,1904.833130,1904.927246,1904.943115,1904.439209,1904.454102,1904.495605,1904.133423</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1891.390015,1892.890015,1894.770020,1893.900024,1901.329956,1896.939941,1898.380005,1894.800049,1896.089966,1901.209961,1897.650024,1896.000000,1909.750000,1916.469971,1917.380005,1910.229980,1915.310059,1912.199951,1911.520020,1910.969971,1912.239990,1915.989990,1912.209961,1912.000000</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>12.515747,11.471191,9.421752,10.544678,2.812378,7.587525,6.477417,9.790283,8.865967,3.586426,7.150391,8.535400,5.341919,12.231201,13.029541,5.977905,10.237549,7.366821,6.592774,6.026856,7.800781,11.535888,7.714356,7.866577</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.661722,0.606015,0.497250,0.556771,0.147916,0.399988,0.341208,0.516692,0.467592,0.188639,0.376802,0.450179,0.279718,0.638215,0.679549,0.312942,0.534511,0.385254,0.344897,0.315382,0.407939,0.602085,0.403426,0.411432</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.4385885498170279</v>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>1903.088989,1903.655884,1905.181641,1903.989014,1904.804565,1904.041260,1904.337769,1903.994385,1903.237061,1904.857300,1904.020874,1903.208496,1903.196411,1904.522705,1903.712280,1904.954346,1904.366455,1903.238037,1904.071045,1904.087524,1903.100098,1904.545654,1903.840942,1903.628418</t>
@@ -3487,6 +3543,49 @@
       <c r="M31" t="inlineStr">
         <is>
           <t>1900.230103,1899.816650,1898.467407,1898.652344,1897.588745,1896.962036,1897.015869,1896.383545,1897.131348,1895.871582,1895.285522,1894.798340,1894.675415,1893.853638,1893.437744,1893.288574,1893.618042,1893.689941,1892.973999,1892.729614,1891.837402,1891.764038,1891.184814,1890.211548</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:35</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>24</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1912.146973,1912.132935,1912.101685,1912.380371,1912.297241,1912.671143,1913.168091,1912.850952,1913.240356,1913.713623,1914.050781,1913.866577,1914.209717,1914.193237,1914.266724,1914.184448,1914.859497,1914.475586,1914.622314,1914.283447,1913.898926,1914.053101,1913.754395,1913.747070</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1911.661743,1911.729248,1912.363403,1911.815308,1912.891113,1912.731812,1912.929688,1912.454590,1913.123291,1913.626221,1913.681030,1912.252441,1912.839355,1914.589722,1913.845459,1913.979492,1913.783691,1912.219482,1913.504395,1913.728760,1912.007324,1913.331299,1913.054932,1913.342773</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1905.372192,1903.969727,1902.502930,1902.043945,1901.034546,1900.982544,1900.557129,1899.343750,1899.009644,1898.781860,1898.455200,1897.920288,1897.997925,1897.327393,1896.998657,1896.290161,1896.397339,1896.467529,1893.897461,1893.099731,1892.686890,1892.265991,1891.162720,1890.722656</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>1908.375854,1907.008667,1906.189941,1906.244263,1905.679443,1905.183105,1905.374756,1904.692627,1905.093262,1904.600342,1904.568359,1904.439819,1904.451660,1903.852417,1904.088013,1903.735596,1904.220825,1903.860962,1903.111084,1902.485474,1901.552124,1901.574341,1900.607666,1900.011719</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1633,6 +1633,44 @@
       </c>
       <c r="F32" t="n">
         <v>1913.7470703125</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2264.409912109375</v>
+      </c>
+      <c r="H32" t="n">
+        <v>350.662841796875</v>
+      </c>
+      <c r="I32" t="n">
+        <v>15.48583760924366</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5.875467386616582</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:35</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>24</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2201.969970703125</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3573,6 +3611,24 @@
           <t>1912.146973,1912.132935,1912.101685,1912.380371,1912.297241,1912.671143,1913.168091,1912.850952,1913.240356,1913.713623,1914.050781,1913.866577,1914.209717,1914.193237,1914.266724,1914.184448,1914.859497,1914.475586,1914.622314,1914.283447,1913.898926,1914.053101,1913.754395,1913.747070</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1906.280029,1910.410034,1909.109985,1908.699951,1916.089966,1914.459961,1920.099976,1917.630005,1918.510010,1921.550049,1935.699951,1931.310059,1968.599976,2085.350098,2088.770020,2090.620117,2091.620117,2101.929932,2218.300049,2285.479980,2262.139893,2261.139893,2261.139893,2264.409912</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>5.866944,1.722901,2.991700,3.680420,3.792725,1.788818,6.931885,4.779053,5.269654,7.836426,21.649170,17.443482,54.390259,171.156861,174.503296,176.435669,176.760620,187.454346,303.677735,371.196533,348.240967,347.086792,347.385498,350.662842</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.307769,0.090185,0.156707,0.192823,0.197941,0.093437,0.361017,0.249217,0.274674,0.407818,1.118416,0.903194,2.762890,8.207584,8.354357,8.439394,8.450895,8.918201,13.689660,16.241513,15.394316,15.350080,15.363291,15.485838</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>5.875467386616582</v>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>1911.661743,1911.729248,1912.363403,1911.815308,1912.891113,1912.731812,1912.929688,1912.454590,1913.123291,1913.626221,1913.681030,1912.252441,1912.839355,1914.589722,1913.845459,1913.979492,1913.783691,1912.219482,1913.504395,1913.728760,1912.007324,1913.331299,1913.054932,1913.342773</t>
@@ -3586,6 +3642,49 @@
       <c r="M32" t="inlineStr">
         <is>
           <t>1908.375854,1907.008667,1906.189941,1906.244263,1905.679443,1905.183105,1905.374756,1904.692627,1905.093262,1904.600342,1904.568359,1904.439819,1904.451660,1903.852417,1904.088013,1903.735596,1904.220825,1903.860962,1903.111084,1902.485474,1901.552124,1901.574341,1900.607666,1900.011719</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:35</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>24</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2260.327881,2259.396729,2253.023682,2249.615723,2244.273926,2246.824219,2247.304688,2247.410156,2243.275635,2236.903809,2234.740479,2232.696777,2229.742920,2230.375000,2227.084229,2223.086426,2222.470703,2218.132812,2215.278076,2213.446289,2210.084473,2207.388428,2203.564209,2201.969971</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2252.504150,2243.324707,2249.192627,2233.139893,2227.745850,2225.006348,2220.704102,2224.131592,2214.539062,2208.694580,2209.529541,2199.421875,2198.078613,2201.002197,2199.597168,2200.103027,2190.881836,2194.800293,2187.339355,2180.874512,2179.774414,2180.404541,2173.342773,2169.123047</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2206.374512,2189.800537,2168.895508,2150.016602,2136.226562,2125.750000,2110.821045,2099.259521,2092.810547,2081.659180,2072.376709,2059.125244,2063.949463,2048.631348,2042.528198,2039.937988,2034.130249,2027.137939,2020.668213,2012.345337,2012.227661,2005.345581,2001.414429,2002.203857</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2227.887939,2219.207275,2202.032471,2193.358887,2177.043457,2171.626953,2166.322998,2157.029541,2149.118652,2139.267578,2130.213135,2128.110840,2120.961426,2114.906250,2109.607422,2108.317139,2104.539551,2097.718506,2094.104248,2090.107666,2085.552734,2077.422607,2075.951660,2072.393555</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1671,6 +1671,44 @@
       </c>
       <c r="F33" t="n">
         <v>2201.969970703125</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2373.590087890625</v>
+      </c>
+      <c r="H33" t="n">
+        <v>171.6201171875</v>
+      </c>
+      <c r="I33" t="n">
+        <v>7.230402505599284</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.915041415955062</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:48:55</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>24</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2343.8828125</v>
       </c>
     </row>
   </sheetData>
@@ -1684,7 +1722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3672,6 +3710,24 @@
           <t>2260.327881,2259.396729,2253.023682,2249.615723,2244.273926,2246.824219,2247.304688,2247.410156,2243.275635,2236.903809,2234.740479,2232.696777,2229.742920,2230.375000,2227.084229,2223.086426,2222.470703,2218.132812,2215.278076,2213.446289,2210.084473,2207.388428,2203.564209,2201.969971</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2250.649902,2249.419922,2248.550049,2246.750000,2261.100098,2249.959961,2280.000000,2276.949951,2285.139893,2294.830078,2288.600098,2274.500000,2279.899902,2325.939941,2343.199951,2343.500000,2315.850098,2323.469971,2317.909912,2318.510010,2313.669922,2326.600098,2340.229980,2373.590088</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>9.677979,9.976807,4.473633,2.865723,16.826172,3.135742,32.695312,29.539795,41.864258,57.926269,53.859619,41.803223,50.156982,95.564941,116.115722,120.413574,93.379395,105.337159,102.631836,105.063721,103.585449,119.211670,136.665771,171.620117</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.430008,0.443528,0.198956,0.127550,0.744159,0.139369,1.434005,1.297341,1.832022,2.524207,2.353387,1.837908,2.199964,4.108659,4.955434,5.138194,4.032186,4.533614,4.427775,4.531519,4.477106,5.123857,5.839844,7.230402</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>2.915041415955062</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>2252.504150,2243.324707,2249.192627,2233.139893,2227.745850,2225.006348,2220.704102,2224.131592,2214.539062,2208.694580,2209.529541,2199.421875,2198.078613,2201.002197,2199.597168,2200.103027,2190.881836,2194.800293,2187.339355,2180.874512,2179.774414,2180.404541,2173.342773,2169.123047</t>
@@ -3685,6 +3741,49 @@
       <c r="M33" t="inlineStr">
         <is>
           <t>2227.887939,2219.207275,2202.032471,2193.358887,2177.043457,2171.626953,2166.322998,2157.029541,2149.118652,2139.267578,2130.213135,2128.110840,2120.961426,2114.906250,2109.607422,2108.317139,2104.539551,2097.718506,2094.104248,2090.107666,2085.552734,2077.422607,2075.951660,2072.393555</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:48:55</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>24</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2374.015869,2376.250488,2375.443115,2377.348389,2376.310547,2378.929688,2380.904053,2377.874512,2376.271484,2377.557617,2375.451660,2375.791748,2373.625244,2373.461670,2373.458496,2364.174072,2364.003662,2364.000732,2355.065430,2351.091553,2349.356201,2347.783447,2346.345459,2343.882812</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2372.901367,2365.778809,2372.547607,2370.952148,2368.694580,2366.461914,2355.077393,2364.230225,2357.545898,2357.868164,2355.507812,2344.797119,2339.680420,2349.770508,2339.264648,2332.829102,2338.176514,2331.476318,2321.430664,2312.155762,2317.298584,2317.260254,2303.854004,2301.778076</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2332.860840,2325.016357,2313.417969,2300.710938,2287.378662,2282.553955,2267.810791,2253.368164,2245.688477,2239.411865,2228.011719,2212.724609,2211.488037,2195.027344,2186.153809,2173.938477,2161.919922,2153.988770,2133.417725,2115.960205,2111.058594,2102.148926,2098.579590,2099.338867</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2349.622314,2346.996094,2337.239746,2333.880371,2322.899170,2319.070557,2316.646240,2304.350830,2299.325195,2298.003174,2286.402832,2283.777832,2274.073242,2265.931152,2260.079590,2252.077148,2243.157715,2239.225586,2223.503174,2213.473877,2208.370117,2199.085449,2199.309326,2196.300049</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,6 +1709,44 @@
       </c>
       <c r="F34" t="n">
         <v>2343.8828125</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2515.989990234375</v>
+      </c>
+      <c r="H34" t="n">
+        <v>172.107177734375</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6.840535073764046</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.318523733023452</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:41:58</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>24</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2503.224609375</v>
       </c>
     </row>
   </sheetData>
@@ -1722,7 +1760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3771,6 +3809,24 @@
           <t>2374.015869,2376.250488,2375.443115,2377.348389,2376.310547,2378.929688,2380.904053,2377.874512,2376.271484,2377.557617,2375.451660,2375.791748,2373.625244,2373.461670,2373.458496,2364.174072,2364.003662,2364.000732,2355.065430,2351.091553,2349.356201,2347.783447,2346.345459,2343.882812</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2344.520020,2340.030029,2353.280029,2367.600098,2371.280029,2369.979980,2443.090088,2403.600098,2395.020020,2369.850098,2387.560059,2388.129883,2392.969971,2392.889893,2406.020020,2423.120117,2419.899902,2413.209961,2440.510010,2489.540039,2489.540039,2521.810059,2521.810059,2515.989990</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>29.495849,36.220459,22.163086,9.748291,5.030518,8.949708,62.186035,25.725586,18.748536,7.707519,12.108399,12.338135,19.344727,19.428223,32.561524,58.946045,55.896240,49.209229,85.444580,138.448486,140.183838,174.026612,175.464600,172.107178</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1.258076,1.547863,0.941796,0.411737,0.212144,0.377628,2.545384,1.070294,0.782813,0.325232,0.507145,0.516644,0.808398,0.811915,1.353336,2.432651,2.309858,2.039161,3.501095,5.561207,5.630913,6.900861,6.957883,6.840535</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>2.318523733023452</v>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>2372.901367,2365.778809,2372.547607,2370.952148,2368.694580,2366.461914,2355.077393,2364.230225,2357.545898,2357.868164,2355.507812,2344.797119,2339.680420,2349.770508,2339.264648,2332.829102,2338.176514,2331.476318,2321.430664,2312.155762,2317.298584,2317.260254,2303.854004,2301.778076</t>
@@ -3784,6 +3840,49 @@
       <c r="M34" t="inlineStr">
         <is>
           <t>2349.622314,2346.996094,2337.239746,2333.880371,2322.899170,2319.070557,2316.646240,2304.350830,2299.325195,2298.003174,2286.402832,2283.777832,2274.073242,2265.931152,2260.079590,2252.077148,2243.157715,2239.225586,2223.503174,2213.473877,2208.370117,2199.085449,2199.309326,2196.300049</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:41:58</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>24</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2513.897705,2514.944336,2514.135498,2515.549316,2512.582764,2514.449951,2512.856201,2510.449707,2511.054199,2511.974854,2510.882324,2511.154053,2505.911621,2506.596191,2509.571289,2506.387451,2507.354004,2506.257812,2507.999023,2505.208740,2502.736328,2503.400635,2506.591064,2503.224609</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2512.081055,2504.592773,2517.004639,2510.225098,2508.090332,2505.647949,2493.551025,2511.671387,2498.510498,2502.116699,2493.302490,2488.281738,2484.754150,2496.222900,2489.093506,2489.962891,2486.729736,2481.727783,2480.977295,2483.827148,2479.528564,2481.878418,2465.982422,2470.268066</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2496.193115,2489.512207,2476.197754,2469.553711,2454.198730,2453.658936,2437.507324,2425.333496,2426.481689,2423.008301,2411.016602,2399.457275,2397.715820,2386.081299,2377.923828,2372.940674,2364.437256,2354.735596,2343.430908,2325.063721,2323.434326,2315.460938,2314.092285,2315.384766</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2503.980713,2502.481934,2491.187256,2491.188721,2478.858643,2476.357422,2472.363770,2463.980713,2463.411377,2462.106689,2455.464844,2453.410156,2442.082764,2435.424316,2430.677490,2431.582764,2426.818359,2420.804443,2415.671875,2407.133301,2401.244385,2398.493408,2400.702148,2398.143799</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1747,6 +1747,44 @@
       </c>
       <c r="F35" t="n">
         <v>2503.224609375</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2426.929931640625</v>
+      </c>
+      <c r="H35" t="n">
+        <v>76.294677734375</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3.143670393598844</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.008984891192476</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:51:51</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2428.493408203125</v>
       </c>
     </row>
   </sheetData>
@@ -1760,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3870,6 +3908,24 @@
           <t>2513.897705,2514.944336,2514.135498,2515.549316,2512.582764,2514.449951,2512.856201,2510.449707,2511.054199,2511.974854,2510.882324,2511.154053,2505.911621,2506.596191,2509.571289,2506.387451,2507.354004,2506.257812,2507.999023,2505.208740,2502.736328,2503.400635,2506.591064,2503.224609</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2515.469971,2514.659912,2514.810059,2440.239990,2437.560059,2432.760010,2425.510010,2421.689941,2412.850098,2424.020020,2428.399902,2429.979980,2413.629883,2410.469971,2422.370117,2426.100098,2427.600098,2439.000000,2431.800049,2406.969971,2414.219971,2430.820068,2430.820068,2426.929932</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1.572266,0.284424,0.674561,75.309326,75.022705,81.689941,87.346191,88.759766,98.204101,87.954834,82.482422,81.174073,92.281738,96.126220,87.201172,80.287353,79.753906,67.257812,76.198974,98.238769,88.516357,72.580567,75.770996,76.294677</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0.062504,0.011311,0.026824,3.086144,3.077779,3.357912,3.601147,3.665199,4.070046,3.628470,3.396575,3.340524,3.823359,3.987862,3.599829,3.309317,3.285298,2.757598,3.133439,4.081429,3.666458,2.985847,3.117096,3.143670</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>3.008984891192476</v>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>2512.081055,2504.592773,2517.004639,2510.225098,2508.090332,2505.647949,2493.551025,2511.671387,2498.510498,2502.116699,2493.302490,2488.281738,2484.754150,2496.222900,2489.093506,2489.962891,2486.729736,2481.727783,2480.977295,2483.827148,2479.528564,2481.878418,2465.982422,2470.268066</t>
@@ -3883,6 +3939,49 @@
       <c r="M35" t="inlineStr">
         <is>
           <t>2503.980713,2502.481934,2491.187256,2491.188721,2478.858643,2476.357422,2472.363770,2463.980713,2463.411377,2462.106689,2455.464844,2453.410156,2442.082764,2435.424316,2430.677490,2431.582764,2426.818359,2420.804443,2415.671875,2407.133301,2401.244385,2398.493408,2400.702148,2398.143799</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:51:51</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2427.962158,2427.240967,2427.502686,2429.777832,2426.344238,2427.558838,2427.218018,2426.278076,2426.915039,2423.249512,2426.266846,2424.619629,2424.518311,2423.129395,2427.463379,2426.678223,2426.809570,2427.144287,2427.885498,2425.731934,2425.098633,2425.984131,2427.593994,2428.493408</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2428.028320,2421.715820,2428.378906,2430.243164,2420.967285,2427.060059,2417.188965,2422.469971,2425.578613,2419.888184,2420.065674,2411.158936,2404.675049,2416.072266,2416.722900,2416.405029,2417.316650,2412.292236,2412.507568,2416.980957,2416.145508,2413.666260,2407.126953,2415.161377</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2416.729736,2411.965332,2404.090576,2402.983398,2392.424072,2391.241211,2384.602539,2377.295654,2376.614258,2371.751953,2368.144531,2358.716553,2361.880859,2351.426514,2347.431152,2344.205566,2340.183594,2336.643799,2327.654297,2315.263428,2313.556396,2308.035156,2308.800049,2311.857910</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2422.823730,2419.013428,2413.904053,2415.886719,2407.479736,2405.858887,2404.505859,2398.102539,2397.957520,2394.634766,2394.867432,2392.217041,2387.826172,2382.397217,2383.298584,2383.114990,2380.036621,2378.210693,2373.675781,2369.952637,2367.400879,2362.233154,2366.038574,2365.455322</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1785,6 +1785,44 @@
       </c>
       <c r="F36" t="n">
         <v>2428.493408203125</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2437.820068359375</v>
+      </c>
+      <c r="H36" t="n">
+        <v>9.32666015625</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.3825819746625819</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.9923950125628858</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>24</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2433.604736328125</v>
       </c>
     </row>
   </sheetData>
@@ -1798,7 +1836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3969,6 +4007,24 @@
           <t>2427.962158,2427.240967,2427.502686,2429.777832,2426.344238,2427.558838,2427.218018,2426.278076,2426.915039,2423.249512,2426.266846,2424.619629,2424.518311,2423.129395,2427.463379,2426.678223,2426.809570,2427.144287,2427.885498,2425.731934,2425.098633,2425.984131,2427.593994,2428.493408</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2416.520020,2413.739990,2379.989990,2373.169922,2389.510010,2388.419922,2412.389893,2411.179932,2414.750000,2433.360107,2426.719971,2459.280029,2438.500000,2438.389893,2450.540039,2440.260010,2448.239990,2444.459961,2450.100098,2469.870117,2455.000000,2463.540039,2465.429932,2437.820068</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>11.442138,13.500977,47.512696,56.607910,36.834228,39.138916,14.828125,15.098144,12.165039,10.110595,0.453125,34.660400,13.981689,15.260498,23.076660,13.581787,21.430420,17.315674,22.214600,44.138183,29.901367,37.555908,37.835938,9.326660</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0.473497,0.559338,1.996340,2.385329,1.541497,1.638695,0.614665,0.626172,0.503780,0.415499,0.018672,1.409372,0.573373,0.625843,0.941697,0.556571,0.875340,0.708364,0.906681,1.787065,1.217978,1.524469,1.534659,0.382582</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.9923950125628858</v>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>2428.028320,2421.715820,2428.378906,2430.243164,2420.967285,2427.060059,2417.188965,2422.469971,2425.578613,2419.888184,2420.065674,2411.158936,2404.675049,2416.072266,2416.722900,2416.405029,2417.316650,2412.292236,2412.507568,2416.980957,2416.145508,2413.666260,2407.126953,2415.161377</t>
@@ -3982,6 +4038,49 @@
       <c r="M36" t="inlineStr">
         <is>
           <t>2422.823730,2419.013428,2413.904053,2415.886719,2407.479736,2405.858887,2404.505859,2398.102539,2397.957520,2394.634766,2394.867432,2392.217041,2387.826172,2382.397217,2383.298584,2383.114990,2380.036621,2378.210693,2373.675781,2369.952637,2367.400879,2362.233154,2366.038574,2365.455322</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>24</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2437.704102,2434.913818,2435.330322,2436.817871,2433.823975,2434.801025,2434.285156,2434.746582,2435.496582,2433.959717,2434.787598,2435.407471,2434.790771,2431.298096,2433.822266,2435.411133,2434.813477,2432.839355,2433.095703,2433.368408,2432.438232,2431.381104,2432.075928,2433.604736</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2435.643311,2428.909180,2433.987793,2437.328857,2433.606934,2433.146484,2422.517090,2428.341064,2432.898926,2429.141113,2431.571777,2423.623047,2419.490234,2423.837402,2423.022461,2426.316895,2422.738281,2421.179199,2418.730713,2424.392822,2422.015381,2419.001465,2417.107910,2421.912598</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2414.180664,2407.138672,2400.004883,2400.197998,2390.876465,2386.279297,2383.842285,2380.052246,2375.361328,2371.162842,2367.408203,2362.751221,2364.037109,2353.054932,2347.973145,2349.473633,2346.500488,2343.633301,2336.636963,2328.764648,2327.158691,2321.456299,2323.217285,2327.401367</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2425.859863,2418.136475,2415.869629,2415.236816,2409.670654,2406.097168,2404.964600,2401.019775,2400.603516,2397.068359,2394.973633,2394.859375,2391.696289,2383.582764,2382.893799,2385.378906,2383.594727,2379.684814,2376.586426,2377.329590,2374.431641,2367.644043,2373.504395,2375.043213</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1823,6 +1823,44 @@
       </c>
       <c r="F37" t="n">
         <v>2433.604736328125</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2495.5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>61.895263671875</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.480275041950511</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.602699528670466</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:51</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>24</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2492.037109375</v>
       </c>
     </row>
   </sheetData>
@@ -1836,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4068,6 +4106,24 @@
           <t>2437.704102,2434.913818,2435.330322,2436.817871,2433.823975,2434.801025,2434.285156,2434.746582,2435.496582,2433.959717,2434.787598,2435.407471,2434.790771,2431.298096,2433.822266,2435.411133,2434.813477,2432.839355,2433.095703,2433.368408,2432.438232,2431.381104,2432.075928,2433.604736</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2443.790039,2430.290039,2438.300049,2449.290039,2456.409912,2454.229980,2454.379883,2462.729980,2464.590088,2494.129883,2512.290039,2493.050049,2515.500000,2487.209961,2476.899902,2468.649902,2473.919922,2469.820068,2474.469971,2482.479980,2482.479980,2493.719971,2493.719971,2495.500000</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6.085937,4.623779,2.969727,12.472168,22.585937,19.428955,20.094727,27.983398,29.093506,60.170166,77.502441,57.642578,80.709229,55.911865,43.077636,33.238769,39.106445,36.980713,41.374268,49.111572,50.041748,62.338867,61.644043,61.895264</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.249037,0.190256,0.121795,0.509216,0.919469,0.791652,0.818729,1.136276,1.180460,2.412471,3.084932,2.312131,3.208477,2.247975,1.739176,1.346435,1.580748,1.497304,1.672046,1.978327,2.015797,2.499834,2.471971,2.480275</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>1.602699528670466</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>2435.643311,2428.909180,2433.987793,2437.328857,2433.606934,2433.146484,2422.517090,2428.341064,2432.898926,2429.141113,2431.571777,2423.623047,2419.490234,2423.837402,2423.022461,2426.316895,2422.738281,2421.179199,2418.730713,2424.392822,2422.015381,2419.001465,2417.107910,2421.912598</t>
@@ -4081,6 +4137,49 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>2425.859863,2418.136475,2415.869629,2415.236816,2409.670654,2406.097168,2404.964600,2401.019775,2400.603516,2397.068359,2394.973633,2394.859375,2391.696289,2383.582764,2382.893799,2385.378906,2383.594727,2379.684814,2376.586426,2377.329590,2374.431641,2367.644043,2373.504395,2375.043213</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:51</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>24</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2496.082520,2495.334473,2496.352539,2497.587891,2494.358398,2497.454590,2497.411621,2494.353027,2494.891357,2493.207031,2493.534668,2494.729004,2492.945801,2490.981445,2494.045166,2494.365967,2493.533691,2491.436279,2491.367676,2492.315674,2490.263428,2490.232422,2490.898193,2492.037109</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2493.080078,2493.699219,2496.035400,2495.578125,2493.227295,2494.907959,2489.918945,2490.633545,2491.705078,2488.546143,2489.923096,2485.092529,2480.462891,2484.025879,2485.449951,2486.852539,2481.889160,2478.857666,2477.873779,2482.431885,2479.853271,2476.874512,2474.867188,2481.349121</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2469.229492,2469.042480,2465.506104,2466.743896,2459.589111,2458.471680,2455.367920,2449.327881,2445.122559,2440.739746,2436.654785,2432.542236,2433.359863,2424.748779,2421.013184,2421.992920,2417.961914,2414.214844,2405.982910,2401.220703,2394.481445,2390.884277,2389.654541,2391.945312</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2481.856445,2479.365479,2479.106201,2480.324707,2474.333008,2473.803467,2472.759033,2467.793945,2466.677734,2463.808838,2462.335938,2461.753418,2459.123047,2452.727539,2453.949951,2454.851562,2454.405762,2449.928711,2446.881104,2446.941895,2441.349121,2435.491211,2439.335449,2440.409180</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1861,6 +1861,44 @@
       </c>
       <c r="F38" t="n">
         <v>2492.037109375</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2455.679931640625</v>
+      </c>
+      <c r="H38" t="n">
+        <v>36.357177734375</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.480534057632054</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.952435432912684</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>24</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2445.212158203125</v>
       </c>
     </row>
   </sheetData>
@@ -1874,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4167,6 +4205,24 @@
           <t>2496.082520,2495.334473,2496.352539,2497.587891,2494.358398,2497.454590,2497.411621,2494.353027,2494.891357,2493.207031,2493.534668,2494.729004,2492.945801,2490.981445,2494.045166,2494.365967,2493.533691,2491.436279,2491.367676,2492.315674,2490.263428,2490.232422,2490.898193,2492.037109</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2507.159912,2498.790039,2494.169922,2507.899902,2500.270020,2478.120117,2484.110107,2474.030029,2481.469971,2477.520020,2473.129883,2460.739990,2476.969971,2483.350098,2471.080078,2471.250000,2467.510010,2463.669922,2435.860107,2441.520020,2451.250000,2446.580078,2446.580078,2455.679932</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>11.077392,3.455566,2.182617,10.312011,5.911622,19.334473,13.301514,20.322998,13.421386,15.687011,20.404785,33.989014,15.975830,7.631347,22.965088,23.115967,26.023681,27.766357,55.507569,50.795654,39.013428,43.652344,44.318115,36.357177</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.441830,0.138290,0.087509,0.411181,0.236439,0.780207,0.535464,0.821453,0.540864,0.633174,0.825059,1.381252,0.644975,0.307301,0.929354,0.935396,1.054654,1.127032,2.278767,2.080493,1.591573,1.784219,1.811431,1.480534</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.952435432912684</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>2493.080078,2493.699219,2496.035400,2495.578125,2493.227295,2494.907959,2489.918945,2490.633545,2491.705078,2488.546143,2489.923096,2485.092529,2480.462891,2484.025879,2485.449951,2486.852539,2481.889160,2478.857666,2477.873779,2482.431885,2479.853271,2476.874512,2474.867188,2481.349121</t>
@@ -4180,6 +4236,49 @@
       <c r="M38" t="inlineStr">
         <is>
           <t>2481.856445,2479.365479,2479.106201,2480.324707,2474.333008,2473.803467,2472.759033,2467.793945,2466.677734,2463.808838,2462.335938,2461.753418,2459.123047,2452.727539,2453.949951,2454.851562,2454.405762,2449.928711,2446.881104,2446.941895,2441.349121,2435.491211,2439.335449,2440.409180</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>24</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2455.762695,2453.937744,2454.038086,2454.469727,2451.406982,2451.804932,2452.617188,2449.080078,2450.776123,2449.094727,2448.301270,2448.428955,2449.683105,2447.391357,2449.437988,2447.264160,2447.993896,2446.823486,2446.183838,2446.256104,2445.870361,2443.830566,2445.147461,2445.212158</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2450.929688,2454.141357,2453.061768,2452.958496,2452.606201,2452.750488,2448.329346,2443.243164,2447.367920,2445.558350,2446.754395,2439.712646,2440.026611,2443.470215,2440.828613,2435.227295,2436.323242,2431.548828,2432.753662,2434.163574,2433.251953,2427.724854,2428.925049,2435.615479</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2432.057129,2431.136719,2426.845947,2427.793457,2422.620117,2419.700928,2419.844482,2414.979004,2410.982178,2405.605469,2400.694336,2396.632812,2400.024170,2391.542236,2386.303223,2381.609375,2377.999023,2374.058105,2367.201416,2363.481201,2359.505859,2352.500244,2351.814697,2350.717285</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2442.895996,2439.860840,2438.667236,2439.001465,2435.229004,2434.110352,2434.968994,2429.319824,2431.028320,2426.811523,2423.383789,2423.205078,2422.342285,2416.497559,2417.075684,2413.252441,2413.469482,2409.562012,2406.635498,2406.443115,2403.258789,2396.009521,2398.959473,2397.527100</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1899,6 +1899,44 @@
       </c>
       <c r="F39" t="n">
         <v>2445.212158203125</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2497.780029296875</v>
+      </c>
+      <c r="H39" t="n">
+        <v>52.56787109375</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.1045836894031</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.7873885642935653</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:22</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2516.124755859375</v>
       </c>
     </row>
   </sheetData>
@@ -1912,7 +1950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4266,6 +4304,24 @@
           <t>2455.762695,2453.937744,2454.038086,2454.469727,2451.406982,2451.804932,2452.617188,2449.080078,2450.776123,2449.094727,2448.301270,2448.428955,2449.683105,2447.391357,2449.437988,2447.264160,2447.993896,2446.823486,2446.183838,2446.256104,2445.870361,2443.830566,2445.147461,2445.212158</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2465.280029,2465.290039,2456.580078,2464.560059,2459.830078,2461.330078,2456.030029,2447.610107,2468.550049,2462.310059,2454.510010,2457.179932,2439.290039,2450.090088,2444.820068,2460.899902,2473.080078,2469.790039,2472.100098,2497.000000,2493.899902,2507.239990,2492.000000,2497.780029</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>9.517334,11.352295,2.541992,10.090332,8.423096,9.525146,3.412841,1.469971,17.773926,13.215332,6.208740,8.750977,10.393066,2.698731,4.617920,13.635742,25.086182,22.966553,25.916260,50.743896,48.029541,63.409424,46.852539,52.567871</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.386055,0.460485,0.103477,0.409417,0.342426,0.386992,0.138958,0.060057,0.720015,0.536705,0.252952,0.356139,0.426069,0.110148,0.188886,0.554096,1.014370,0.929899,1.048350,2.032194,1.925881,2.529053,1.880118,2.104584</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.7873885642935653</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>2450.929688,2454.141357,2453.061768,2452.958496,2452.606201,2452.750488,2448.329346,2443.243164,2447.367920,2445.558350,2446.754395,2439.712646,2440.026611,2443.470215,2440.828613,2435.227295,2436.323242,2431.548828,2432.753662,2434.163574,2433.251953,2427.724854,2428.925049,2435.615479</t>
@@ -4279,6 +4335,49 @@
       <c r="M39" t="inlineStr">
         <is>
           <t>2442.895996,2439.860840,2438.667236,2439.001465,2435.229004,2434.110352,2434.968994,2429.319824,2431.028320,2426.811523,2423.383789,2423.205078,2422.342285,2416.497559,2417.075684,2413.252441,2413.469482,2409.562012,2406.635498,2406.443115,2403.258789,2396.009521,2398.959473,2397.527100</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:22</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2529.570312,2526.749756,2527.788574,2525.969238,2524.319580,2525.156006,2525.886475,2520.172119,2522.135010,2520.841309,2521.952148,2519.959473,2521.029785,2518.250732,2521.710205,2519.903564,2520.667480,2518.648926,2517.555420,2515.744873,2516.601074,2513.194092,2515.162354,2516.124756</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2524.361084,2529.622559,2525.072510,2522.678955,2525.978760,2519.979492,2521.271484,2515.322754,2518.862061,2515.457520,2520.269043,2506.884277,2511.317383,2514.657715,2514.662598,2513.071533,2511.270508,2505.290039,2508.821045,2506.192871,2507.383301,2503.293457,2505.614014,2507.845215</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2497.602539,2494.929199,2494.159668,2495.167236,2490.614014,2487.957275,2488.353027,2482.633789,2478.713135,2473.221191,2472.496582,2470.752441,2473.693115,2463.358154,2462.187256,2459.687744,2456.811279,2456.151367,2448.917725,2441.106445,2444.136475,2434.915527,2436.363770,2437.196777</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2510.382812,2505.461426,2508.603760,2506.111816,2504.455078,2501.649902,2501.333740,2493.920166,2496.666260,2492.687012,2493.585449,2492.731934,2494.186035,2484.667725,2486.856934,2485.539551,2486.254883,2483.223389,2479.076904,2476.421875,2476.144531,2469.669434,2471.087891,2472.882812</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1937,6 +1937,44 @@
       </c>
       <c r="F40" t="n">
         <v>2516.124755859375</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2488.659912109375</v>
+      </c>
+      <c r="H40" t="n">
+        <v>27.46484375</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.103599717115262</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.629590558084355</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:19</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>24</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2502.6318359375</v>
       </c>
     </row>
   </sheetData>
@@ -1950,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4365,6 +4403,24 @@
           <t>2529.570312,2526.749756,2527.788574,2525.969238,2524.319580,2525.156006,2525.886475,2520.172119,2522.135010,2520.841309,2521.952148,2519.959473,2521.029785,2518.250732,2521.710205,2519.903564,2520.667480,2518.648926,2517.555420,2515.744873,2516.601074,2513.194092,2515.162354,2516.124756</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2534.699951,2503.500000,2501.580078,2495.360107,2497.500000,2517.649902,2522.020020,2522.399902,2518.479980,2507.260010,2499.159912,2508.729980,2504.510010,2515.610107,2511.729980,2516.149902,2512.879883,2492.479980,2490.750000,2486.850098,2494.010010,2503.610107,2496.600098,2488.659912</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>5.129639,23.249756,26.208496,30.609131,26.819580,7.506104,3.866455,2.227783,3.655030,13.581299,22.792236,11.229493,16.519775,2.640625,9.980225,3.753662,7.787597,26.168946,26.805420,28.894775,22.591064,9.583985,18.562256,27.464844</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.202377,0.928690,1.047678,1.226642,1.073857,0.298139,0.153308,0.088320,0.145128,0.541679,0.911996,0.447617,0.659601,0.104970,0.397345,0.149183,0.309907,1.049916,1.076199,1.161903,0.905813,0.382807,0.743501,1.103600</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.629590558084355</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>2524.361084,2529.622559,2525.072510,2522.678955,2525.978760,2519.979492,2521.271484,2515.322754,2518.862061,2515.457520,2520.269043,2506.884277,2511.317383,2514.657715,2514.662598,2513.071533,2511.270508,2505.290039,2508.821045,2506.192871,2507.383301,2503.293457,2505.614014,2507.845215</t>
@@ -4378,6 +4434,49 @@
       <c r="M40" t="inlineStr">
         <is>
           <t>2510.382812,2505.461426,2508.603760,2506.111816,2504.455078,2501.649902,2501.333740,2493.920166,2496.666260,2492.687012,2493.585449,2492.731934,2494.186035,2484.667725,2486.856934,2485.539551,2486.254883,2483.223389,2479.076904,2476.421875,2476.144531,2469.669434,2471.087891,2472.882812</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:19</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>24</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2508.181152,2505.411133,2504.935791,2506.115967,2504.765625,2506.726562,2507.271729,2503.994385,2505.047119,2505.550049,2503.864746,2503.806885,2504.848877,2502.299805,2504.229004,2504.250977,2505.152344,2501.980469,2501.901855,2502.250488,2502.895508,2500.713135,2500.530518,2502.631836</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2505.251465,2508.748779,2499.044189,2504.185059,2507.875000,2500.955566,2501.946289,2496.687988,2505.174561,2501.671875,2503.728027,2494.733398,2495.000000,2498.159180,2496.753418,2492.461670,2496.395020,2494.084229,2495.864258,2490.943359,2490.699463,2487.730713,2491.164062,2493.681152</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2490.405273,2489.308105,2486.930420,2491.383301,2484.878418,2484.780273,2486.316895,2481.247559,2476.805664,2476.043457,2470.370117,2470.341064,2471.152832,2465.208740,2463.600342,2461.651855,2460.941650,2457.187256,2451.392822,2448.028809,2448.296143,2444.154785,2442.295898,2445.276611</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2500.503662,2496.194580,2496.846191,2497.285645,2494.384033,2494.426025,2494.166748,2489.706055,2491.482910,2490.122803,2486.446045,2486.743164,2489.310059,2482.242432,2483.028320,2482.729980,2485.021973,2478.365479,2476.758545,2476.418213,2476.729004,2472.072510,2472.651367,2475.867676</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1975,6 +1975,44 @@
       </c>
       <c r="F41" t="n">
         <v>2502.6318359375</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2435.639892578125</v>
+      </c>
+      <c r="H41" t="n">
+        <v>66.991943359375</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.750486373766198</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.375199329442559</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:51:54</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>24</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2438.7021484375</v>
       </c>
     </row>
   </sheetData>
@@ -1988,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4464,6 +4502,24 @@
           <t>2508.181152,2505.411133,2504.935791,2506.115967,2504.765625,2506.726562,2507.271729,2503.994385,2505.047119,2505.550049,2503.864746,2503.806885,2504.848877,2502.299805,2504.229004,2504.250977,2505.152344,2501.980469,2501.901855,2502.250488,2502.895508,2500.713135,2500.530518,2502.631836</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2499.010010,2510.320068,2513.199951,2472.100098,2442.239990,2443.810059,2428.100098,2435.679932,2427.709961,2424.929932,2442.250000,2442.790039,2442.500000,2443.620117,2438.780029,2435.110107,2440.590088,2439.030029,2435.639893,2435.639893,2435.639893,2435.639893,2435.639893,2435.639893</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>9.171142,4.908935,8.264160,34.015869,62.525635,62.916503,79.171631,68.314453,77.337158,80.620117,61.614746,61.016846,62.348877,58.679688,65.448975,69.140870,64.562256,62.950440,66.261962,66.610595,67.255615,65.073242,64.890625,66.991943</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0.366991,0.195550,0.328830,1.375991,2.560176,2.574525,3.260641,2.804739,3.185601,3.324637,2.522868,2.497834,2.552666,2.401342,2.683677,2.839332,2.645354,2.580962,2.720516,2.734829,2.761312,2.671710,2.664213,2.750486</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>2.375199329442559</v>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>2505.251465,2508.748779,2499.044189,2504.185059,2507.875000,2500.955566,2501.946289,2496.687988,2505.174561,2501.671875,2503.728027,2494.733398,2495.000000,2498.159180,2496.753418,2492.461670,2496.395020,2494.084229,2495.864258,2490.943359,2490.699463,2487.730713,2491.164062,2493.681152</t>
@@ -4477,6 +4533,49 @@
       <c r="M41" t="inlineStr">
         <is>
           <t>2500.503662,2496.194580,2496.846191,2497.285645,2494.384033,2494.426025,2494.166748,2489.706055,2491.482910,2490.122803,2486.446045,2486.743164,2489.310059,2482.242432,2483.028320,2482.729980,2485.021973,2478.365479,2476.758545,2476.418213,2476.729004,2472.072510,2472.651367,2475.867676</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:51:54</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>24</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2438.573486,2436.323730,2437.125488,2438.343750,2438.703613,2440.313965,2441.118164,2437.001709,2439.426025,2439.978027,2437.192139,2436.979980,2438.546631,2436.472412,2438.263184,2438.226074,2438.918213,2438.555176,2439.841553,2439.551270,2440.709473,2437.665039,2437.227051,2438.702148</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2439.035400,2440.756104,2436.549561,2437.745361,2441.627686,2436.242188,2437.471680,2434.517090,2438.522461,2436.577637,2435.096924,2430.087158,2427.458740,2436.668457,2431.398438,2426.467773,2429.020020,2430.175049,2433.601562,2427.403809,2429.540771,2424.331055,2426.037109,2424.071533</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2425.390381,2423.193604,2420.020508,2423.612549,2416.600342,2413.806641,2416.791504,2409.476074,2404.205078,2401.928955,2395.376465,2395.710938,2393.453125,2386.481201,2384.319580,2380.194336,2378.662598,2375.268066,2370.894043,2366.763184,2365.379883,2360.673340,2358.525146,2358.187012</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2433.714355,2428.502441,2428.534424,2428.787842,2425.618164,2426.593750,2425.639648,2418.236328,2421.950195,2420.171631,2415.257080,2415.271729,2414.967773,2409.784180,2410.911621,2408.559570,2408.237305,2405.465088,2404.729980,2404.473145,2404.151855,2397.551514,2398.126221,2401.445801</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2013,6 +2013,44 @@
       </c>
       <c r="F42" t="n">
         <v>2438.7021484375</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2458.25</v>
+      </c>
+      <c r="H42" t="n">
+        <v>19.5478515625</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.7951937989423371</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.4852004010196476</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:37</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>24</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2460.532958984375</v>
       </c>
     </row>
   </sheetData>
@@ -2026,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4563,6 +4601,24 @@
           <t>2438.573486,2436.323730,2437.125488,2438.343750,2438.703613,2440.313965,2441.118164,2437.001709,2439.426025,2439.978027,2437.192139,2436.979980,2438.546631,2436.472412,2438.263184,2438.226074,2438.918213,2438.555176,2439.841553,2439.551270,2440.709473,2437.665039,2437.227051,2438.702148</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2436.320068,2434.379883,2435.320068,2434.889893,2435.870117,2434.770020,2435.760010,2448.659912,2444.790039,2450.840088,2450.649902,2452.459961,2453.399902,2452.770020,2451.459961,2452.340088,2457.469971,2459.050049,2456.760010,2455.070068,2457.350098,2456.159912,2458.250000,2458.250000</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2.253418,1.943847,1.805420,3.453857,2.833496,5.543945,5.358154,11.658203,5.364014,10.862061,13.457763,15.479981,14.853271,16.297608,13.196777,14.114014,18.551758,20.494873,16.918457,15.518798,16.640625,18.494873,21.022949,19.547852</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.092493,0.079850,0.074135,0.141849,0.116324,0.227699,0.219979,0.476105,0.219406,0.443197,0.549151,0.631202,0.605416,0.664457,0.538323,0.575532,0.754913,0.833447,0.688649,0.632112,0.677178,0.753000,0.855200,0.795194</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.4852004010196476</v>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>2439.035400,2440.756104,2436.549561,2437.745361,2441.627686,2436.242188,2437.471680,2434.517090,2438.522461,2436.577637,2435.096924,2430.087158,2427.458740,2436.668457,2431.398438,2426.467773,2429.020020,2430.175049,2433.601562,2427.403809,2429.540771,2424.331055,2426.037109,2424.071533</t>
@@ -4576,6 +4632,49 @@
       <c r="M42" t="inlineStr">
         <is>
           <t>2433.714355,2428.502441,2428.534424,2428.787842,2425.618164,2426.593750,2425.639648,2418.236328,2421.950195,2420.171631,2415.257080,2415.271729,2414.967773,2409.784180,2410.911621,2408.559570,2408.237305,2405.465088,2404.729980,2404.473145,2404.151855,2397.551514,2398.126221,2401.445801</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:37</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>24</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2461.656738,2459.606689,2460.601807,2462.066406,2462.396729,2463.279785,2463.822998,2461.380615,2462.450195,2462.798584,2462.210205,2461.129395,2463.202393,2459.379395,2462.766113,2462.376465,2464.213135,2460.032715,2461.730225,2461.613037,2462.698242,2459.328613,2459.608643,2460.532959</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2459.261230,2458.525146,2460.664307,2459.883301,2466.950684,2457.337158,2460.429932,2461.222900,2461.223633,2460.067871,2458.524170,2455.825195,2455.737793,2457.493652,2459.838867,2453.425781,2456.871094,2452.844727,2456.805908,2454.736816,2456.981445,2448.375732,2452.471191,2450.825928</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2450.581299,2450.110840,2448.630127,2452.904785,2447.294922,2443.672852,2445.493408,2441.619629,2435.827637,2434.315918,2430.821533,2428.963867,2427.587646,2423.352295,2422.818604,2419.718506,2420.218018,2413.603027,2410.710693,2407.137695,2407.481934,2403.231689,2403.215820,2400.807373</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2457.955078,2454.549805,2455.220459,2456.251465,2453.323242,2452.891846,2452.782227,2449.378662,2450.875977,2449.357178,2447.131592,2445.331787,2447.353516,2440.037354,2443.347168,2441.096680,2442.548340,2436.952637,2436.650391,2436.949219,2437.177002,2431.364746,2432.127686,2435.289795</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2051,6 +2051,44 @@
       </c>
       <c r="F43" t="n">
         <v>2460.532958984375</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2422.0400390625</v>
+      </c>
+      <c r="H43" t="n">
+        <v>38.492919921875</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.589276779122713</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.069973197612403</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:10</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>24</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2432.97705078125</v>
       </c>
     </row>
   </sheetData>
@@ -2064,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4662,6 +4700,24 @@
           <t>2461.656738,2459.606689,2460.601807,2462.066406,2462.396729,2463.279785,2463.822998,2461.380615,2462.450195,2462.798584,2462.210205,2461.129395,2463.202393,2459.379395,2462.766113,2462.376465,2464.213135,2460.032715,2461.730225,2461.613037,2462.698242,2459.328613,2459.608643,2460.532959</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2461.189941,2455.229980,2456.959961,2453.229980,2459.300049,2460.010010,2469.000000,2475.419922,2477.030029,2481.020020,2529.100098,2505.489990,2510.649902,2503.590088,2490.610107,2481.709961,2470.679932,2417.810059,2428.360107,2412.560059,2407.449951,2420.810059,2417.159912,2422.040039</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.466797,4.376709,3.641846,8.836426,3.096680,3.269775,5.177002,14.039307,14.579834,18.221436,66.889893,44.360595,47.447509,44.210693,27.843994,19.333496,6.466797,42.222656,33.370118,49.052978,55.248291,38.518554,42.448731,38.492920</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.018966,0.178261,0.148226,0.360196,0.125917,0.132917,0.209680,0.567148,0.588601,0.734433,2.644810,1.770536,1.889850,1.765892,1.117959,0.779039,0.261742,1.746318,1.374183,2.033233,2.294888,1.591143,1.756141,1.589277</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>1.069973197612403</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>2459.261230,2458.525146,2460.664307,2459.883301,2466.950684,2457.337158,2460.429932,2461.222900,2461.223633,2460.067871,2458.524170,2455.825195,2455.737793,2457.493652,2459.838867,2453.425781,2456.871094,2452.844727,2456.805908,2454.736816,2456.981445,2448.375732,2452.471191,2450.825928</t>
@@ -4675,6 +4731,49 @@
       <c r="M43" t="inlineStr">
         <is>
           <t>2457.955078,2454.549805,2455.220459,2456.251465,2453.323242,2452.891846,2452.782227,2449.378662,2450.875977,2449.357178,2447.131592,2445.331787,2447.353516,2440.037354,2443.347168,2441.096680,2442.548340,2436.952637,2436.650391,2436.949219,2437.177002,2431.364746,2432.127686,2435.289795</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:10</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>24</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2426.406006,2426.379639,2426.522217,2429.032715,2428.476318,2431.099121,2432.093262,2430.774902,2431.079102,2432.041016,2432.055664,2432.891602,2434.588379,2432.770996,2434.789551,2433.212646,2434.069824,2432.212158,2433.640625,2434.825195,2433.198242,2431.417969,2431.843750,2432.977051</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2426.887207,2428.815918,2427.371826,2432.178467,2432.752930,2427.348145,2430.015137,2431.015381,2430.330078,2430.568359,2432.159668,2429.997070,2426.926758,2433.689941,2428.953369,2426.503418,2429.396484,2427.447266,2429.741943,2424.586426,2428.425049,2418.181641,2426.737793,2425.298340</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2408.155273,2406.744629,2402.904297,2408.957275,2400.191406,2400.588867,2401.739014,2397.377686,2393.260986,2392.010010,2389.586182,2390.040527,2388.524658,2385.207520,2382.911865,2377.428223,2376.744141,2371.246826,2367.037842,2364.619385,2361.912109,2357.464844,2356.683594,2354.782715</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2418.859131,2414.104004,2413.081787,2415.973633,2411.954590,2412.858887,2412.310791,2409.790771,2411.322266,2409.943359,2409.044922,2409.370605,2409.836670,2405.281494,2406.633057,2401.925537,2403.027100,2398.893555,2398.154785,2400.471680,2397.728027,2392.184570,2393.935303,2396.990234</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2089,6 +2089,44 @@
       </c>
       <c r="F44" t="n">
         <v>2432.97705078125</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2471.419921875</v>
+      </c>
+      <c r="H44" t="n">
+        <v>38.44287109375</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.555497337926467</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.247613258037289</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:48:57</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>24</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2469.2568359375</v>
       </c>
     </row>
   </sheetData>
@@ -2102,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4761,6 +4799,24 @@
           <t>2426.406006,2426.379639,2426.522217,2429.032715,2428.476318,2431.099121,2432.093262,2430.774902,2431.079102,2432.041016,2432.055664,2432.891602,2434.588379,2432.770996,2434.789551,2433.212646,2434.069824,2432.212158,2433.640625,2434.825195,2433.198242,2431.417969,2431.843750,2432.977051</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2438.340088,2440.459961,2446.110107,2446.139893,2454.679932,2445.750000,2450.820068,2439.370117,2466.290039,2467.219971,2468.870117,2475.040039,2477.370117,2481.600098,2472.479980,2478.090088,2468.919922,2467.290039,2471.219971,2462.290039,2464.330078,2471.610107,2471.419922,2471.419922</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>11.934082,14.080322,19.587890,17.107178,26.203614,14.650879,18.726806,8.595215,35.210937,35.178955,36.814453,42.148437,42.781738,48.829102,37.690429,44.877442,34.850098,35.077881,37.579346,27.464844,31.131836,40.192138,39.576172,38.442871</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0.489435,0.576954,0.800777,0.699354,1.067496,0.599034,0.764104,0.352354,1.427688,1.425854,1.491146,1.702940,1.726901,1.967646,1.524398,1.810969,1.411552,1.421717,1.520680,1.115419,1.263298,1.626152,1.601354,1.555497</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1.247613258037289</v>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>2426.887207,2428.815918,2427.371826,2432.178467,2432.752930,2427.348145,2430.015137,2431.015381,2430.330078,2430.568359,2432.159668,2429.997070,2426.926758,2433.689941,2428.953369,2426.503418,2429.396484,2427.447266,2429.741943,2424.586426,2428.425049,2418.181641,2426.737793,2425.298340</t>
@@ -4774,6 +4830,49 @@
       <c r="M44" t="inlineStr">
         <is>
           <t>2418.859131,2414.104004,2413.081787,2415.973633,2411.954590,2412.858887,2412.310791,2409.790771,2411.322266,2409.943359,2409.044922,2409.370605,2409.836670,2405.281494,2406.633057,2401.925537,2403.027100,2398.893555,2398.154785,2400.471680,2397.728027,2392.184570,2393.935303,2396.990234</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:48:57</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>24</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2473.865234,2473.566895,2472.837158,2474.519287,2475.236328,2476.172607,2475.455566,2473.000244,2472.894043,2473.082031,2471.765137,2472.644531,2473.170654,2471.278076,2473.043701,2472.233398,2472.461182,2471.979004,2471.919189,2473.130859,2471.772461,2469.245605,2469.374268,2469.256836</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2473.190918,2475.065918,2475.575439,2474.505859,2478.997559,2470.780762,2474.358887,2474.279785,2468.658936,2467.107178,2468.124268,2467.761719,2465.719727,2470.855957,2468.201416,2462.120117,2468.960693,2463.467041,2466.732910,2462.098145,2463.602051,2453.593994,2456.487549,2458.580566</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2459.465088,2458.963379,2455.511475,2461.171875,2454.581299,2453.490234,2453.387939,2448.161865,2443.526123,2441.558594,2437.862061,2437.690918,2436.653076,2430.307617,2427.909180,2422.745605,2421.457031,2418.538818,2412.079834,2409.792725,2408.211914,2402.643311,2402.344727,2398.348145</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2467.572998,2464.574219,2462.960205,2464.902832,2463.110107,2462.473145,2461.188477,2457.503418,2458.558105,2456.291992,2455.362549,2454.295898,2455.000000,2448.629150,2450.387939,2447.767090,2447.367188,2445.700684,2443.699463,2445.294189,2442.510498,2435.803711,2437.249512,2438.615234</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2127,6 +2127,44 @@
       </c>
       <c r="F45" t="n">
         <v>2469.2568359375</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2407.800048828125</v>
+      </c>
+      <c r="H45" t="n">
+        <v>61.456787109375</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.552404097644486</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.657603064604459</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:10:07</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>24</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2416.3720703125</v>
       </c>
     </row>
   </sheetData>
@@ -2140,7 +2178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4860,6 +4898,24 @@
           <t>2473.865234,2473.566895,2472.837158,2474.519287,2475.236328,2476.172607,2475.455566,2473.000244,2472.894043,2473.082031,2471.765137,2472.644531,2473.170654,2471.278076,2473.043701,2472.233398,2472.461182,2471.979004,2471.919189,2473.130859,2471.772461,2469.245605,2469.374268,2469.256836</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2484.070068,2471.139893,2472.020020,2447.500000,2451.610107,2456.239990,2458.320068,2445.850098,2443.750000,2448.360107,2448.020020,2431.919922,2417.709961,2412.520020,2417.800049,2419.939941,2414.360107,2411.739990,2412.949951,2408.000000,2398.179932,2408.320068,2413.189941,2407.800049</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>10.204834,2.427002,0.817138,27.019287,23.626221,19.932617,17.135498,27.150146,29.144043,24.721924,23.745117,40.724609,55.460693,58.758056,55.243652,52.293457,58.101075,60.239014,58.969238,65.130859,73.592529,60.925537,56.184327,61.456787</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0.410811,0.098214,0.033055,1.103955,0.963702,0.811509,0.697041,1.110049,1.192595,1.009734,0.969972,1.674587,2.293935,2.435547,2.284873,2.160940,2.406479,2.497741,2.443865,2.704770,3.068683,2.529794,2.328218,2.552404</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1.657603064604459</v>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>2473.190918,2475.065918,2475.575439,2474.505859,2478.997559,2470.780762,2474.358887,2474.279785,2468.658936,2467.107178,2468.124268,2467.761719,2465.719727,2470.855957,2468.201416,2462.120117,2468.960693,2463.467041,2466.732910,2462.098145,2463.602051,2453.593994,2456.487549,2458.580566</t>
@@ -4873,6 +4929,49 @@
       <c r="M45" t="inlineStr">
         <is>
           <t>2467.572998,2464.574219,2462.960205,2464.902832,2463.110107,2462.473145,2461.188477,2457.503418,2458.558105,2456.291992,2455.362549,2454.295898,2455.000000,2448.629150,2450.387939,2447.767090,2447.367188,2445.700684,2443.699463,2445.294189,2442.510498,2435.803711,2437.249512,2438.615234</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:10:07</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>24</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2409.371582,2407.871582,2407.865479,2408.877441,2408.632812,2410.286133,2411.526123,2409.256836,2410.191895,2411.776123,2412.031738,2412.751953,2413.489990,2412.108887,2414.023438,2413.110596,2413.918945,2414.385742,2415.791992,2416.609863,2417.387939,2416.120117,2416.003906,2416.372070</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2408.100098,2413.040283,2409.786133,2412.454102,2411.684326,2409.262939,2412.993408,2409.441650,2408.681396,2410.027344,2409.989746,2410.798096,2408.127930,2414.234863,2409.874512,2405.187012,2408.813477,2409.100586,2411.032715,2405.858154,2408.472412,2400.377441,2407.334229,2406.348389</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2395.049561,2392.481689,2388.362305,2392.069336,2385.395020,2385.033691,2387.158691,2382.961670,2378.121582,2376.566650,2375.204590,2375.808105,2372.740479,2367.613770,2366.391846,2361.469238,2361.860107,2359.140137,2353.074219,2350.584717,2348.180420,2345.178223,2343.927734,2339.938477</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2404.339844,2398.246338,2396.975342,2397.105713,2395.121826,2394.880615,2395.915039,2391.459473,2393.982910,2393.187500,2393.181152,2391.615479,2391.161377,2387.995117,2390.910645,2387.434814,2387.965332,2385.846924,2385.304443,2386.831787,2385.696289,2380.188232,2381.112305,2384.664795</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2165,6 +2165,44 @@
       </c>
       <c r="F46" t="n">
         <v>2416.3720703125</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2404.510009765625</v>
+      </c>
+      <c r="H46" t="n">
+        <v>11.862060546875</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.4933254799813135</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.9317578789801831</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:07:05</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>24</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2398.20361328125</v>
       </c>
     </row>
   </sheetData>
@@ -2178,7 +2216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4959,6 +4997,24 @@
           <t>2409.371582,2407.871582,2407.865479,2408.877441,2408.632812,2410.286133,2411.526123,2409.256836,2410.191895,2411.776123,2412.031738,2412.751953,2413.489990,2412.108887,2414.023438,2413.110596,2413.918945,2414.385742,2415.791992,2416.609863,2417.387939,2416.120117,2416.003906,2416.372070</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2421.409912,2419.500000,2416.530029,2391.840088,2375.540039,2371.250000,2380.500000,2376.570068,2401.719971,2393.500000,2390.159912,2384.790039,2392.540039,2394.050049,2391.909912,2392.870117,2389.649902,2378.729980,2390.830078,2379.100098,2385.709961,2404.949951,2402.300049,2404.510010</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>12.038330,11.628418,8.664550,17.037353,33.092773,39.036133,31.026123,32.686768,8.471924,18.276123,21.871826,27.961914,20.949951,18.058838,22.113526,20.240479,24.269043,35.655762,24.961914,37.509765,31.677978,11.170166,13.703857,11.862060</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.497162,0.480612,0.358553,0.712312,1.393063,1.646226,1.303345,1.375376,0.352744,0.763573,0.915078,1.172511,0.875636,0.754322,0.924513,0.845866,1.015590,1.498941,1.044069,1.576637,1.327822,0.464466,0.570447,0.493325</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.9317578789801831</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>2408.100098,2413.040283,2409.786133,2412.454102,2411.684326,2409.262939,2412.993408,2409.441650,2408.681396,2410.027344,2409.989746,2410.798096,2408.127930,2414.234863,2409.874512,2405.187012,2408.813477,2409.100586,2411.032715,2405.858154,2408.472412,2400.377441,2407.334229,2406.348389</t>
@@ -4972,6 +5028,49 @@
       <c r="M46" t="inlineStr">
         <is>
           <t>2404.339844,2398.246338,2396.975342,2397.105713,2395.121826,2394.880615,2395.915039,2391.459473,2393.982910,2393.187500,2393.181152,2391.615479,2391.161377,2387.995117,2390.910645,2387.434814,2387.965332,2385.846924,2385.304443,2386.831787,2385.696289,2380.188232,2381.112305,2384.664795</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:07:05</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>24</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2406.200439,2405.200684,2405.063477,2405.732422,2405.481934,2405.850830,2404.971191,2403.860352,2403.090088,2401.989258,2401.340332,2401.877441,2402.093506,2399.716309,2401.048828,2399.997803,2399.669922,2397.107910,2398.354248,2397.406250,2397.874512,2396.968262,2395.902832,2398.203613</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2404.219727,2405.570557,2403.589844,2406.308594,2405.336182,2405.322754,2400.637451,2403.244385,2401.830322,2401.669434,2398.415283,2400.699707,2396.978760,2399.200928,2397.031494,2394.592773,2393.724609,2395.440674,2393.729004,2388.600098,2394.520752,2386.089600,2389.573486,2388.752197</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2385.923828,2383.826904,2380.076172,2383.106689,2377.454102,2376.054199,2376.603760,2373.908447,2366.483398,2361.604248,2358.077881,2359.413086,2355.234863,2352.495605,2351.926270,2347.114746,2347.684570,2341.686279,2337.596680,2334.726074,2333.888672,2329.821777,2328.105225,2327.586426</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2397.714111,2391.575195,2392.113525,2390.399414,2388.600586,2386.625977,2386.089844,2383.332520,2384.852295,2379.295410,2376.787109,2375.177246,2376.526855,2372.237549,2374.472168,2370.835938,2371.727051,2364.570312,2365.211426,2365.491699,2364.984131,2358.430664,2360.500977,2364.359619</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2203,6 +2203,44 @@
       </c>
       <c r="F47" t="n">
         <v>2398.20361328125</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2503.68994140625</v>
+      </c>
+      <c r="H47" t="n">
+        <v>105.486328125</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4.213234489640973</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.788314003147516</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:45</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>24</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2487.122802734375</v>
       </c>
     </row>
   </sheetData>
@@ -2216,7 +2254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5058,6 +5096,24 @@
           <t>2406.200439,2405.200684,2405.063477,2405.732422,2405.481934,2405.850830,2404.971191,2403.860352,2403.090088,2401.989258,2401.340332,2401.877441,2402.093506,2399.716309,2401.048828,2399.997803,2399.669922,2397.107910,2398.354248,2397.406250,2397.874512,2396.968262,2395.902832,2398.203613</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2403.530029,2407.429932,2397.340088,2402.320068,2392.479980,2395.639893,2405.770020,2422.409912,2429.389893,2489.500000,2516.979980,2494.129883,2500.459961,2513.219971,2518.260010,2505.300049,2511.560059,2496.939941,2507.739990,2501.310059,2506.639893,2507.649902,2504.840088,2503.689941</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2.670410,2.229248,7.723389,3.412354,13.001954,10.210937,0.798829,18.549560,26.299805,87.510742,115.639648,92.252442,98.366455,113.503662,117.211182,105.302246,111.890137,99.832031,109.385742,103.903809,108.765381,110.681640,108.937256,105.486328</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.111104,0.092599,0.322165,0.142044,0.543451,0.426230,0.033205,0.765748,1.082568,3.515193,4.594381,3.698783,3.933934,4.516265,4.654451,4.203179,4.455005,3.998175,4.361925,4.153976,4.339091,4.413760,4.349070,4.213235</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>2.788314003147516</v>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>2404.219727,2405.570557,2403.589844,2406.308594,2405.336182,2405.322754,2400.637451,2403.244385,2401.830322,2401.669434,2398.415283,2400.699707,2396.978760,2399.200928,2397.031494,2394.592773,2393.724609,2395.440674,2393.729004,2388.600098,2394.520752,2386.089600,2389.573486,2388.752197</t>
@@ -5071,6 +5127,49 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>2397.714111,2391.575195,2392.113525,2390.399414,2388.600586,2386.625977,2386.089844,2383.332520,2384.852295,2379.295410,2376.787109,2375.177246,2376.526855,2372.237549,2374.472168,2370.835938,2371.727051,2364.570312,2365.211426,2365.491699,2364.984131,2358.430664,2360.500977,2364.359619</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:45</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>24</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2507.282227,2507.012939,2505.294678,2506.241699,2502.701904,2502.565430,2501.672607,2500.317139,2499.666504,2499.169678,2500.610352,2498.916748,2499.448486,2496.452148,2496.910156,2494.249023,2493.257568,2491.389160,2490.546631,2490.300293,2487.496094,2488.730957,2485.607910,2487.122803</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2502.350342,2504.257324,2504.562744,2505.350830,2498.261230,2495.108643,2496.144287,2499.311768,2491.127441,2489.799316,2487.729004,2487.990967,2484.089844,2488.912598,2484.187500,2481.639404,2476.165771,2470.967041,2468.842041,2470.962891,2472.701172,2466.619141,2462.983154,2463.357666</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2489.531738,2486.349609,2478.967773,2481.514648,2467.124756,2463.656006,2459.244873,2454.917725,2446.800537,2441.427734,2438.566162,2436.034424,2431.997803,2423.820312,2419.420898,2410.165527,2405.336182,2397.192627,2386.785889,2380.942139,2374.069824,2371.607422,2364.227539,2359.907715</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2501.773193,2495.388916,2492.351074,2492.086914,2484.310059,2480.900146,2477.397461,2473.712891,2474.897217,2470.832275,2471.645020,2465.358643,2465.696777,2459.318848,2458.436279,2451.764404,2451.006836,2443.811523,2439.338379,2438.227539,2433.467285,2427.940918,2426.599365,2429.853027</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2241,6 +2241,44 @@
       </c>
       <c r="F48" t="n">
         <v>2487.122802734375</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2452.2900390625</v>
+      </c>
+      <c r="H48" t="n">
+        <v>34.832763671875</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.420417777547692</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.362564197685699</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:42</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>24</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2448.373046875</v>
       </c>
     </row>
   </sheetData>
@@ -2254,7 +2292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5157,6 +5195,24 @@
           <t>2507.282227,2507.012939,2505.294678,2506.241699,2502.701904,2502.565430,2501.672607,2500.317139,2499.666504,2499.169678,2500.610352,2498.916748,2499.448486,2496.452148,2496.910156,2494.249023,2493.257568,2491.389160,2490.546631,2490.300293,2487.496094,2488.730957,2485.607910,2487.122803</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2508.949951,2507.719971,2504.179932,2526.879883,2520.689941,2526.139893,2522.979980,2451.419922,2451.860107,2440.169922,2452.080078,2460.469971,2445.469971,2450.679932,2456.479980,2451.489990,2452.429932,2451.500000,2456.070068,2452.340088,2452.159912,2453.300049,2452.840088,2452.290039</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>1.667724,0.707032,1.114746,20.638184,17.988037,23.574463,21.307373,48.897217,47.806397,58.999756,48.530274,38.446777,53.978515,45.772216,40.430176,42.759033,40.827636,39.889160,34.476563,37.960205,35.336182,35.430908,32.767822,34.832764</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.066471,0.028194,0.044515,0.816746,0.713616,0.933221,0.844532,1.994649,1.949801,2.417854,1.979147,1.562579,2.207286,1.867735,1.645858,1.744206,1.664783,1.627133,1.403729,1.547918,1.441023,1.444214,1.335914,1.420418</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>1.362564197685699</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>2502.350342,2504.257324,2504.562744,2505.350830,2498.261230,2495.108643,2496.144287,2499.311768,2491.127441,2489.799316,2487.729004,2487.990967,2484.089844,2488.912598,2484.187500,2481.639404,2476.165771,2470.967041,2468.842041,2470.962891,2472.701172,2466.619141,2462.983154,2463.357666</t>
@@ -5170,6 +5226,49 @@
       <c r="M48" t="inlineStr">
         <is>
           <t>2501.773193,2495.388916,2492.351074,2492.086914,2484.310059,2480.900146,2477.397461,2473.712891,2474.897217,2470.832275,2471.645020,2465.358643,2465.696777,2459.318848,2458.436279,2451.764404,2451.006836,2443.811523,2439.338379,2438.227539,2433.467285,2427.940918,2426.599365,2429.853027</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:42</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>24</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2454.189453,2453.744873,2453.679443,2455.951904,2453.078857,2455.018066,2454.932129,2453.266846,2453.819336,2453.270508,2454.496582,2454.089355,2453.445312,2450.846191,2453.252197,2451.873047,2450.762939,2450.538818,2451.416504,2451.046875,2451.122070,2450.662842,2448.737305,2448.373047</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2450.023193,2455.084961,2451.499512,2457.065430,2450.449219,2449.518066,2452.450439,2450.019043,2444.776367,2452.045410,2442.062744,2445.683594,2441.826904,2446.295410,2440.635010,2437.686523,2437.150391,2435.525879,2434.752197,2435.790771,2434.825928,2427.352051,2426.793457,2429.615234</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2437.164062,2434.961426,2428.799805,2434.274414,2423.977783,2424.823730,2420.688965,2415.456055,2408.298584,2403.443848,2399.250000,2397.741699,2394.701172,2384.138916,2380.554688,2374.021240,2369.568359,2363.668701,2357.035156,2350.251465,2344.788574,2340.307373,2335.938232,2328.474121</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2447.150635,2442.112061,2441.511475,2442.603516,2438.005371,2438.458740,2435.963867,2430.705078,2433.549316,2429.054199,2428.932617,2424.629639,2422.977051,2417.437500,2418.393555,2414.461670,2413.931885,2408.884766,2406.656738,2406.085938,2403.311035,2396.511719,2396.441895,2398.026367</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2279,6 +2279,44 @@
       </c>
       <c r="F49" t="n">
         <v>2448.373046875</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2507.030029296875</v>
+      </c>
+      <c r="H49" t="n">
+        <v>58.656982421875</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.339700032963945</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.8758873716720598</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:32</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>24</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2489.438720703125</v>
       </c>
     </row>
   </sheetData>
@@ -2292,7 +2330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5256,6 +5294,24 @@
           <t>2454.189453,2453.744873,2453.679443,2455.951904,2453.078857,2455.018066,2454.932129,2453.266846,2453.819336,2453.270508,2454.496582,2454.089355,2453.445312,2450.846191,2453.252197,2451.873047,2450.762939,2450.538818,2451.416504,2451.046875,2451.122070,2450.662842,2448.737305,2448.373047</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2451.120117,2453.739990,2457.820068,2456.919922,2458.439941,2454.219971,2453.699951,2458.820068,2454.520020,2457.399902,2460.409912,2471.229980,2481.310059,2480.850098,2477.679932,2477.860107,2488.879883,2481.020020,2482.830078,2490.399902,2505.780029,2503.479980,2509.659912,2507.030029</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>3.069336,0.004883,4.140625,0.968018,5.361084,0.798095,1.232178,5.553222,0.700684,4.129394,5.913330,17.140625,27.864747,30.003907,24.427735,25.987060,38.116944,30.481202,31.413574,39.353027,54.657959,52.817138,60.922607,58.656982</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.125222,0.000199,0.168467,0.039400,0.218069,0.032519,0.050217,0.225849,0.028547,0.168039,0.240339,0.693607,1.122985,1.209420,0.985912,1.048770,1.531490,1.228575,1.265233,1.580189,2.181275,2.109749,2.427524,2.339700</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.8758873716720598</v>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>2450.023193,2455.084961,2451.499512,2457.065430,2450.449219,2449.518066,2452.450439,2450.019043,2444.776367,2452.045410,2442.062744,2445.683594,2441.826904,2446.295410,2440.635010,2437.686523,2437.150391,2435.525879,2434.752197,2435.790771,2434.825928,2427.352051,2426.793457,2429.615234</t>
@@ -5269,6 +5325,49 @@
       <c r="M49" t="inlineStr">
         <is>
           <t>2447.150635,2442.112061,2441.511475,2442.603516,2438.005371,2438.458740,2435.963867,2430.705078,2433.549316,2429.054199,2428.932617,2424.629639,2422.977051,2417.437500,2418.393555,2414.461670,2413.931885,2408.884766,2406.656738,2406.085938,2403.311035,2396.511719,2396.441895,2398.026367</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:32</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>24</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2508.940430,2507.962158,2506.887939,2507.952881,2505.814697,2505.187256,2503.802246,2501.070068,2501.902832,2500.793701,2500.291504,2500.524414,2499.221191,2496.987793,2497.603760,2496.693359,2495.495850,2494.470703,2493.992188,2493.005859,2492.094727,2490.855225,2489.451660,2489.438721</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2502.793213,2504.891113,2506.190430,2503.757324,2505.685303,2497.295898,2496.859619,2500.956787,2492.479736,2495.034912,2488.487549,2487.323975,2489.099365,2488.421143,2486.479980,2485.681396,2485.345459,2479.930908,2481.345947,2478.619141,2479.833740,2475.904297,2469.794922,2472.713379</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2489.686035,2487.992676,2481.537354,2485.220947,2476.410645,2474.445068,2468.918945,2464.612549,2454.809570,2449.819824,2443.660889,2445.415039,2441.217529,2437.100830,2432.326172,2428.464844,2425.636963,2421.006348,2412.400391,2406.820312,2404.047119,2399.578857,2397.792236,2394.235107</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2500.412598,2496.328857,2495.146484,2495.027344,2491.845215,2486.947998,2483.161865,2478.870361,2479.627197,2475.525391,2472.572754,2470.044922,2469.581299,2465.078125,2464.667969,2463.083740,2461.730225,2458.010010,2453.899170,2452.493408,2450.803467,2444.446533,2444.659668,2448.249756</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2317,6 +2317,44 @@
       </c>
       <c r="F50" t="n">
         <v>2489.438720703125</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2497.64990234375</v>
+      </c>
+      <c r="H50" t="n">
+        <v>8.211181640625</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.3287563093978774</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.4013810861769102</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:51</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>24</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2487.896728515625</v>
       </c>
     </row>
   </sheetData>
@@ -2330,7 +2368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5355,6 +5393,24 @@
           <t>2508.940430,2507.962158,2506.887939,2507.952881,2505.814697,2505.187256,2503.802246,2501.070068,2501.902832,2500.793701,2500.291504,2500.524414,2499.221191,2496.987793,2497.603760,2496.693359,2495.495850,2494.470703,2493.992188,2493.005859,2492.094727,2490.855225,2489.451660,2489.438721</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2513.620117,2506.110107,2497.520020,2495.830078,2499.310059,2501.969971,2502.239990,2500.419922,2494.750000,2478.530029,2479.850098,2484.459961,2491.270020,2494.300049,2490.500000,2499.270020,2507.379883,2507.959961,2514.860107,2512.689941,2503.699951,2511.659912,2497.399902,2497.649902</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>4.679687,1.852051,9.367919,12.122803,6.504638,3.217285,1.562256,0.650146,7.152832,22.263672,20.441406,16.064453,7.951171,2.687744,7.103760,2.576661,11.884033,13.489258,20.867919,19.684082,11.605224,20.804687,7.948242,8.211181</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.186173,0.073901,0.375089,0.485722,0.260257,0.128590,0.062434,0.026001,0.286715,0.898261,0.824300,0.646597,0.319161,0.107755,0.285234,0.103097,0.473962,0.537858,0.829785,0.783387,0.463523,0.828324,0.318261,0.328756</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.4013810861769102</v>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>2502.793213,2504.891113,2506.190430,2503.757324,2505.685303,2497.295898,2496.859619,2500.956787,2492.479736,2495.034912,2488.487549,2487.323975,2489.099365,2488.421143,2486.479980,2485.681396,2485.345459,2479.930908,2481.345947,2478.619141,2479.833740,2475.904297,2469.794922,2472.713379</t>
@@ -5368,6 +5424,49 @@
       <c r="M50" t="inlineStr">
         <is>
           <t>2500.412598,2496.328857,2495.146484,2495.027344,2491.845215,2486.947998,2483.161865,2478.870361,2479.627197,2475.525391,2472.572754,2470.044922,2469.581299,2465.078125,2464.667969,2463.083740,2461.730225,2458.010010,2453.899170,2452.493408,2450.803467,2444.446533,2444.659668,2448.249756</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:51</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>24</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2499.764160,2497.738281,2496.859131,2498.094727,2495.118164,2495.902100,2494.916260,2493.544434,2494.889893,2493.066650,2491.143799,2491.735352,2491.107178,2489.050049,2491.358154,2490.316406,2492.328857,2489.987793,2490.640137,2490.539062,2491.025391,2489.449707,2488.075439,2487.896729</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2495.791748,2493.933350,2494.023926,2496.236816,2496.565918,2491.357178,2488.842773,2490.639404,2485.550537,2483.514160,2484.944824,2480.902588,2482.400879,2480.946289,2480.211426,2477.384277,2479.369385,2476.920166,2478.950439,2473.516846,2477.763428,2474.393555,2470.589844,2471.821533</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2484.334717,2482.711182,2477.187012,2479.307617,2471.322021,2470.622559,2465.743652,2461.249756,2455.539551,2451.544434,2443.574463,2444.475586,2440.600098,2439.618164,2435.513428,2432.115479,2433.290527,2428.552979,2422.503662,2418.119629,2418.822754,2416.657227,2412.431641,2410.533447</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2493.032715,2487.983887,2486.520020,2487.059570,2482.743896,2479.903076,2477.548340,2474.318848,2475.465820,2472.124268,2465.262939,2465.432861,2465.495361,2461.399658,2461.997070,2461.121582,2462.109375,2458.858154,2455.749023,2454.704346,2455.689941,2449.571777,2448.208984,2450.089111</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2355,6 +2355,44 @@
       </c>
       <c r="F51" t="n">
         <v>2487.896728515625</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2481</v>
+      </c>
+      <c r="H51" t="n">
+        <v>6.896728515625</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.2779818023226522</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.2510376294709857</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:36</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>24</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2475.58837890625</v>
       </c>
     </row>
   </sheetData>
@@ -2368,7 +2406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5454,6 +5492,24 @@
           <t>2499.764160,2497.738281,2496.859131,2498.094727,2495.118164,2495.902100,2494.916260,2493.544434,2494.889893,2493.066650,2491.143799,2491.735352,2491.107178,2489.050049,2491.358154,2490.316406,2492.328857,2489.987793,2490.640137,2490.539062,2491.025391,2489.449707,2488.075439,2487.896729</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2504.540039,2498.000000,2489.169922,2491.199951,2484.209961,2488.750000,2488.989990,2505.179932,2498.610107,2489.820068,2470.030029,2482.600098,2494.979980,2491.199951,2495.820068,2494.159912,2490.459961,2482.310059,2489.570068,2495.370117,2503.689941,2484.060059,2485.320068,2481.000000</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>4.775879,0.261719,7.689209,6.894776,10.908203,7.152100,5.926270,11.635498,3.720214,3.246582,21.113770,9.135254,3.872802,2.149902,4.461914,3.843506,1.868896,7.677734,1.070069,4.831055,12.664550,5.389648,2.755371,6.896729</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.190689,0.010477,0.308907,0.276765,0.439101,0.287377,0.238099,0.464458,0.148891,0.130394,0.854798,0.367971,0.155224,0.086300,0.178775,0.154100,0.075042,0.309298,0.042982,0.193601,0.505835,0.216969,0.110866,0.277982</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.2510376294709857</v>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>2495.791748,2493.933350,2494.023926,2496.236816,2496.565918,2491.357178,2488.842773,2490.639404,2485.550537,2483.514160,2484.944824,2480.902588,2482.400879,2480.946289,2480.211426,2477.384277,2479.369385,2476.920166,2478.950439,2473.516846,2477.763428,2474.393555,2470.589844,2471.821533</t>
@@ -5467,6 +5523,49 @@
       <c r="M51" t="inlineStr">
         <is>
           <t>2493.032715,2487.983887,2486.520020,2487.059570,2482.743896,2479.903076,2477.548340,2474.318848,2475.465820,2472.124268,2465.262939,2465.432861,2465.495361,2461.399658,2461.997070,2461.121582,2462.109375,2458.858154,2455.749023,2454.704346,2455.689941,2449.571777,2448.208984,2450.089111</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:36</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>24</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2483.050537,2481.594238,2479.586670,2481.768066,2479.415527,2481.654785,2481.214844,2480.139648,2481.883545,2482.010254,2479.410645,2480.798096,2480.081787,2479.123291,2480.310303,2479.968506,2479.637451,2477.722656,2479.107910,2477.722168,2479.445312,2477.496826,2475.387695,2475.588379</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2477.554443,2480.110107,2477.230225,2481.977539,2482.961914,2478.470215,2477.927734,2479.669922,2477.545410,2473.816650,2475.472168,2470.606689,2472.026123,2475.337646,2472.004639,2465.253418,2468.879639,2469.168701,2471.915283,2463.210449,2466.980469,2465.530518,2460.012695,2461.171875</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2468.408447,2466.972168,2460.082520,2464.313721,2456.890381,2457.306396,2455.759033,2452.058594,2446.213379,2443.209717,2435.209961,2437.912109,2432.792236,2432.570801,2428.273193,2425.414551,2422.989502,2419.353516,2414.139648,2409.516846,2411.966797,2410.234863,2406.112549,2404.696533</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2476.393066,2471.824463,2468.442383,2469.744141,2466.678467,2466.387939,2464.942139,2462.946045,2465.086182,2462.502930,2454.990234,2456.771729,2455.559082,2452.508545,2452.694824,2451.792969,2450.421387,2446.552246,2446.189209,2444.975830,2447.392822,2440.651855,2439.918457,2442.171875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2393,6 +2393,44 @@
       </c>
       <c r="F52" t="n">
         <v>2475.58837890625</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2497.389892578125</v>
+      </c>
+      <c r="H52" t="n">
+        <v>21.801513671875</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.8729719671191867</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.4192499397629185</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:14</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2486.343017578125</v>
       </c>
     </row>
   </sheetData>
@@ -2406,7 +2444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5553,6 +5591,24 @@
           <t>2483.050537,2481.594238,2479.586670,2481.768066,2479.415527,2481.654785,2481.214844,2480.139648,2481.883545,2482.010254,2479.410645,2480.798096,2480.081787,2479.123291,2480.310303,2479.968506,2479.637451,2477.722656,2479.107910,2477.722168,2479.445312,2477.496826,2475.387695,2475.588379</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2472.659912,2467.780029,2478.929932,2476.479980,2491.320068,2479.270020,2473.729980,2471.790039,2458.360107,2485.070068,2498.399902,2496.590088,2487.879883,2486.739990,2482.229980,2483.020020,2482.550049,2488.580078,2484.959961,2496.280029,2497.449951,2494.280029,2488.719971,2497.389893</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>10.390625,13.814209,0.656738,5.288086,11.904541,2.384765,7.484864,8.349609,23.523438,3.059814,18.989257,15.791992,7.798096,7.616699,1.919677,3.051514,2.912598,10.857422,5.852051,18.557861,18.004639,16.783203,13.332276,21.801514</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.420221,0.559783,0.026493,0.213532,0.477841,0.096188,0.302574,0.337796,0.956875,0.123128,0.760057,0.632542,0.313443,0.306293,0.077337,0.122895,0.117323,0.436290,0.235499,0.743421,0.720921,0.672868,0.535708,0.872972</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.4192499397629185</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>2477.554443,2480.110107,2477.230225,2481.977539,2482.961914,2478.470215,2477.927734,2479.669922,2477.545410,2473.816650,2475.472168,2470.606689,2472.026123,2475.337646,2472.004639,2465.253418,2468.879639,2469.168701,2471.915283,2463.210449,2466.980469,2465.530518,2460.012695,2461.171875</t>
@@ -5566,6 +5622,49 @@
       <c r="M52" t="inlineStr">
         <is>
           <t>2476.393066,2471.824463,2468.442383,2469.744141,2466.678467,2466.387939,2464.942139,2462.946045,2465.086182,2462.502930,2454.990234,2456.771729,2455.559082,2452.508545,2452.694824,2451.792969,2450.421387,2446.552246,2446.189209,2444.975830,2447.392822,2440.651855,2439.918457,2442.171875</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:14</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2498.865234,2496.809814,2494.415039,2494.787354,2491.882812,2493.330566,2493.253174,2490.592285,2491.517578,2491.369629,2490.238037,2490.815186,2489.131836,2488.104736,2489.139160,2488.503174,2489.248047,2487.148438,2487.967041,2487.709229,2487.927734,2486.408447,2486.107666,2486.343018</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2492.269775,2493.972412,2492.887695,2490.587402,2493.025879,2486.934570,2487.006836,2488.744873,2484.320068,2486.050781,2485.301025,2480.717773,2481.611572,2484.183594,2481.119141,2477.527832,2479.784180,2476.953125,2479.289551,2475.506104,2477.617188,2475.719238,2472.878662,2475.593018</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2481.775879,2479.480469,2473.009521,2475.475830,2467.705566,2468.760010,2466.380127,2461.676025,2457.006592,2454.075684,2448.554688,2451.726318,2447.694824,2446.741455,2442.783447,2439.148926,2440.089355,2437.761230,2432.917480,2430.168213,2432.332275,2430.426025,2429.201172,2428.223389</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2491.158691,2485.919678,2483.020508,2482.079102,2478.159180,2476.464111,2475.344727,2472.158447,2473.942383,2470.427246,2466.541504,2467.548340,2467.045166,2462.961670,2463.142090,2460.956543,2463.092285,2459.006348,2458.572266,2457.984863,2459.719971,2454.865723,2454.745850,2457.077148</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2431,6 +2431,44 @@
       </c>
       <c r="F53" t="n">
         <v>2486.343017578125</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2476.830078125</v>
+      </c>
+      <c r="H53" t="n">
+        <v>9.512939453125</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.3840771935524316</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.5489840858463235</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:20:03</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>24</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2472.09130859375</v>
       </c>
     </row>
   </sheetData>
@@ -2444,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5652,6 +5690,24 @@
           <t>2498.865234,2496.809814,2494.415039,2494.787354,2491.882812,2493.330566,2493.253174,2490.592285,2491.517578,2491.369629,2490.238037,2490.815186,2489.131836,2488.104736,2489.139160,2488.503174,2489.248047,2487.148438,2487.967041,2487.709229,2487.927734,2486.408447,2486.107666,2486.343018</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2496.260010,2500.879883,2510.209961,2519.709961,2490.020020,2487.139893,2500.149902,2511.100098,2502.060059,2498.780029,2489.850098,2495.479980,2493.250000,2481.040039,2465.000000,2471.120117,2461.199951,2449.500000,2467.719971,2464.040039,2462.919922,2474.169922,2474.500000,2476.830078</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2.605224,4.070069,15.794922,24.922607,1.862792,6.190673,6.896728,20.507813,10.542481,7.410400,0.387939,4.664794,4.118164,7.064697,24.139160,17.383057,28.048096,37.648438,20.247070,23.669190,25.007812,12.238525,11.607666,9.512940</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0.104365,0.162745,0.629227,0.989106,0.074810,0.248907,0.275853,0.816686,0.421352,0.296561,0.015581,0.186930,0.165173,0.284747,0.979276,0.703448,1.139611,1.536985,0.820477,0.960585,1.015373,0.494652,0.469091,0.384077</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0.5489840858463235</v>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>2492.269775,2493.972412,2492.887695,2490.587402,2493.025879,2486.934570,2487.006836,2488.744873,2484.320068,2486.050781,2485.301025,2480.717773,2481.611572,2484.183594,2481.119141,2477.527832,2479.784180,2476.953125,2479.289551,2475.506104,2477.617188,2475.719238,2472.878662,2475.593018</t>
@@ -5665,6 +5721,49 @@
       <c r="M53" t="inlineStr">
         <is>
           <t>2491.158691,2485.919678,2483.020508,2482.079102,2478.159180,2476.464111,2475.344727,2472.158447,2473.942383,2470.427246,2466.541504,2467.548340,2467.045166,2462.961670,2463.142090,2460.956543,2463.092285,2459.006348,2458.572266,2457.984863,2459.719971,2454.865723,2454.745850,2457.077148</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:20:03</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>24</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2476.596680,2474.821289,2474.918213,2475.523193,2472.702881,2472.485596,2473.383057,2472.086426,2472.427002,2472.086182,2471.528076,2473.378906,2472.125977,2471.541016,2472.957520,2471.500488,2471.945312,2470.230957,2472.032471,2471.676270,2470.681152,2471.053223,2471.345215,2472.091309</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2471.592773,2471.750488,2472.954102,2471.474609,2474.601807,2471.363037,2467.599609,2469.568115,2467.239014,2470.155029,2470.890381,2466.004883,2465.280029,2468.356201,2465.860840,2463.248291,2462.918457,2463.131104,2466.062500,2460.744629,2462.662598,2461.947266,2462.328613,2462.867432</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2458.882324,2457.371826,2453.369629,2455.731445,2448.131348,2448.078369,2448.721191,2445.586182,2441.651367,2438.691895,2433.278076,2437.750732,2434.498047,2435.781982,2432.845703,2428.353271,2428.992432,2426.324951,2423.171387,2421.574707,2421.108398,2421.472656,2420.404053,2419.888916</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2468.252930,2463.091309,2462.770996,2461.372070,2456.668945,2454.859619,2455.086182,2453.500244,2455.798828,2451.603027,2447.313965,2449.936523,2450.288330,2448.669678,2449.805908,2446.860107,2447.562744,2443.745605,2445.035156,2445.554199,2445.462402,2441.536865,2441.971680,2444.457275</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2469,6 +2469,44 @@
       </c>
       <c r="F54" t="n">
         <v>2472.09130859375</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2450.330078125</v>
+      </c>
+      <c r="H54" t="n">
+        <v>21.76123046875</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.8880938393982315</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.7418919409334781</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:49</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>24</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2447.28466796875</v>
       </c>
     </row>
   </sheetData>
@@ -2482,7 +2520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5751,6 +5789,24 @@
           <t>2476.596680,2474.821289,2474.918213,2475.523193,2472.702881,2472.485596,2473.383057,2472.086426,2472.427002,2472.086182,2471.528076,2473.378906,2472.125977,2471.541016,2472.957520,2471.500488,2471.945312,2470.230957,2472.032471,2471.676270,2470.681152,2471.053223,2471.345215,2472.091309</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2481.229980,2479.600098,2472.199951,2470.620117,2467.800049,2463.399902,2461.500000,2413.469971,2434.520020,2443.229980,2440.439941,2447.669922,2465.590088,2467.520020,2461.790039,2460.870117,2459.479980,2444.310059,2437.209961,2455.989990,2453.659912,2446.159912,2446.189941,2450.330078</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>4.633300,4.778809,2.718262,4.903076,4.902832,9.085694,11.883057,58.616455,37.906982,28.856202,31.088135,25.708984,6.535889,4.020996,11.167481,10.630371,12.465332,25.920898,34.822510,15.686280,17.021240,24.893311,25.155274,21.761231</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0.186734,0.192725,0.109953,0.198455,0.198672,0.368827,0.482757,2.428721,1.557062,1.181068,1.273874,1.050345,0.265084,0.162957,0.453633,0.431976,0.506828,1.060459,1.428786,0.638695,0.693708,1.017649,1.028345,0.888094</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0.7418919409334781</v>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>2471.592773,2471.750488,2472.954102,2471.474609,2474.601807,2471.363037,2467.599609,2469.568115,2467.239014,2470.155029,2470.890381,2466.004883,2465.280029,2468.356201,2465.860840,2463.248291,2462.918457,2463.131104,2466.062500,2460.744629,2462.662598,2461.947266,2462.328613,2462.867432</t>
@@ -5764,6 +5820,49 @@
       <c r="M54" t="inlineStr">
         <is>
           <t>2468.252930,2463.091309,2462.770996,2461.372070,2456.668945,2454.859619,2455.086182,2453.500244,2455.798828,2451.603027,2447.313965,2449.936523,2450.288330,2448.669678,2449.805908,2446.860107,2447.562744,2443.745605,2445.035156,2445.554199,2445.462402,2441.536865,2441.971680,2444.457275</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:49</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>24</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2451.787598,2450.127686,2449.580566,2451.062988,2450.426025,2450.569336,2450.266357,2449.766846,2450.124023,2449.638672,2448.423828,2450.849854,2450.416992,2450.102295,2451.553467,2451.585449,2451.238525,2448.754395,2449.765381,2448.260986,2449.270508,2448.295410,2446.999756,2447.284668</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2447.910400,2448.388184,2446.703125,2446.625732,2451.067383,2448.359863,2446.308594,2448.320068,2445.903076,2447.212891,2447.789551,2445.034424,2444.746338,2447.966797,2446.854248,2442.620361,2444.848389,2445.912354,2444.889648,2437.865967,2443.151855,2440.691162,2438.062256,2437.452637</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2432.552490,2430.342041,2424.185059,2426.605713,2422.774170,2422.579346,2421.839355,2418.746094,2414.872803,2411.825928,2407.132568,2411.370117,2406.469238,2410.656738,2409.737305,2407.183105,2407.667236,2404.180908,2400.181152,2396.775391,2397.830322,2396.940674,2393.824951,2392.527588</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2442.716797,2437.841309,2435.077637,2434.262451,2431.779053,2430.600098,2430.762451,2429.673340,2431.344727,2427.557617,2422.131104,2425.725342,2426.282227,2425.342285,2428.193848,2427.357178,2425.608643,2422.154785,2422.811035,2421.713379,2422.691650,2417.653320,2416.983887,2418.746094</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2507,6 +2507,44 @@
       </c>
       <c r="F55" t="n">
         <v>2447.28466796875</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2511.860107421875</v>
+      </c>
+      <c r="H55" t="n">
+        <v>64.575439453125</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2.570821490509039</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.659419124667894</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:18:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>24</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2498.6357421875</v>
       </c>
     </row>
   </sheetData>
@@ -2520,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5850,6 +5888,24 @@
           <t>2451.787598,2450.127686,2449.580566,2451.062988,2450.426025,2450.569336,2450.266357,2449.766846,2450.124023,2449.638672,2448.423828,2450.849854,2450.416992,2450.102295,2451.553467,2451.585449,2451.238525,2448.754395,2449.765381,2448.260986,2449.270508,2448.295410,2446.999756,2447.284668</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2467.469971,2466.159912,2466.040039,2475.709961,2468.310059,2461.010010,2457.610107,2510.169922,2626.739990,2607.100098,2558.800049,2577.439941,2566.139893,2536.000000,2539.010010,2530.060059,2516.330078,2511.459961,2516.100098,2511.060059,2513.340088,2514.389893,2512.899902,2511.860107</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>15.682373,16.032226,16.459473,24.646973,17.884034,10.440674,7.343750,60.403076,176.615967,157.461426,110.376221,126.590087,115.722901,85.897705,87.456543,78.474610,65.091553,62.705566,66.334717,62.799073,64.069580,66.094483,65.900146,64.575439</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0.635565,0.650089,0.667445,0.995552,0.724546,0.424243,0.298817,2.406334,6.723770,6.039715,4.313593,4.911466,4.509610,3.387133,3.444514,3.101690,2.586765,2.496777,2.636410,2.500899,2.549181,2.628649,2.622474,2.570821</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>2.659419124667894</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>2447.910400,2448.388184,2446.703125,2446.625732,2451.067383,2448.359863,2446.308594,2448.320068,2445.903076,2447.212891,2447.789551,2445.034424,2444.746338,2447.966797,2446.854248,2442.620361,2444.848389,2445.912354,2444.889648,2437.865967,2443.151855,2440.691162,2438.062256,2437.452637</t>
@@ -5863,6 +5919,49 @@
       <c r="M55" t="inlineStr">
         <is>
           <t>2442.716797,2437.841309,2435.077637,2434.262451,2431.779053,2430.600098,2430.762451,2429.673340,2431.344727,2427.557617,2422.131104,2425.725342,2426.282227,2425.342285,2428.193848,2427.357178,2425.608643,2422.154785,2422.811035,2421.713379,2422.691650,2417.653320,2416.983887,2418.746094</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:18:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>24</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2514.172607,2511.222656,2510.258301,2512.547852,2511.814941,2511.960449,2510.958740,2509.290771,2509.900391,2508.754883,2507.893555,2509.531006,2506.952393,2503.866211,2503.761230,2501.847412,2500.639160,2498.188965,2499.522461,2496.629150,2498.615723,2497.742920,2497.243652,2498.635742</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2507.114014,2508.676270,2509.011719,2510.290527,2510.705811,2507.895508,2503.546631,2508.258789,2502.683350,2508.920166,2502.797852,2502.180664,2495.768799,2498.662842,2495.635498,2496.572021,2490.516113,2486.149414,2488.199707,2484.714600,2488.267822,2489.264404,2488.290283,2486.154297</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2498.208252,2496.766846,2492.307861,2496.304443,2491.252686,2487.730469,2482.454346,2477.019287,2470.904297,2467.665283,2462.815918,2465.367432,2458.213867,2457.687744,2451.775879,2449.135742,2445.751709,2442.060059,2437.429688,2430.491699,2433.125977,2433.155273,2429.552734,2426.330078</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2508.440918,2502.010254,2501.103027,2503.218750,2500.975586,2496.647217,2492.698486,2489.862793,2491.879395,2489.066650,2485.404053,2485.540771,2483.687988,2479.250244,2479.024902,2477.735840,2473.328857,2469.929932,2469.592285,2469.004883,2470.828369,2464.856201,2463.799072,2466.952637</t>
         </is>
       </c>
     </row>
